--- a/data/processed/panel_pais_anio.xlsx
+++ b/data/processed/panel_pais_anio.xlsx
@@ -112,9 +112,6 @@
     <t>ingreso_publico</t>
   </si>
   <si>
-    <t>embig</t>
-  </si>
-  <si>
     <t>subsidio_pc_usd</t>
   </si>
   <si>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>brecha_nga</t>
+  </si>
+  <si>
+    <t>exportador_neto</t>
   </si>
   <si>
     <t>ABW</t>
@@ -893,14 +893,17 @@
       <c r="AC2">
         <v>52.32</v>
       </c>
+      <c r="AI2">
+        <v>0.6346660000000001</v>
+      </c>
       <c r="AJ2">
-        <v>0.6346660000000001</v>
+        <v>0.559889</v>
       </c>
       <c r="AK2">
-        <v>0.559889</v>
-      </c>
-      <c r="AL2">
         <v>-1.558068</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -973,14 +976,17 @@
       <c r="AC3">
         <v>43.64</v>
       </c>
+      <c r="AI3">
+        <v>0.641451</v>
+      </c>
       <c r="AJ3">
-        <v>0.641451</v>
+        <v>0.5633880000000001</v>
       </c>
       <c r="AK3">
-        <v>0.5633880000000001</v>
-      </c>
-      <c r="AL3">
         <v>-1.557264</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1053,14 +1059,17 @@
       <c r="AC4">
         <v>54.13</v>
       </c>
+      <c r="AI4">
+        <v>0.636995</v>
+      </c>
       <c r="AJ4">
-        <v>0.636995</v>
+        <v>0.5632029999999999</v>
       </c>
       <c r="AK4">
-        <v>0.5632029999999999</v>
-      </c>
-      <c r="AL4">
         <v>0.6141319999999979</v>
+      </c>
+      <c r="AL4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1133,14 +1142,17 @@
       <c r="AC5">
         <v>71.34</v>
       </c>
+      <c r="AI5">
+        <v>0.671455</v>
+      </c>
       <c r="AJ5">
-        <v>0.671455</v>
+        <v>0.570015</v>
       </c>
       <c r="AK5">
-        <v>0.570015</v>
-      </c>
-      <c r="AL5">
         <v>2.886388</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1213,14 +1225,17 @@
       <c r="AC6">
         <v>64.3</v>
       </c>
+      <c r="AI6">
+        <v>0.6840200000000001</v>
+      </c>
       <c r="AJ6">
-        <v>0.6840200000000001</v>
+        <v>0.590947</v>
       </c>
       <c r="AK6">
-        <v>0.590947</v>
-      </c>
-      <c r="AL6">
         <v>-1.653452000000001</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1293,14 +1308,17 @@
       <c r="AC7">
         <v>41.96</v>
       </c>
+      <c r="AI7">
+        <v>0.7618630000000001</v>
+      </c>
       <c r="AJ7">
-        <v>0.7618630000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="AK7">
-        <v>0.6355</v>
-      </c>
-      <c r="AL7">
         <v>-6.039182</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1367,14 +1385,17 @@
       <c r="AC8">
         <v>70.86</v>
       </c>
+      <c r="AI8">
+        <v>0.7449480000000001</v>
+      </c>
       <c r="AJ8">
-        <v>0.7449480000000001</v>
+        <v>0.616397</v>
       </c>
       <c r="AK8">
-        <v>0.616397</v>
-      </c>
-      <c r="AL8">
         <v>-6.061880000000002</v>
+      </c>
+      <c r="AL8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1441,14 +1462,17 @@
       <c r="AC9">
         <v>100.93</v>
       </c>
+      <c r="AI9">
+        <v>0.74829</v>
+      </c>
       <c r="AJ9">
-        <v>0.74829</v>
+        <v>0.7249060000000001</v>
       </c>
       <c r="AK9">
-        <v>0.7249060000000001</v>
-      </c>
-      <c r="AL9">
         <v>-5.981989</v>
+      </c>
+      <c r="AL9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1515,14 +1539,17 @@
       <c r="AC10">
         <v>82.48999999999999</v>
       </c>
+      <c r="AI10">
+        <v>0.7407339999999999</v>
+      </c>
       <c r="AJ10">
-        <v>0.7407339999999999</v>
+        <v>0.8275380000000001</v>
       </c>
       <c r="AK10">
-        <v>0.8275380000000001</v>
-      </c>
-      <c r="AL10">
         <v>-5.981839000000001</v>
+      </c>
+      <c r="AL10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1620,22 +1647,22 @@
         <v>22.1490803040164</v>
       </c>
       <c r="AG11">
-        <v>589.8</v>
+        <v>0.9986617829592704</v>
       </c>
       <c r="AH11">
-        <v>0.9986617829592704</v>
+        <v>0.3448304460971852</v>
       </c>
       <c r="AI11">
-        <v>0.3448304460971852</v>
+        <v>0.797229</v>
       </c>
       <c r="AJ11">
-        <v>0.797229</v>
+        <v>0.7063370000000001</v>
       </c>
       <c r="AK11">
-        <v>0.7063370000000001</v>
-      </c>
-      <c r="AL11">
         <v>-11.52011476141434</v>
+      </c>
+      <c r="AL11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1733,22 +1760,22 @@
         <v>21.2567013071388</v>
       </c>
       <c r="AG12">
-        <v>475.6</v>
+        <v>0.8456930680351684</v>
       </c>
       <c r="AH12">
-        <v>0.8456930680351684</v>
+        <v>0.1970500786827665</v>
       </c>
       <c r="AI12">
-        <v>0.1970500786827665</v>
+        <v>0.6513</v>
       </c>
       <c r="AJ12">
-        <v>0.6513</v>
+        <v>0.5724489999999999</v>
       </c>
       <c r="AK12">
-        <v>0.5724489999999999</v>
-      </c>
-      <c r="AL12">
         <v>-5.043751</v>
+      </c>
+      <c r="AL12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -1846,22 +1873,22 @@
         <v>19.3371239744582</v>
       </c>
       <c r="AG13">
-        <v>412</v>
+        <v>0.7605615721708542</v>
       </c>
       <c r="AH13">
-        <v>0.7605615721708542</v>
+        <v>0.1799570228689238</v>
       </c>
       <c r="AI13">
-        <v>0.1799570228689238</v>
+        <v>0.646995</v>
       </c>
       <c r="AJ13">
-        <v>0.646995</v>
+        <v>0.521049</v>
       </c>
       <c r="AK13">
-        <v>0.521049</v>
-      </c>
-      <c r="AL13">
         <v>-3.726535</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -1959,22 +1986,22 @@
         <v>17.7024488717292</v>
       </c>
       <c r="AG14">
-        <v>547.5</v>
+        <v>0.864184420512183</v>
       </c>
       <c r="AH14">
-        <v>0.864184420512183</v>
+        <v>0.2375619748667303</v>
       </c>
       <c r="AI14">
-        <v>0.2375619748667303</v>
+        <v>0.374723</v>
       </c>
       <c r="AJ14">
-        <v>0.374723</v>
+        <v>0.239049</v>
       </c>
       <c r="AK14">
-        <v>0.239049</v>
-      </c>
-      <c r="AL14">
         <v>-5.228548</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2072,22 +2099,22 @@
         <v>17.7888990504455</v>
       </c>
       <c r="AG15">
-        <v>1316.5</v>
+        <v>0.8013857314531383</v>
       </c>
       <c r="AH15">
-        <v>0.8013857314531383</v>
+        <v>0.1988898471626896</v>
       </c>
       <c r="AI15">
-        <v>0.1988898471626896</v>
+        <v>0.2196419999999999</v>
       </c>
       <c r="AJ15">
-        <v>0.2196419999999999</v>
+        <v>0.172181</v>
       </c>
       <c r="AK15">
-        <v>0.172181</v>
-      </c>
-      <c r="AL15">
         <v>-3.773823999999999</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2185,22 +2212,22 @@
         <v>17.4777322783093</v>
       </c>
       <c r="AG16">
-        <v>2235.2</v>
+        <v>0.6219406994652591</v>
       </c>
       <c r="AH16">
-        <v>0.6219406994652591</v>
+        <v>0.1783335106128036</v>
       </c>
       <c r="AI16">
-        <v>0.1783335106128036</v>
+        <v>0.353249</v>
       </c>
       <c r="AJ16">
-        <v>0.353249</v>
+        <v>0.305328</v>
       </c>
       <c r="AK16">
-        <v>0.305328</v>
-      </c>
-      <c r="AL16">
         <v>-3.010518000000001</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2298,22 +2325,22 @@
         <v>18.0764989044589</v>
       </c>
       <c r="AG17">
-        <v>1578</v>
+        <v>1.054314013380204</v>
       </c>
       <c r="AH17">
-        <v>1.054314013380204</v>
+        <v>0.3132579521849953</v>
       </c>
       <c r="AI17">
-        <v>0.3132579521849953</v>
+        <v>0.1414200000000001</v>
       </c>
       <c r="AJ17">
-        <v>0.1414200000000001</v>
+        <v>0.1562969999999999</v>
       </c>
       <c r="AK17">
-        <v>0.1562969999999999</v>
-      </c>
-      <c r="AL17">
         <v>-9.563148</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2411,22 +2438,22 @@
         <v>17.893195301026</v>
       </c>
       <c r="AG18">
-        <v>2174.7</v>
+        <v>1.282986343283853</v>
       </c>
       <c r="AH18">
-        <v>1.282986343283853</v>
+        <v>0.3334231425549618</v>
       </c>
       <c r="AI18">
-        <v>0.3334231425549618</v>
+        <v>-0.1283609999999999</v>
       </c>
       <c r="AJ18">
-        <v>-0.1283609999999999</v>
+        <v>-0.141312</v>
       </c>
       <c r="AK18">
-        <v>-0.141312</v>
-      </c>
-      <c r="AL18">
         <v>-10.006493</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2524,22 +2551,22 @@
         <v>17.7753274051522</v>
       </c>
       <c r="AG19">
-        <v>2223</v>
+        <v>1.021644018452963</v>
       </c>
       <c r="AH19">
-        <v>1.021644018452963</v>
+        <v>0.2625451417601113</v>
       </c>
       <c r="AI19">
-        <v>0.2625451417601113</v>
+        <v>-0.09214300000000009</v>
       </c>
       <c r="AJ19">
-        <v>-0.09214300000000009</v>
+        <v>0.1926190000000001</v>
       </c>
       <c r="AK19">
-        <v>0.1926190000000001</v>
-      </c>
-      <c r="AL19">
         <v>-6.907171</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2612,14 +2639,17 @@
       <c r="AC20">
         <v>52.32</v>
       </c>
+      <c r="AI20">
+        <v>0.7194199999999999</v>
+      </c>
       <c r="AJ20">
-        <v>0.7194199999999999</v>
+        <v>0.307774</v>
       </c>
       <c r="AK20">
-        <v>0.307774</v>
-      </c>
-      <c r="AL20">
         <v>0.3932029999999997</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -2692,14 +2722,17 @@
       <c r="AC21">
         <v>43.64</v>
       </c>
+      <c r="AI21">
+        <v>0.8512500000000001</v>
+      </c>
       <c r="AJ21">
-        <v>0.8512500000000001</v>
+        <v>0.4255829999999999</v>
       </c>
       <c r="AK21">
-        <v>0.4255829999999999</v>
-      </c>
-      <c r="AL21">
         <v>0.3496109999999994</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -2772,14 +2805,17 @@
       <c r="AC22">
         <v>54.13</v>
       </c>
+      <c r="AI22">
+        <v>0.7283490000000001</v>
+      </c>
       <c r="AJ22">
-        <v>0.7283490000000001</v>
+        <v>0.3587130000000001</v>
       </c>
       <c r="AK22">
-        <v>0.3587130000000001</v>
-      </c>
-      <c r="AL22">
         <v>0.3812020000000018</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -2852,14 +2888,17 @@
       <c r="AC23">
         <v>71.34</v>
       </c>
+      <c r="AI23">
+        <v>0.6012479999999999</v>
+      </c>
       <c r="AJ23">
-        <v>0.6012479999999999</v>
+        <v>0.261412</v>
       </c>
       <c r="AK23">
-        <v>0.261412</v>
-      </c>
-      <c r="AL23">
         <v>0.4217009999999988</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:38">
@@ -2932,14 +2971,17 @@
       <c r="AC24">
         <v>64.3</v>
       </c>
+      <c r="AI24">
+        <v>0.6439009999999999</v>
+      </c>
       <c r="AJ24">
-        <v>0.6439009999999999</v>
+        <v>0.3049209999999999</v>
       </c>
       <c r="AK24">
-        <v>0.3049209999999999</v>
-      </c>
-      <c r="AL24">
         <v>0.3258829999999975</v>
+      </c>
+      <c r="AL24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -3012,14 +3054,17 @@
       <c r="AC25">
         <v>41.96</v>
       </c>
+      <c r="AI25">
+        <v>0.88332</v>
+      </c>
       <c r="AJ25">
-        <v>0.88332</v>
+        <v>0.498842</v>
       </c>
       <c r="AK25">
-        <v>0.498842</v>
-      </c>
-      <c r="AL25">
         <v>0.2979979999999998</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:38">
@@ -3110,20 +3155,23 @@
       <c r="AC26">
         <v>70.86</v>
       </c>
+      <c r="AG26">
+        <v>0.5720372261497413</v>
+      </c>
       <c r="AH26">
-        <v>0.5720372261497413</v>
+        <v>0.1253673501788355</v>
       </c>
       <c r="AI26">
-        <v>0.1253673501788355</v>
+        <v>0.5518819999999999</v>
       </c>
       <c r="AJ26">
-        <v>0.5518819999999999</v>
+        <v>0.2456590000000001</v>
       </c>
       <c r="AK26">
-        <v>0.2456590000000001</v>
-      </c>
-      <c r="AL26">
         <v>0.5814889999999977</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -3214,20 +3262,23 @@
       <c r="AC27">
         <v>100.93</v>
       </c>
+      <c r="AG27">
+        <v>0.6715103964603115</v>
+      </c>
       <c r="AH27">
-        <v>0.6715103964603115</v>
+        <v>0.1022329949611937</v>
       </c>
       <c r="AI27">
-        <v>0.1022329949611937</v>
+        <v>0.486596</v>
       </c>
       <c r="AJ27">
-        <v>0.486596</v>
+        <v>0.1210800000000001</v>
       </c>
       <c r="AK27">
-        <v>0.1210800000000001</v>
-      </c>
-      <c r="AL27">
         <v>0.8436900000000023</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -3318,20 +3369,23 @@
       <c r="AC28">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG28">
+        <v>0.4899296458964391</v>
+      </c>
       <c r="AH28">
-        <v>0.4899296458964391</v>
+        <v>0.1743000039893411</v>
       </c>
       <c r="AI28">
-        <v>0.1743000039893411</v>
+        <v>0.637524</v>
       </c>
       <c r="AJ28">
-        <v>0.637524</v>
+        <v>0.565848</v>
       </c>
       <c r="AK28">
-        <v>0.565848</v>
-      </c>
-      <c r="AL28">
         <v>0.4429639999999999</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -3431,20 +3485,23 @@
       <c r="AF29">
         <v>14.6273782452524</v>
       </c>
+      <c r="AG29">
+        <v>0.4560006036404706</v>
+      </c>
       <c r="AH29">
-        <v>0.4560006036404706</v>
+        <v>0.004822801297914218</v>
       </c>
       <c r="AI29">
-        <v>0.004822801297914218</v>
+        <v>0.7321899999999999</v>
       </c>
       <c r="AJ29">
-        <v>0.7321899999999999</v>
+        <v>0.612677</v>
       </c>
       <c r="AK29">
-        <v>0.612677</v>
-      </c>
-      <c r="AL29">
         <v>0.0001989999999985059</v>
+      </c>
+      <c r="AL29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:38">
@@ -3544,20 +3601,23 @@
       <c r="AF30">
         <v>16.7435935230496</v>
       </c>
+      <c r="AG30">
+        <v>0.5174097130947023</v>
+      </c>
       <c r="AH30">
-        <v>0.5174097130947023</v>
+        <v>0.002876664953659235</v>
       </c>
       <c r="AI30">
-        <v>0.002876664953659235</v>
+        <v>0.6953780000000001</v>
       </c>
       <c r="AJ30">
-        <v>0.6953780000000001</v>
+        <v>0.557866</v>
       </c>
       <c r="AK30">
-        <v>0.557866</v>
-      </c>
-      <c r="AL30">
         <v>-0.0001310000000032119</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:38">
@@ -3657,20 +3717,23 @@
       <c r="AF31">
         <v>16.6326878235545</v>
       </c>
+      <c r="AG31">
+        <v>0.8617648528569762</v>
+      </c>
       <c r="AH31">
-        <v>0.8617648528569762</v>
+        <v>0.004543280521858236</v>
       </c>
       <c r="AI31">
-        <v>0.004543280521858236</v>
+        <v>0.70523</v>
       </c>
       <c r="AJ31">
-        <v>0.70523</v>
+        <v>0.5693039999999999</v>
       </c>
       <c r="AK31">
-        <v>0.5693039999999999</v>
-      </c>
-      <c r="AL31">
         <v>0.0001919999999984157</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:38">
@@ -3770,20 +3833,23 @@
       <c r="AF32">
         <v>15.9117105591613</v>
       </c>
+      <c r="AG32">
+        <v>0.6680470336684079</v>
+      </c>
       <c r="AH32">
-        <v>0.6680470336684079</v>
+        <v>0.003427961240044781</v>
       </c>
       <c r="AI32">
-        <v>0.003427961240044781</v>
+        <v>0.8060419999999999</v>
       </c>
       <c r="AJ32">
-        <v>0.8060419999999999</v>
+        <v>0.6233399999999999</v>
       </c>
       <c r="AK32">
-        <v>0.6233399999999999</v>
-      </c>
-      <c r="AL32">
         <v>3.099999999989222E-05</v>
+      </c>
+      <c r="AL32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:38">
@@ -3883,20 +3949,23 @@
       <c r="AF33">
         <v>18.2742562325827</v>
       </c>
+      <c r="AG33">
+        <v>0.594675810768165</v>
+      </c>
       <c r="AH33">
-        <v>0.594675810768165</v>
+        <v>0.002069143664126318</v>
       </c>
       <c r="AI33">
-        <v>0.002069143664126318</v>
+        <v>0.8033670000000001</v>
       </c>
       <c r="AJ33">
-        <v>0.8033670000000001</v>
+        <v>0.620844</v>
       </c>
       <c r="AK33">
-        <v>0.620844</v>
-      </c>
-      <c r="AL33">
         <v>0.0001839999999972974</v>
+      </c>
+      <c r="AL33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:38">
@@ -3996,20 +4065,23 @@
       <c r="AF34">
         <v>20.1369104813185</v>
       </c>
+      <c r="AG34">
+        <v>0.2614321247077997</v>
+      </c>
       <c r="AH34">
-        <v>0.2614321247077997</v>
+        <v>0.003942436261446929</v>
       </c>
       <c r="AI34">
-        <v>0.003942436261446929</v>
+        <v>0.7891699999999999</v>
       </c>
       <c r="AJ34">
-        <v>0.7891699999999999</v>
+        <v>0.5933790000000001</v>
       </c>
       <c r="AK34">
-        <v>0.5933790000000001</v>
-      </c>
-      <c r="AL34">
         <v>-4.899999999707916E-05</v>
+      </c>
+      <c r="AL34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -4109,20 +4181,23 @@
       <c r="AF35">
         <v>15.8516580958711</v>
       </c>
+      <c r="AG35">
+        <v>0.744087907693997</v>
+      </c>
       <c r="AH35">
-        <v>0.744087907693997</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>0.770316</v>
       </c>
       <c r="AJ35">
-        <v>0.770316</v>
+        <v>0.5784539999999999</v>
       </c>
       <c r="AK35">
-        <v>0.5784539999999999</v>
-      </c>
-      <c r="AL35">
         <v>0.0005090000000009809</v>
+      </c>
+      <c r="AL35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:38">
@@ -4222,20 +4297,23 @@
       <c r="AF36">
         <v>18.7489017543607</v>
       </c>
+      <c r="AG36">
+        <v>1.025361325992459</v>
+      </c>
       <c r="AH36">
-        <v>1.025361325992459</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>0.7805500000000001</v>
       </c>
       <c r="AJ36">
-        <v>0.7805500000000001</v>
+        <v>0.585833</v>
       </c>
       <c r="AK36">
-        <v>0.585833</v>
-      </c>
-      <c r="AL36">
         <v>0.0002139999999997144</v>
+      </c>
+      <c r="AL36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:38">
@@ -4335,20 +4413,23 @@
       <c r="AF37">
         <v>18.691039629894</v>
       </c>
+      <c r="AG37">
+        <v>0.9544623982118635</v>
+      </c>
       <c r="AH37">
-        <v>0.9544623982118635</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>0.799505</v>
       </c>
       <c r="AJ37">
-        <v>0.799505</v>
+        <v>0.6173179999999999</v>
       </c>
       <c r="AK37">
-        <v>0.6173179999999999</v>
-      </c>
-      <c r="AL37">
         <v>-0.0007200000000011642</v>
+      </c>
+      <c r="AL37" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -4445,20 +4526,23 @@
       <c r="AF38">
         <v>22.1980924438071</v>
       </c>
+      <c r="AG38">
+        <v>0.01616345087384453</v>
+      </c>
       <c r="AH38">
-        <v>0.01616345087384453</v>
+        <v>0.2372427777605076</v>
       </c>
       <c r="AI38">
-        <v>0.2372427777605076</v>
+        <v>0.6281059999999999</v>
       </c>
       <c r="AJ38">
-        <v>0.6281059999999999</v>
+        <v>0.6039519999999999</v>
       </c>
       <c r="AK38">
-        <v>0.6039519999999999</v>
-      </c>
-      <c r="AL38">
         <v>-0.0001649999999990825</v>
+      </c>
+      <c r="AL38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -4555,20 +4639,23 @@
       <c r="AF39">
         <v>22.4029818854459</v>
       </c>
+      <c r="AG39">
+        <v>0.01696077064510215</v>
+      </c>
       <c r="AH39">
-        <v>0.01696077064510215</v>
+        <v>0.1797507574269304</v>
       </c>
       <c r="AI39">
-        <v>0.1797507574269304</v>
+        <v>0.852471</v>
       </c>
       <c r="AJ39">
-        <v>0.852471</v>
+        <v>0.750429</v>
       </c>
       <c r="AK39">
-        <v>0.750429</v>
-      </c>
-      <c r="AL39">
         <v>0.0008169999999978472</v>
+      </c>
+      <c r="AL39" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:38">
@@ -4665,20 +4752,23 @@
       <c r="AF40">
         <v>23.8070928559695</v>
       </c>
+      <c r="AG40">
+        <v>0.02259485649453168</v>
+      </c>
       <c r="AH40">
-        <v>0.02259485649453168</v>
+        <v>0.3123273387420333</v>
       </c>
       <c r="AI40">
-        <v>0.3123273387420333</v>
+        <v>0.9857860000000001</v>
       </c>
       <c r="AJ40">
-        <v>0.9857860000000001</v>
+        <v>0.7992210000000001</v>
       </c>
       <c r="AK40">
-        <v>0.7992210000000001</v>
-      </c>
-      <c r="AL40">
         <v>0.0009600000000027364</v>
+      </c>
+      <c r="AL40" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:38">
@@ -4769,20 +4859,23 @@
       <c r="AC41">
         <v>71.34</v>
       </c>
+      <c r="AG41">
+        <v>0.02821093916367924</v>
+      </c>
       <c r="AH41">
-        <v>0.02821093916367924</v>
+        <v>0.405034681111427</v>
       </c>
       <c r="AI41">
-        <v>0.405034681111427</v>
+        <v>0.951076</v>
       </c>
       <c r="AJ41">
-        <v>0.951076</v>
+        <v>0.7499909999999999</v>
       </c>
       <c r="AK41">
-        <v>0.7499909999999999</v>
-      </c>
-      <c r="AL41">
         <v>-0.0009370000000004097</v>
+      </c>
+      <c r="AL41" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -4873,20 +4966,23 @@
       <c r="AC42">
         <v>64.3</v>
       </c>
+      <c r="AG42">
+        <v>0.09555183267902002</v>
+      </c>
       <c r="AH42">
-        <v>0.09555183267902002</v>
+        <v>0.8253029733504709</v>
       </c>
       <c r="AI42">
-        <v>0.8253029733504709</v>
+        <v>0.9051620000000001</v>
       </c>
       <c r="AJ42">
-        <v>0.9051620000000001</v>
+        <v>0.7539369999999999</v>
       </c>
       <c r="AK42">
-        <v>0.7539369999999999</v>
-      </c>
-      <c r="AL42">
         <v>0.0001539999999984332</v>
+      </c>
+      <c r="AL42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:38">
@@ -4977,19 +5073,22 @@
       <c r="AC43">
         <v>41.96</v>
       </c>
+      <c r="AG43">
+        <v>0.02374291669392448</v>
+      </c>
       <c r="AH43">
-        <v>0.02374291669392448</v>
+        <v>0.3057506913829312</v>
       </c>
       <c r="AI43">
-        <v>0.3057506913829312</v>
+        <v>0.9389660000000001</v>
       </c>
       <c r="AJ43">
-        <v>0.9389660000000001</v>
+        <v>0.7788160000000001</v>
       </c>
       <c r="AK43">
-        <v>0.7788160000000001</v>
-      </c>
-      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5081,20 +5180,23 @@
       <c r="AC44">
         <v>70.86</v>
       </c>
+      <c r="AG44">
+        <v>0.04773712955697176</v>
+      </c>
       <c r="AH44">
-        <v>0.04773712955697176</v>
+        <v>0.6456843742329527</v>
       </c>
       <c r="AI44">
-        <v>0.6456843742329527</v>
+        <v>0.8175559999999999</v>
       </c>
       <c r="AJ44">
-        <v>0.8175559999999999</v>
+        <v>0.7183259999999999</v>
       </c>
       <c r="AK44">
-        <v>0.7183259999999999</v>
-      </c>
-      <c r="AL44">
         <v>0.000868000000000535</v>
+      </c>
+      <c r="AL44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:38">
@@ -5185,20 +5287,23 @@
       <c r="AC45">
         <v>100.93</v>
       </c>
+      <c r="AG45">
+        <v>0.1614112318518836</v>
+      </c>
       <c r="AH45">
-        <v>0.1614112318518836</v>
+        <v>0.4141747611438393</v>
       </c>
       <c r="AI45">
-        <v>0.4141747611438393</v>
+        <v>0.4231310000000001</v>
       </c>
       <c r="AJ45">
-        <v>0.4231310000000001</v>
+        <v>0.377936</v>
       </c>
       <c r="AK45">
-        <v>0.377936</v>
-      </c>
-      <c r="AL45">
         <v>-0.000401999999997571</v>
+      </c>
+      <c r="AL45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:38">
@@ -5289,20 +5394,23 @@
       <c r="AC46">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG46">
+        <v>0.1158677341079852</v>
+      </c>
       <c r="AH46">
-        <v>0.1158677341079852</v>
+        <v>0.5659391015557231</v>
       </c>
       <c r="AI46">
-        <v>0.5659391015557231</v>
+        <v>0.463083</v>
       </c>
       <c r="AJ46">
-        <v>0.463083</v>
+        <v>0.570354</v>
       </c>
       <c r="AK46">
-        <v>0.570354</v>
-      </c>
-      <c r="AL46">
         <v>0.0007719999999995508</v>
+      </c>
+      <c r="AL46" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -5393,20 +5501,23 @@
       <c r="AC47">
         <v>52.32</v>
       </c>
+      <c r="AG47">
+        <v>0.339712184452695</v>
+      </c>
       <c r="AH47">
-        <v>0.339712184452695</v>
+        <v>0.3152180059634936</v>
       </c>
       <c r="AI47">
-        <v>0.3152180059634936</v>
+        <v>-0.23706</v>
       </c>
       <c r="AJ47">
-        <v>-0.23706</v>
+        <v>-0.02617000000000003</v>
       </c>
       <c r="AK47">
-        <v>-0.02617000000000003</v>
-      </c>
-      <c r="AL47">
         <v>-9.860749000000002</v>
+      </c>
+      <c r="AL47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:38">
@@ -5497,20 +5608,23 @@
       <c r="AC48">
         <v>43.64</v>
       </c>
+      <c r="AG48">
+        <v>0.2815176868441289</v>
+      </c>
       <c r="AH48">
-        <v>0.2815176868441289</v>
+        <v>0.1962194716022663</v>
       </c>
       <c r="AI48">
-        <v>0.1962194716022663</v>
+        <v>-0.102531</v>
       </c>
       <c r="AJ48">
-        <v>-0.102531</v>
+        <v>0.06631600000000004</v>
       </c>
       <c r="AK48">
-        <v>0.06631600000000004</v>
-      </c>
-      <c r="AL48">
         <v>-5.551352000000001</v>
+      </c>
+      <c r="AL48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -5601,20 +5715,23 @@
       <c r="AC49">
         <v>54.13</v>
       </c>
+      <c r="AG49">
+        <v>0.3505525893803847</v>
+      </c>
       <c r="AH49">
-        <v>0.3505525893803847</v>
+        <v>0.2335003345158158</v>
       </c>
       <c r="AI49">
-        <v>0.2335003345158158</v>
+        <v>-0.2031879999999999</v>
       </c>
       <c r="AJ49">
-        <v>-0.2031879999999999</v>
+        <v>-0.03719299999999992</v>
       </c>
       <c r="AK49">
-        <v>-0.03719299999999992</v>
-      </c>
-      <c r="AL49">
         <v>-3.558459999999999</v>
+      </c>
+      <c r="AL49" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:38">
@@ -5705,20 +5822,23 @@
       <c r="AC50">
         <v>71.34</v>
       </c>
+      <c r="AG50">
+        <v>0.4594643788762242</v>
+      </c>
       <c r="AH50">
-        <v>0.4594643788762242</v>
+        <v>0.3790147583477143</v>
       </c>
       <c r="AI50">
-        <v>0.3790147583477143</v>
+        <v>-0.308253</v>
       </c>
       <c r="AJ50">
-        <v>-0.308253</v>
+        <v>-0.195557</v>
       </c>
       <c r="AK50">
-        <v>-0.195557</v>
-      </c>
-      <c r="AL50">
         <v>-5.038514000000001</v>
+      </c>
+      <c r="AL50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:38">
@@ -5809,20 +5929,23 @@
       <c r="AC51">
         <v>64.3</v>
       </c>
+      <c r="AG51">
+        <v>0.4144535761973656</v>
+      </c>
       <c r="AH51">
-        <v>0.4144535761973656</v>
+        <v>0.2809787979196107</v>
       </c>
       <c r="AI51">
-        <v>0.2809787979196107</v>
+        <v>-0.248711</v>
       </c>
       <c r="AJ51">
-        <v>-0.248711</v>
+        <v>-0.141208</v>
       </c>
       <c r="AK51">
-        <v>-0.141208</v>
-      </c>
-      <c r="AL51">
         <v>0.2625339999999987</v>
+      </c>
+      <c r="AL51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:38">
@@ -5913,20 +6036,23 @@
       <c r="AC52">
         <v>41.96</v>
       </c>
+      <c r="AG52">
+        <v>0.2367720133613741</v>
+      </c>
       <c r="AH52">
-        <v>0.2367720133613741</v>
+        <v>0.1430446636716746</v>
       </c>
       <c r="AI52">
-        <v>0.1430446636716746</v>
+        <v>-0.0007759999999999989</v>
       </c>
       <c r="AJ52">
-        <v>-0.0007759999999999989</v>
+        <v>0.09414399999999995</v>
       </c>
       <c r="AK52">
-        <v>0.09414399999999995</v>
-      </c>
-      <c r="AL52">
         <v>-1.219817000000001</v>
+      </c>
+      <c r="AL52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:38">
@@ -6017,20 +6143,23 @@
       <c r="AC53">
         <v>70.86</v>
       </c>
+      <c r="AG53">
+        <v>0.4934436730221975</v>
+      </c>
       <c r="AH53">
-        <v>0.4934436730221975</v>
+        <v>0.3808753684116203</v>
       </c>
       <c r="AI53">
-        <v>0.3808753684116203</v>
+        <v>-0.31441</v>
       </c>
       <c r="AJ53">
-        <v>-0.31441</v>
+        <v>-0.1496770000000001</v>
       </c>
       <c r="AK53">
-        <v>-0.1496770000000001</v>
-      </c>
-      <c r="AL53">
         <v>-9.517052</v>
+      </c>
+      <c r="AL53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:38">
@@ -6121,20 +6250,23 @@
       <c r="AC54">
         <v>100.93</v>
       </c>
+      <c r="AG54">
+        <v>0.659263495616622</v>
+      </c>
       <c r="AH54">
-        <v>0.659263495616622</v>
+        <v>0.4887198209572496</v>
       </c>
       <c r="AI54">
-        <v>0.4887198209572496</v>
+        <v>-0.5952529999999999</v>
       </c>
       <c r="AJ54">
-        <v>-0.5952529999999999</v>
+        <v>-0.48922</v>
       </c>
       <c r="AK54">
-        <v>-0.48922</v>
-      </c>
-      <c r="AL54">
         <v>-9.516555</v>
+      </c>
+      <c r="AL54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:38">
@@ -6225,20 +6357,23 @@
       <c r="AC55">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG55">
+        <v>0.5289632395689846</v>
+      </c>
       <c r="AH55">
-        <v>0.5289632395689846</v>
+        <v>0.3860885022699449</v>
       </c>
       <c r="AI55">
-        <v>0.3860885022699449</v>
+        <v>-0.4444149999999999</v>
       </c>
       <c r="AJ55">
-        <v>-0.4444149999999999</v>
+        <v>-0.154438</v>
       </c>
       <c r="AK55">
-        <v>-0.154438</v>
-      </c>
-      <c r="AL55">
         <v>-8.351131999999998</v>
+      </c>
+      <c r="AL55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:38">
@@ -6339,22 +6474,22 @@
         <v>25.8123252140431</v>
       </c>
       <c r="AG56">
-        <v>360.3</v>
+        <v>0.1989257779608123</v>
       </c>
       <c r="AH56">
-        <v>0.1989257779608123</v>
+        <v>0.02553335979550531</v>
       </c>
       <c r="AI56">
-        <v>0.02553335979550531</v>
+        <v>0.420272</v>
       </c>
       <c r="AJ56">
-        <v>0.420272</v>
+        <v>0.3784760000000001</v>
       </c>
       <c r="AK56">
-        <v>0.3784760000000001</v>
-      </c>
-      <c r="AL56">
         <v>-9.039189575061371</v>
+      </c>
+      <c r="AL56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:38">
@@ -6455,22 +6590,22 @@
         <v>26.173225388189</v>
       </c>
       <c r="AG57">
-        <v>395.4</v>
+        <v>0.1591596304688321</v>
       </c>
       <c r="AH57">
-        <v>0.1591596304688321</v>
+        <v>0.03525790519664117</v>
       </c>
       <c r="AI57">
-        <v>0.03525790519664117</v>
+        <v>0.6153590000000001</v>
       </c>
       <c r="AJ57">
-        <v>0.6153590000000001</v>
+        <v>0.47548</v>
       </c>
       <c r="AK57">
-        <v>0.47548</v>
-      </c>
-      <c r="AL57">
         <v>-8.501096906381314</v>
+      </c>
+      <c r="AL57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:38">
@@ -6571,22 +6706,22 @@
         <v>24.3609920782892</v>
       </c>
       <c r="AG58">
-        <v>263.5</v>
+        <v>0.1797728297184986</v>
       </c>
       <c r="AH58">
-        <v>0.1797728297184986</v>
+        <v>0.03082807036662708</v>
       </c>
       <c r="AI58">
-        <v>0.03082807036662708</v>
+        <v>0.653685</v>
       </c>
       <c r="AJ58">
-        <v>0.653685</v>
+        <v>0.4875720000000001</v>
       </c>
       <c r="AK58">
-        <v>0.4875720000000001</v>
-      </c>
-      <c r="AL58">
         <v>-8.153611630473939</v>
+      </c>
+      <c r="AL58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:38">
@@ -6687,22 +6822,22 @@
         <v>25.2724385286024</v>
       </c>
       <c r="AG59">
-        <v>264.5</v>
+        <v>0.1973861296504714</v>
       </c>
       <c r="AH59">
-        <v>0.1973861296504714</v>
+        <v>0.0307429295615615</v>
       </c>
       <c r="AI59">
-        <v>0.0307429295615615</v>
+        <v>0.5621229999999999</v>
       </c>
       <c r="AJ59">
-        <v>0.5621229999999999</v>
+        <v>0.3008879999999999</v>
       </c>
       <c r="AK59">
-        <v>0.3008879999999999</v>
-      </c>
-      <c r="AL59">
         <v>-7.275042633058519</v>
+      </c>
+      <c r="AL59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -6803,22 +6938,22 @@
         <v>25.5600401306072</v>
       </c>
       <c r="AG60">
-        <v>235.5</v>
+        <v>0.2219138568021822</v>
       </c>
       <c r="AH60">
-        <v>0.2219138568021822</v>
+        <v>0.04043239789457322</v>
       </c>
       <c r="AI60">
-        <v>0.04043239789457322</v>
+        <v>0.4859049999999999</v>
       </c>
       <c r="AJ60">
-        <v>0.4859049999999999</v>
+        <v>0.2909390000000001</v>
       </c>
       <c r="AK60">
-        <v>0.2909390000000001</v>
-      </c>
-      <c r="AL60">
         <v>-8.563268206696364</v>
+      </c>
+      <c r="AL60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:38">
@@ -6919,22 +7054,22 @@
         <v>22.1948673455795</v>
       </c>
       <c r="AG61">
-        <v>316.5</v>
+        <v>0.2104521730849312</v>
       </c>
       <c r="AH61">
-        <v>0.2104521730849312</v>
+        <v>0.02925697551759552</v>
       </c>
       <c r="AI61">
-        <v>0.02925697551759552</v>
+        <v>0.411819</v>
       </c>
       <c r="AJ61">
-        <v>0.411819</v>
+        <v>0.26701</v>
       </c>
       <c r="AK61">
-        <v>0.26701</v>
-      </c>
-      <c r="AL61">
         <v>-7.073888609481067</v>
+      </c>
+      <c r="AL61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -7035,22 +7170,22 @@
         <v>24.6358299212806</v>
       </c>
       <c r="AG62">
-        <v>281.2</v>
+        <v>0.3168810523575522</v>
       </c>
       <c r="AH62">
-        <v>0.3168810523575522</v>
+        <v>0.0186064545479455</v>
       </c>
       <c r="AI62">
-        <v>0.0186064545479455</v>
+        <v>0.3534409999999999</v>
       </c>
       <c r="AJ62">
-        <v>0.3534409999999999</v>
+        <v>0.199214</v>
       </c>
       <c r="AK62">
-        <v>0.199214</v>
-      </c>
-      <c r="AL62">
         <v>-6.822478103704036</v>
+      </c>
+      <c r="AL62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -7151,22 +7286,22 @@
         <v>26.9365134620331</v>
       </c>
       <c r="AG63">
-        <v>296.7</v>
+        <v>0.3182467318351081</v>
       </c>
       <c r="AH63">
-        <v>0.3182467318351081</v>
+        <v>0.01008835583474965</v>
       </c>
       <c r="AI63">
-        <v>0.01008835583474965</v>
+        <v>0.150479</v>
       </c>
       <c r="AJ63">
-        <v>0.150479</v>
+        <v>0.258179</v>
       </c>
       <c r="AK63">
-        <v>0.258179</v>
-      </c>
-      <c r="AL63">
         <v>-8.429119209515335</v>
+      </c>
+      <c r="AL63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -7267,22 +7402,22 @@
         <v>25.3707484836752</v>
       </c>
       <c r="AG64">
-        <v>229.4</v>
+        <v>0.2723665450514142</v>
       </c>
       <c r="AH64">
-        <v>0.2723665450514142</v>
+        <v>0.01313174937046982</v>
       </c>
       <c r="AI64">
-        <v>0.01313174937046982</v>
+        <v>0.1834629999999999</v>
       </c>
       <c r="AJ64">
-        <v>0.1834629999999999</v>
+        <v>0.4244510000000001</v>
       </c>
       <c r="AK64">
-        <v>0.4244510000000001</v>
-      </c>
-      <c r="AL64">
         <v>-8.787885464972419</v>
+      </c>
+      <c r="AL64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -7382,20 +7517,23 @@
       <c r="AF65">
         <v>22.10491944754</v>
       </c>
+      <c r="AG65">
+        <v>0.07019294620254873</v>
+      </c>
       <c r="AH65">
-        <v>0.07019294620254873</v>
+        <v>0.9986721560276816</v>
       </c>
       <c r="AI65">
-        <v>0.9986721560276816</v>
+        <v>1.077307</v>
       </c>
       <c r="AJ65">
-        <v>1.077307</v>
+        <v>0.754041</v>
       </c>
       <c r="AK65">
-        <v>0.754041</v>
-      </c>
-      <c r="AL65">
         <v>7.200336</v>
+      </c>
+      <c r="AL65" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:38">
@@ -7495,20 +7633,23 @@
       <c r="AF66">
         <v>25.2273067617101</v>
       </c>
+      <c r="AG66">
+        <v>0.07174090622302046</v>
+      </c>
       <c r="AH66">
-        <v>0.07174090622302046</v>
+        <v>0.9970736948003567</v>
       </c>
       <c r="AI66">
-        <v>0.9970736948003567</v>
+        <v>1.060754</v>
       </c>
       <c r="AJ66">
-        <v>1.060754</v>
+        <v>0.5727719999999999</v>
       </c>
       <c r="AK66">
-        <v>0.5727719999999999</v>
-      </c>
-      <c r="AL66">
         <v>7.974453</v>
+      </c>
+      <c r="AL66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -7599,20 +7740,23 @@
       <c r="AC67">
         <v>54.13</v>
       </c>
+      <c r="AG67">
+        <v>0.07904909281277159</v>
+      </c>
       <c r="AH67">
-        <v>0.07904909281277159</v>
+        <v>0.9981623694490049</v>
       </c>
       <c r="AI67">
-        <v>0.9981623694490049</v>
+        <v>1.122788</v>
       </c>
       <c r="AJ67">
-        <v>1.122788</v>
+        <v>0.6676409999999999</v>
       </c>
       <c r="AK67">
-        <v>0.6676409999999999</v>
-      </c>
-      <c r="AL67">
         <v>6.855086</v>
+      </c>
+      <c r="AL67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:38">
@@ -7703,20 +7847,23 @@
       <c r="AC68">
         <v>71.34</v>
       </c>
+      <c r="AG68">
+        <v>0.09899000424423764</v>
+      </c>
       <c r="AH68">
-        <v>0.09899000424423764</v>
+        <v>0.8815412195842189</v>
       </c>
       <c r="AI68">
-        <v>0.8815412195842189</v>
+        <v>1.326418</v>
       </c>
       <c r="AJ68">
-        <v>1.326418</v>
+        <v>0.819896</v>
       </c>
       <c r="AK68">
-        <v>0.819896</v>
-      </c>
-      <c r="AL68">
         <v>8.319675</v>
+      </c>
+      <c r="AL68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:38">
@@ -7807,20 +7954,23 @@
       <c r="AC69">
         <v>64.3</v>
       </c>
+      <c r="AG69">
+        <v>0.1018087698090169</v>
+      </c>
       <c r="AH69">
-        <v>0.1018087698090169</v>
+        <v>0.8418690036119334</v>
       </c>
       <c r="AI69">
-        <v>0.8418690036119334</v>
+        <v>1.407998</v>
       </c>
       <c r="AJ69">
-        <v>1.407998</v>
+        <v>0.9153969999999999</v>
       </c>
       <c r="AK69">
-        <v>0.9153969999999999</v>
-      </c>
-      <c r="AL69">
         <v>10.534123</v>
+      </c>
+      <c r="AL69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:38">
@@ -7911,20 +8061,23 @@
       <c r="AC70">
         <v>41.96</v>
       </c>
+      <c r="AG70">
+        <v>0.06519171996221718</v>
+      </c>
       <c r="AH70">
-        <v>0.06519171996221718</v>
+        <v>0.9947797399523766</v>
       </c>
       <c r="AI70">
-        <v>0.9947797399523766</v>
+        <v>1.377816</v>
       </c>
       <c r="AJ70">
-        <v>1.377816</v>
+        <v>0.9243349999999999</v>
       </c>
       <c r="AK70">
-        <v>0.9243349999999999</v>
-      </c>
-      <c r="AL70">
         <v>11.614015</v>
+      </c>
+      <c r="AL70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:38">
@@ -8015,20 +8168,23 @@
       <c r="AC71">
         <v>70.86</v>
       </c>
+      <c r="AG71">
+        <v>0.09303799200012243</v>
+      </c>
       <c r="AH71">
-        <v>0.09303799200012243</v>
+        <v>0.8061949943107525</v>
       </c>
       <c r="AI71">
-        <v>0.8061949943107525</v>
+        <v>1.27268</v>
       </c>
       <c r="AJ71">
-        <v>1.27268</v>
+        <v>0.8346750000000001</v>
       </c>
       <c r="AK71">
-        <v>0.8346750000000001</v>
-      </c>
-      <c r="AL71">
         <v>4.847939</v>
+      </c>
+      <c r="AL71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:38">
@@ -8119,20 +8275,23 @@
       <c r="AC72">
         <v>100.93</v>
       </c>
+      <c r="AG72">
+        <v>0.1062319080492729</v>
+      </c>
       <c r="AH72">
-        <v>0.1062319080492729</v>
+        <v>0.7391303674075436</v>
       </c>
       <c r="AI72">
-        <v>0.7391303674075436</v>
+        <v>1.131912</v>
       </c>
       <c r="AJ72">
-        <v>1.131912</v>
+        <v>0.7863289999999999</v>
       </c>
       <c r="AK72">
-        <v>0.7863289999999999</v>
-      </c>
-      <c r="AL72">
         <v>-1.674976000000001</v>
+      </c>
+      <c r="AL72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:38">
@@ -8223,20 +8382,23 @@
       <c r="AC73">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG73">
+        <v>0.08077982507837604</v>
+      </c>
       <c r="AH73">
-        <v>0.08077982507837604</v>
+        <v>0.8516786008673098</v>
       </c>
       <c r="AI73">
-        <v>0.8516786008673098</v>
+        <v>1.130566</v>
       </c>
       <c r="AJ73">
-        <v>1.130566</v>
+        <v>0.920579</v>
       </c>
       <c r="AK73">
-        <v>0.920579</v>
-      </c>
-      <c r="AL73">
         <v>5.174824000000001</v>
+      </c>
+      <c r="AL73" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:38">
@@ -8333,20 +8495,23 @@
       <c r="AF74">
         <v>21.1423576597254</v>
       </c>
+      <c r="AG74">
+        <v>0.7646415168135781</v>
+      </c>
       <c r="AH74">
-        <v>0.7646415168135781</v>
+        <v>0.04814538003978179</v>
       </c>
       <c r="AI74">
-        <v>0.04814538003978179</v>
+        <v>0.517966</v>
       </c>
       <c r="AJ74">
-        <v>0.517966</v>
+        <v>0.232962</v>
       </c>
       <c r="AK74">
-        <v>0.232962</v>
-      </c>
-      <c r="AL74">
         <v>-3.750222634326807</v>
+      </c>
+      <c r="AL74" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:38">
@@ -8443,20 +8608,23 @@
       <c r="AF75">
         <v>20.8570992758656</v>
       </c>
+      <c r="AG75">
+        <v>0.8120319790686434</v>
+      </c>
       <c r="AH75">
-        <v>0.8120319790686434</v>
+        <v>0.02241041784900684</v>
       </c>
       <c r="AI75">
-        <v>0.02241041784900684</v>
+        <v>0.5379130000000001</v>
       </c>
       <c r="AJ75">
-        <v>0.5379130000000001</v>
+        <v>0.1647069999999999</v>
       </c>
       <c r="AK75">
-        <v>0.1647069999999999</v>
-      </c>
-      <c r="AL75">
         <v>-3.798398999999996</v>
+      </c>
+      <c r="AL75" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:38">
@@ -8554,22 +8722,22 @@
         <v>21.1680432165628</v>
       </c>
       <c r="AG76">
-        <v>130.2</v>
+        <v>0.7897740017971175</v>
       </c>
       <c r="AH76">
-        <v>0.7897740017971175</v>
+        <v>0.02921228234689353</v>
       </c>
       <c r="AI76">
-        <v>0.02921228234689353</v>
+        <v>0.5342979999999999</v>
       </c>
       <c r="AJ76">
-        <v>0.5342979999999999</v>
+        <v>0.182595</v>
       </c>
       <c r="AK76">
-        <v>0.182595</v>
-      </c>
-      <c r="AL76">
         <v>-3.631309999999999</v>
+      </c>
+      <c r="AL76" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:38">
@@ -8667,22 +8835,22 @@
         <v>22.1740306166793</v>
       </c>
       <c r="AG77">
-        <v>132.8</v>
+        <v>0.7880594644948724</v>
       </c>
       <c r="AH77">
-        <v>0.7880594644948724</v>
+        <v>0.03068853608458817</v>
       </c>
       <c r="AI77">
-        <v>0.03068853608458817</v>
+        <v>0.5557540000000001</v>
       </c>
       <c r="AJ77">
-        <v>0.5557540000000001</v>
+        <v>0.1873549999999999</v>
       </c>
       <c r="AK77">
-        <v>0.1873549999999999</v>
-      </c>
-      <c r="AL77">
         <v>-4.246721999999998</v>
+      </c>
+      <c r="AL77" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:38">
@@ -8780,22 +8948,22 @@
         <v>21.739927149931</v>
       </c>
       <c r="AG78">
-        <v>136.3</v>
+        <v>0.8162852585746241</v>
       </c>
       <c r="AH78">
-        <v>0.8162852585746241</v>
+        <v>0.0312708845558245</v>
       </c>
       <c r="AI78">
-        <v>0.0312708845558245</v>
+        <v>0.4758000000000001</v>
       </c>
       <c r="AJ78">
-        <v>0.4758000000000001</v>
+        <v>0.176351</v>
       </c>
       <c r="AK78">
-        <v>0.176351</v>
-      </c>
-      <c r="AL78">
         <v>-4.105066999999998</v>
+      </c>
+      <c r="AL78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:38">
@@ -8893,22 +9061,22 @@
         <v>19.9382667510933</v>
       </c>
       <c r="AG79">
-        <v>197</v>
+        <v>0.6512278306965467</v>
       </c>
       <c r="AH79">
-        <v>0.6512278306965467</v>
+        <v>0.03701123190169985</v>
       </c>
       <c r="AI79">
-        <v>0.03701123190169985</v>
+        <v>0.540563</v>
       </c>
       <c r="AJ79">
-        <v>0.540563</v>
+        <v>0.23602</v>
       </c>
       <c r="AK79">
-        <v>0.23602</v>
-      </c>
-      <c r="AL79">
         <v>-3.77825</v>
+      </c>
+      <c r="AL79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:38">
@@ -9006,22 +9174,22 @@
         <v>24.1674095479002</v>
       </c>
       <c r="AG80">
-        <v>140.8</v>
+        <v>0.8021127799348304</v>
       </c>
       <c r="AH80">
-        <v>0.8021127799348304</v>
+        <v>0.03352059342279543</v>
       </c>
       <c r="AI80">
-        <v>0.03352059342279543</v>
+        <v>0.4172399999999999</v>
       </c>
       <c r="AJ80">
-        <v>0.4172399999999999</v>
+        <v>0.1519170000000001</v>
       </c>
       <c r="AK80">
-        <v>0.1519170000000001</v>
-      </c>
-      <c r="AL80">
         <v>-2.433712999999997</v>
+      </c>
+      <c r="AL80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:38">
@@ -9119,22 +9287,22 @@
         <v>26.0812426572599</v>
       </c>
       <c r="AG81">
-        <v>177.8</v>
+        <v>0.9157179348253978</v>
       </c>
       <c r="AH81">
-        <v>0.9157179348253978</v>
+        <v>0.01366023086604998</v>
       </c>
       <c r="AI81">
-        <v>0.01366023086604998</v>
+        <v>0.243549</v>
       </c>
       <c r="AJ81">
-        <v>0.243549</v>
+        <v>-0.004466000000000081</v>
       </c>
       <c r="AK81">
-        <v>-0.004466000000000081</v>
-      </c>
-      <c r="AL81">
         <v>-1.163345999999997</v>
+      </c>
+      <c r="AL81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:38">
@@ -9232,22 +9400,22 @@
         <v>22.9465317535315</v>
       </c>
       <c r="AG82">
-        <v>140.1</v>
+        <v>0.5884371595505187</v>
       </c>
       <c r="AH82">
-        <v>0.5884371595505187</v>
+        <v>0.02445868467671351</v>
       </c>
       <c r="AI82">
-        <v>0.02445868467671351</v>
+        <v>0.547383</v>
       </c>
       <c r="AJ82">
-        <v>0.547383</v>
+        <v>0.4546119999999999</v>
       </c>
       <c r="AK82">
-        <v>0.4546119999999999</v>
-      </c>
-      <c r="AL82">
         <v>-2.0625</v>
+      </c>
+      <c r="AL82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:38">
@@ -9348,22 +9516,22 @@
         <v>24.1024162766989</v>
       </c>
       <c r="AG83">
-        <v>249.5</v>
+        <v>0.3256033943633691</v>
       </c>
       <c r="AH83">
-        <v>0.3256033943633691</v>
+        <v>0.03860649649821091</v>
       </c>
       <c r="AI83">
-        <v>0.03860649649821091</v>
+        <v>0.1240609999999999</v>
       </c>
       <c r="AJ83">
-        <v>0.1240609999999999</v>
+        <v>0.229513</v>
       </c>
       <c r="AK83">
-        <v>0.229513</v>
-      </c>
-      <c r="AL83">
         <v>-5.265325000000001</v>
+      </c>
+      <c r="AL83" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:38">
@@ -9464,22 +9632,22 @@
         <v>24.2234212780588</v>
       </c>
       <c r="AG84">
-        <v>279.6</v>
+        <v>0.3625566077717619</v>
       </c>
       <c r="AH84">
-        <v>0.3625566077717619</v>
+        <v>0.026903653984797</v>
       </c>
       <c r="AI84">
-        <v>0.026903653984797</v>
+        <v>0.116458</v>
       </c>
       <c r="AJ84">
-        <v>0.116458</v>
+        <v>0.1773130000000001</v>
       </c>
       <c r="AK84">
-        <v>0.1773130000000001</v>
-      </c>
-      <c r="AL84">
         <v>-1.529195000000001</v>
+      </c>
+      <c r="AL84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:38">
@@ -9580,22 +9748,22 @@
         <v>22.5842861999584</v>
       </c>
       <c r="AG85">
-        <v>193.9</v>
+        <v>0.3630110123661155</v>
       </c>
       <c r="AH85">
-        <v>0.3630110123661155</v>
+        <v>0.02076159117672383</v>
       </c>
       <c r="AI85">
-        <v>0.02076159117672383</v>
+        <v>0.11542</v>
       </c>
       <c r="AJ85">
-        <v>0.11542</v>
+        <v>0.1323359999999999</v>
       </c>
       <c r="AK85">
-        <v>0.1323359999999999</v>
-      </c>
-      <c r="AL85">
         <v>-1.463829999999998</v>
+      </c>
+      <c r="AL85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:38">
@@ -9696,22 +9864,22 @@
         <v>23.4751871722398</v>
       </c>
       <c r="AG86">
-        <v>183.4</v>
+        <v>0.3916222384329775</v>
       </c>
       <c r="AH86">
-        <v>0.3916222384329775</v>
+        <v>0.02793534784806655</v>
       </c>
       <c r="AI86">
-        <v>0.02793534784806655</v>
+        <v>0.07560900000000004</v>
       </c>
       <c r="AJ86">
-        <v>0.07560900000000004</v>
+        <v>0.02941899999999997</v>
       </c>
       <c r="AK86">
-        <v>0.02941899999999997</v>
-      </c>
-      <c r="AL86">
         <v>-4.768172878251871</v>
+      </c>
+      <c r="AL86" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:38">
@@ -9812,22 +9980,22 @@
         <v>25.575368512731</v>
       </c>
       <c r="AG87">
-        <v>183.7</v>
+        <v>0.4291959769269287</v>
       </c>
       <c r="AH87">
-        <v>0.4291959769269287</v>
+        <v>0.03693460811831228</v>
       </c>
       <c r="AI87">
-        <v>0.03693460811831228</v>
+        <v>0.04222800000000004</v>
       </c>
       <c r="AJ87">
-        <v>0.04222800000000004</v>
+        <v>0.04271400000000003</v>
       </c>
       <c r="AK87">
-        <v>0.04271400000000003</v>
-      </c>
-      <c r="AL87">
         <v>-4.568232000000002</v>
+      </c>
+      <c r="AL87" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:38">
@@ -9928,22 +10096,22 @@
         <v>23.6871303712315</v>
       </c>
       <c r="AG88">
-        <v>261.4</v>
+        <v>0.3378370706526375</v>
       </c>
       <c r="AH88">
-        <v>0.3378370706526375</v>
+        <v>0.03604946859279811</v>
       </c>
       <c r="AI88">
-        <v>0.03604946859279811</v>
+        <v>0.126559</v>
       </c>
       <c r="AJ88">
-        <v>0.126559</v>
+        <v>0.161302</v>
       </c>
       <c r="AK88">
-        <v>0.161302</v>
-      </c>
-      <c r="AL88">
         <v>-4.391302</v>
+      </c>
+      <c r="AL88" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:38">
@@ -10044,22 +10212,22 @@
         <v>24.1312117221098</v>
       </c>
       <c r="AG89">
-        <v>261.3</v>
+        <v>0.5242926420230365</v>
       </c>
       <c r="AH89">
-        <v>0.5242926420230365</v>
+        <v>0.1076122602683817</v>
       </c>
       <c r="AI89">
-        <v>0.1076122602683817</v>
+        <v>-0.1799729999999999</v>
       </c>
       <c r="AJ89">
-        <v>-0.1799729999999999</v>
+        <v>-0.07467299999999999</v>
       </c>
       <c r="AK89">
-        <v>-0.07467299999999999</v>
-      </c>
-      <c r="AL89">
         <v>-4.080454999999999</v>
+      </c>
+      <c r="AL89" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:38">
@@ -10160,22 +10328,22 @@
         <v>25.4074707206706</v>
       </c>
       <c r="AG90">
-        <v>394.6</v>
+        <v>0.6921359170818548</v>
       </c>
       <c r="AH90">
-        <v>0.6921359170818548</v>
+        <v>0.2327777723093422</v>
       </c>
       <c r="AI90">
-        <v>0.2327777723093422</v>
+        <v>-0.484696</v>
       </c>
       <c r="AJ90">
-        <v>-0.484696</v>
+        <v>-0.42037</v>
       </c>
       <c r="AK90">
-        <v>-0.42037</v>
-      </c>
-      <c r="AL90">
         <v>-4.323236999999999</v>
+      </c>
+      <c r="AL90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:38">
@@ -10276,22 +10444,22 @@
         <v>28.4136914959886</v>
       </c>
       <c r="AG91">
-        <v>357.6</v>
+        <v>0.5357007914156112</v>
       </c>
       <c r="AH91">
-        <v>0.5357007914156112</v>
+        <v>0.07081031425184185</v>
       </c>
       <c r="AI91">
-        <v>0.07081031425184185</v>
+        <v>-0.02932099999999993</v>
       </c>
       <c r="AJ91">
-        <v>-0.02932099999999993</v>
+        <v>-0.138081</v>
       </c>
       <c r="AK91">
-        <v>-0.138081</v>
-      </c>
-      <c r="AL91">
         <v>-4.536567</v>
+      </c>
+      <c r="AL91" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:38">
@@ -10385,20 +10553,23 @@
       <c r="AF92">
         <v>23.4572080583441</v>
       </c>
+      <c r="AG92">
+        <v>0.2003440111794715</v>
+      </c>
       <c r="AH92">
-        <v>0.2003440111794715</v>
+        <v>0.05097565204070389</v>
       </c>
       <c r="AI92">
-        <v>0.05097565204070389</v>
+        <v>0.5257869999999999</v>
       </c>
       <c r="AJ92">
-        <v>0.5257869999999999</v>
+        <v>0.4270099999999999</v>
       </c>
       <c r="AK92">
-        <v>0.4270099999999999</v>
-      </c>
-      <c r="AL92">
         <v>-0.0004759999999990328</v>
+      </c>
+      <c r="AL92" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:38">
@@ -10492,20 +10663,23 @@
       <c r="AF93">
         <v>24.0079934600948</v>
       </c>
+      <c r="AG93">
+        <v>0.2541735171297335</v>
+      </c>
       <c r="AH93">
-        <v>0.2541735171297335</v>
+        <v>0.04152400111110519</v>
       </c>
       <c r="AI93">
-        <v>0.04152400111110519</v>
+        <v>0.4852820000000001</v>
       </c>
       <c r="AJ93">
-        <v>0.4852820000000001</v>
+        <v>0.342261</v>
       </c>
       <c r="AK93">
-        <v>0.342261</v>
-      </c>
-      <c r="AL93">
         <v>0.0001560000000004891</v>
+      </c>
+      <c r="AL93" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:38">
@@ -10599,20 +10773,23 @@
       <c r="AF94">
         <v>23.3185966619773</v>
       </c>
+      <c r="AG94">
+        <v>0.2954108554916408</v>
+      </c>
       <c r="AH94">
-        <v>0.2954108554916408</v>
+        <v>0.03879851344896825</v>
       </c>
       <c r="AI94">
-        <v>0.03879851344896825</v>
+        <v>0.4693769999999999</v>
       </c>
       <c r="AJ94">
-        <v>0.4693769999999999</v>
+        <v>0.3364590000000001</v>
       </c>
       <c r="AK94">
-        <v>0.3364590000000001</v>
-      </c>
-      <c r="AL94">
         <v>-6.399999999828765E-05</v>
+      </c>
+      <c r="AL94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:38">
@@ -10706,20 +10883,23 @@
       <c r="AF95">
         <v>24.3167782701782</v>
       </c>
+      <c r="AG95">
+        <v>0.2883821074409657</v>
+      </c>
       <c r="AH95">
-        <v>0.2883821074409657</v>
+        <v>0.04626169685836625</v>
       </c>
       <c r="AI95">
-        <v>0.04626169685836625</v>
+        <v>0.4610209999999999</v>
       </c>
       <c r="AJ95">
-        <v>0.4610209999999999</v>
+        <v>0.3062029999999999</v>
       </c>
       <c r="AK95">
-        <v>0.3062029999999999</v>
-      </c>
-      <c r="AL95">
         <v>-0.0001999999999995339</v>
+      </c>
+      <c r="AL95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:38">
@@ -10816,20 +10996,23 @@
       <c r="AF96">
         <v>27.5354175556737</v>
       </c>
+      <c r="AG96">
+        <v>0.2992418878592031</v>
+      </c>
       <c r="AH96">
-        <v>0.2992418878592031</v>
+        <v>0.0667447624660126</v>
       </c>
       <c r="AI96">
-        <v>0.0667447624660126</v>
+        <v>0.438963</v>
       </c>
       <c r="AJ96">
-        <v>0.438963</v>
+        <v>0.30589</v>
       </c>
       <c r="AK96">
-        <v>0.30589</v>
-      </c>
-      <c r="AL96">
         <v>-8.499999999855845E-05</v>
+      </c>
+      <c r="AL96" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:38">
@@ -10926,20 +11109,23 @@
       <c r="AF97">
         <v>27.1843242899476</v>
       </c>
+      <c r="AG97">
+        <v>0.1654386167841267</v>
+      </c>
       <c r="AH97">
-        <v>0.1654386167841267</v>
+        <v>0.06605059576905259</v>
       </c>
       <c r="AI97">
-        <v>0.06605059576905259</v>
+        <v>0.5826220000000001</v>
       </c>
       <c r="AJ97">
-        <v>0.5826220000000001</v>
+        <v>0.390973</v>
       </c>
       <c r="AK97">
-        <v>0.390973</v>
-      </c>
-      <c r="AL97">
         <v>0.0002539999999999765</v>
+      </c>
+      <c r="AL97" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:38">
@@ -11036,20 +11222,23 @@
       <c r="AF98">
         <v>28.2061355248318</v>
       </c>
+      <c r="AG98">
+        <v>0.3435822906395561</v>
+      </c>
       <c r="AH98">
-        <v>0.3435822906395561</v>
+        <v>0.06336248485876857</v>
       </c>
       <c r="AI98">
-        <v>0.06336248485876857</v>
+        <v>0.4193819999999999</v>
       </c>
       <c r="AJ98">
-        <v>0.4193819999999999</v>
+        <v>0.286178</v>
       </c>
       <c r="AK98">
-        <v>0.286178</v>
-      </c>
-      <c r="AL98">
         <v>-0.0003820000000001045</v>
+      </c>
+      <c r="AL98" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:38">
@@ -11146,20 +11335,23 @@
       <c r="AF99">
         <v>28.8914258324714</v>
       </c>
+      <c r="AG99">
+        <v>0.3725200992630867</v>
+      </c>
       <c r="AH99">
-        <v>0.3725200992630867</v>
+        <v>0.0577819507361867</v>
       </c>
       <c r="AI99">
-        <v>0.0577819507361867</v>
+        <v>0.3556820000000001</v>
       </c>
       <c r="AJ99">
-        <v>0.3556820000000001</v>
+        <v>0.273983</v>
       </c>
       <c r="AK99">
-        <v>0.273983</v>
-      </c>
-      <c r="AL99">
         <v>-0.0002889999999986514</v>
+      </c>
+      <c r="AL99" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:38">
@@ -11256,20 +11448,23 @@
       <c r="AF100">
         <v>29.3390402864479</v>
       </c>
+      <c r="AG100">
+        <v>0.3036371620794919</v>
+      </c>
       <c r="AH100">
-        <v>0.3036371620794919</v>
+        <v>0.05809915123431144</v>
       </c>
       <c r="AI100">
-        <v>0.05809915123431144</v>
+        <v>0.454278</v>
       </c>
       <c r="AJ100">
-        <v>0.454278</v>
+        <v>0.4928119999999999</v>
       </c>
       <c r="AK100">
-        <v>0.4928119999999999</v>
-      </c>
-      <c r="AL100">
         <v>0.0001029999999992981</v>
+      </c>
+      <c r="AL100" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:38">
@@ -11342,14 +11537,17 @@
       <c r="AC101">
         <v>52.32</v>
       </c>
+      <c r="AI101">
+        <v>0.5370819999999999</v>
+      </c>
       <c r="AJ101">
-        <v>0.5370819999999999</v>
+        <v>0.434943</v>
       </c>
       <c r="AK101">
-        <v>0.434943</v>
-      </c>
-      <c r="AL101">
         <v>0.0005960000000015953</v>
+      </c>
+      <c r="AL101" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:38">
@@ -11422,14 +11620,17 @@
       <c r="AC102">
         <v>43.64</v>
       </c>
+      <c r="AI102">
+        <v>0.5228489999999999</v>
+      </c>
       <c r="AJ102">
-        <v>0.5228489999999999</v>
+        <v>0.380753</v>
       </c>
       <c r="AK102">
-        <v>0.380753</v>
-      </c>
-      <c r="AL102">
         <v>0.0004570000000008179</v>
+      </c>
+      <c r="AL102" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:38">
@@ -11502,14 +11703,17 @@
       <c r="AC103">
         <v>54.13</v>
       </c>
+      <c r="AI103">
+        <v>0.520764</v>
+      </c>
       <c r="AJ103">
-        <v>0.520764</v>
+        <v>0.3869969999999999</v>
       </c>
       <c r="AK103">
-        <v>0.3869969999999999</v>
-      </c>
-      <c r="AL103">
         <v>-0.000128000000000128</v>
+      </c>
+      <c r="AL103" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:38">
@@ -11582,14 +11786,17 @@
       <c r="AC104">
         <v>71.34</v>
       </c>
+      <c r="AI104">
+        <v>0.5098010000000001</v>
+      </c>
       <c r="AJ104">
-        <v>0.5098010000000001</v>
+        <v>0.387857</v>
       </c>
       <c r="AK104">
-        <v>0.387857</v>
-      </c>
-      <c r="AL104">
         <v>-0.0003749999999982379</v>
+      </c>
+      <c r="AL104" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:38">
@@ -11662,14 +11869,17 @@
       <c r="AC105">
         <v>64.3</v>
       </c>
+      <c r="AI105">
+        <v>0.4936690000000001</v>
+      </c>
       <c r="AJ105">
-        <v>0.4936690000000001</v>
+        <v>0.3871329999999999</v>
       </c>
       <c r="AK105">
-        <v>0.3871329999999999</v>
-      </c>
-      <c r="AL105">
         <v>0.0009199999999971453</v>
+      </c>
+      <c r="AL105" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:38">
@@ -11742,13 +11952,16 @@
       <c r="AC106">
         <v>41.96</v>
       </c>
+      <c r="AI106">
+        <v>0.5182259999999999</v>
+      </c>
       <c r="AJ106">
-        <v>0.5182259999999999</v>
+        <v>0.397017</v>
       </c>
       <c r="AK106">
-        <v>0.397017</v>
-      </c>
-      <c r="AL106">
+        <v>0</v>
+      </c>
+      <c r="AL106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11840,20 +12053,23 @@
       <c r="AC107">
         <v>70.86</v>
       </c>
+      <c r="AG107">
+        <v>0.2150667197598824</v>
+      </c>
       <c r="AH107">
-        <v>0.2150667197598824</v>
+        <v>0.2023220784348661</v>
       </c>
       <c r="AI107">
-        <v>0.2023220784348661</v>
+        <v>0.455124</v>
       </c>
       <c r="AJ107">
-        <v>0.455124</v>
+        <v>0.311575</v>
       </c>
       <c r="AK107">
-        <v>0.311575</v>
-      </c>
-      <c r="AL107">
         <v>0.0008100000000013097</v>
+      </c>
+      <c r="AL107" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:38">
@@ -11944,20 +12160,23 @@
       <c r="AC108">
         <v>100.93</v>
       </c>
+      <c r="AG108">
+        <v>0.2326171490706407</v>
+      </c>
       <c r="AH108">
-        <v>0.2326171490706407</v>
+        <v>0.1953738102064777</v>
       </c>
       <c r="AI108">
-        <v>0.1953738102064777</v>
+        <v>0.4707340000000002</v>
       </c>
       <c r="AJ108">
-        <v>0.4707340000000002</v>
+        <v>0.3814489999999999</v>
       </c>
       <c r="AK108">
-        <v>0.3814489999999999</v>
-      </c>
-      <c r="AL108">
         <v>-0.0002679999999983806</v>
+      </c>
+      <c r="AL108" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:38">
@@ -12048,20 +12267,23 @@
       <c r="AC109">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG109">
+        <v>0.1926922233347343</v>
+      </c>
       <c r="AH109">
-        <v>0.1926922233347343</v>
+        <v>0.1631895010215924</v>
       </c>
       <c r="AI109">
-        <v>0.1631895010215924</v>
+        <v>0.556214</v>
       </c>
       <c r="AJ109">
-        <v>0.556214</v>
+        <v>0.531328</v>
       </c>
       <c r="AK109">
-        <v>0.531328</v>
-      </c>
-      <c r="AL109">
         <v>-0.0004109999999997171</v>
+      </c>
+      <c r="AL109" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:38">
@@ -12158,20 +12380,23 @@
       <c r="AF110">
         <v>14.5186216543802</v>
       </c>
+      <c r="AG110">
+        <v>0.2369215651027185</v>
+      </c>
       <c r="AH110">
-        <v>0.2369215651027185</v>
+        <v>0.2000368806668209</v>
       </c>
       <c r="AI110">
-        <v>0.2000368806668209</v>
+        <v>0.5224920000000001</v>
       </c>
       <c r="AJ110">
-        <v>0.5224920000000001</v>
+        <v>0.3909200000000002</v>
       </c>
       <c r="AK110">
-        <v>0.3909200000000002</v>
-      </c>
-      <c r="AL110">
         <v>-0.5331262612976495</v>
+      </c>
+      <c r="AL110" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:38">
@@ -12268,20 +12493,23 @@
       <c r="AF111">
         <v>14.827297566694</v>
       </c>
+      <c r="AG111">
+        <v>0.2556994874684549</v>
+      </c>
       <c r="AH111">
-        <v>0.2556994874684549</v>
+        <v>0.1924626934700369</v>
       </c>
       <c r="AI111">
-        <v>0.1924626934700369</v>
+        <v>0.549878</v>
       </c>
       <c r="AJ111">
-        <v>0.549878</v>
+        <v>0.34128</v>
       </c>
       <c r="AK111">
-        <v>0.34128</v>
-      </c>
-      <c r="AL111">
         <v>-0.1264140000000005</v>
+      </c>
+      <c r="AL111" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:38">
@@ -12378,20 +12606,23 @@
       <c r="AF112">
         <v>14.9920997503639</v>
       </c>
+      <c r="AG112">
+        <v>0.2180222631220768</v>
+      </c>
       <c r="AH112">
-        <v>0.2180222631220768</v>
+        <v>0.1477499484716935</v>
       </c>
       <c r="AI112">
-        <v>0.1477499484716935</v>
+        <v>0.557296</v>
       </c>
       <c r="AJ112">
-        <v>0.557296</v>
+        <v>0.316043</v>
       </c>
       <c r="AK112">
-        <v>0.316043</v>
-      </c>
-      <c r="AL112">
         <v>-0.4162529999999975</v>
+      </c>
+      <c r="AL112" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:38">
@@ -12488,20 +12719,23 @@
       <c r="AF113">
         <v>15.269462908084</v>
       </c>
+      <c r="AG113">
+        <v>0.2725469395050613</v>
+      </c>
       <c r="AH113">
-        <v>0.2725469395050613</v>
+        <v>0.2440233201758201</v>
       </c>
       <c r="AI113">
-        <v>0.2440233201758201</v>
+        <v>0.5205599999999999</v>
       </c>
       <c r="AJ113">
-        <v>0.5205599999999999</v>
+        <v>0.2957179999999999</v>
       </c>
       <c r="AK113">
-        <v>0.2957179999999999</v>
-      </c>
-      <c r="AL113">
         <v>-0.7851609999999987</v>
+      </c>
+      <c r="AL113" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:38">
@@ -12598,20 +12832,23 @@
       <c r="AF114">
         <v>15.5470600045533</v>
       </c>
+      <c r="AG114">
+        <v>0.3979691196730002</v>
+      </c>
       <c r="AH114">
-        <v>0.3979691196730002</v>
+        <v>0.1959821491297361</v>
       </c>
       <c r="AI114">
-        <v>0.1959821491297361</v>
+        <v>0.4626730000000001</v>
       </c>
       <c r="AJ114">
-        <v>0.4626730000000001</v>
+        <v>0.2714249999999999</v>
       </c>
       <c r="AK114">
-        <v>0.2714249999999999</v>
-      </c>
-      <c r="AL114">
         <v>0.07633799999999979</v>
+      </c>
+      <c r="AL114" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:38">
@@ -12708,20 +12945,23 @@
       <c r="AF115">
         <v>14.8813590480588</v>
       </c>
+      <c r="AG115">
+        <v>0.3934607016032607</v>
+      </c>
       <c r="AH115">
-        <v>0.3934607016032607</v>
+        <v>0.1763323970967435</v>
       </c>
       <c r="AI115">
-        <v>0.1763323970967435</v>
+        <v>0.4667060000000001</v>
       </c>
       <c r="AJ115">
-        <v>0.4667060000000001</v>
+        <v>0.263153</v>
       </c>
       <c r="AK115">
-        <v>0.263153</v>
-      </c>
-      <c r="AL115">
         <v>0.3227099999999972</v>
+      </c>
+      <c r="AL115" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:38">
@@ -12818,20 +13058,23 @@
       <c r="AF116">
         <v>16.4297863174204</v>
       </c>
+      <c r="AG116">
+        <v>0.6242257713279917</v>
+      </c>
       <c r="AH116">
-        <v>0.6242257713279917</v>
+        <v>0.3067879423056801</v>
       </c>
       <c r="AI116">
-        <v>0.3067879423056801</v>
+        <v>0.3808159999999999</v>
       </c>
       <c r="AJ116">
-        <v>0.3808159999999999</v>
+        <v>0.282828</v>
       </c>
       <c r="AK116">
-        <v>0.282828</v>
-      </c>
-      <c r="AL116">
         <v>-2.225742000000004</v>
+      </c>
+      <c r="AL116" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:38">
@@ -12928,20 +13171,23 @@
       <c r="AF117">
         <v>16.3623217477379</v>
       </c>
+      <c r="AG117">
+        <v>0.787853165816615</v>
+      </c>
       <c r="AH117">
-        <v>0.787853165816615</v>
+        <v>0.2585107468155523</v>
       </c>
       <c r="AI117">
-        <v>0.2585107468155523</v>
+        <v>0.2696369999999999</v>
       </c>
       <c r="AJ117">
-        <v>0.2696369999999999</v>
+        <v>0.1065370000000001</v>
       </c>
       <c r="AK117">
-        <v>0.1065370000000001</v>
-      </c>
-      <c r="AL117">
         <v>-4.583881999999996</v>
+      </c>
+      <c r="AL117" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:38">
@@ -13038,20 +13284,23 @@
       <c r="AF118">
         <v>17.015284341071</v>
       </c>
+      <c r="AG118">
+        <v>0.6711089089001835</v>
+      </c>
       <c r="AH118">
-        <v>0.6711089089001835</v>
+        <v>0.2235511547558562</v>
       </c>
       <c r="AI118">
-        <v>0.2235511547558562</v>
+        <v>0.3679060000000001</v>
       </c>
       <c r="AJ118">
-        <v>0.3679060000000001</v>
+        <v>0.322648</v>
       </c>
       <c r="AK118">
-        <v>0.322648</v>
-      </c>
-      <c r="AL118">
         <v>-0.9682139999999997</v>
+      </c>
+      <c r="AL118" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:38">
@@ -13149,22 +13398,22 @@
         <v>30.8458833789351</v>
       </c>
       <c r="AG119">
-        <v>995.2</v>
+        <v>0.7198231545371626</v>
       </c>
       <c r="AH119">
-        <v>0.7198231545371626</v>
+        <v>0.4363266416704328</v>
       </c>
       <c r="AI119">
-        <v>0.4363266416704328</v>
+        <v>-0.1641730000000001</v>
       </c>
       <c r="AJ119">
-        <v>-0.1641730000000001</v>
+        <v>-0.453379</v>
       </c>
       <c r="AK119">
-        <v>-0.453379</v>
-      </c>
-      <c r="AL119">
         <v>1.369807999999999</v>
+      </c>
+      <c r="AL119" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:38">
@@ -13262,22 +13511,22 @@
         <v>28.6412079584013</v>
       </c>
       <c r="AG120">
-        <v>998.3</v>
+        <v>0.6968334263134307</v>
       </c>
       <c r="AH120">
-        <v>0.6968334263134307</v>
+        <v>0.4419762616779271</v>
       </c>
       <c r="AI120">
-        <v>0.4419762616779271</v>
+        <v>-0.158373</v>
       </c>
       <c r="AJ120">
-        <v>-0.158373</v>
+        <v>-0.4483719999999999</v>
       </c>
       <c r="AK120">
-        <v>-0.4483719999999999</v>
-      </c>
-      <c r="AL120">
         <v>2.589419999999999</v>
+      </c>
+      <c r="AL120" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:38">
@@ -13375,22 +13624,22 @@
         <v>27.9863154861129</v>
       </c>
       <c r="AG121">
-        <v>621.4</v>
+        <v>0.744794356753479</v>
       </c>
       <c r="AH121">
-        <v>0.744794356753479</v>
+        <v>0.435630718480602</v>
       </c>
       <c r="AI121">
-        <v>0.435630718480602</v>
+        <v>-0.153663</v>
       </c>
       <c r="AJ121">
-        <v>-0.153663</v>
+        <v>-0.438735</v>
       </c>
       <c r="AK121">
-        <v>-0.438735</v>
-      </c>
-      <c r="AL121">
         <v>-0.5413069999999998</v>
+      </c>
+      <c r="AL121" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -13488,22 +13737,22 @@
         <v>31.2062328120813</v>
       </c>
       <c r="AG122">
-        <v>639.8</v>
+        <v>0.7969343365391971</v>
       </c>
       <c r="AH122">
-        <v>0.7969343365391971</v>
+        <v>0.4605953287247337</v>
       </c>
       <c r="AI122">
-        <v>0.4605953287247337</v>
+        <v>-0.271239</v>
       </c>
       <c r="AJ122">
-        <v>-0.271239</v>
+        <v>-0.495824</v>
       </c>
       <c r="AK122">
-        <v>-0.495824</v>
-      </c>
-      <c r="AL122">
         <v>-3.121864000000002</v>
+      </c>
+      <c r="AL122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:38">
@@ -13601,22 +13850,22 @@
         <v>29.6599984642663</v>
       </c>
       <c r="AG123">
-        <v>693.9</v>
+        <v>0.7440816858162707</v>
       </c>
       <c r="AH123">
-        <v>0.7440816858162707</v>
+        <v>0.4201496541424785</v>
       </c>
       <c r="AI123">
-        <v>0.4201496541424785</v>
+        <v>-0.2145899999999999</v>
       </c>
       <c r="AJ123">
-        <v>-0.2145899999999999</v>
+        <v>-0.4449050000000001</v>
       </c>
       <c r="AK123">
-        <v>-0.4449050000000001</v>
-      </c>
-      <c r="AL123">
         <v>-2.870073000000001</v>
+      </c>
+      <c r="AL123" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:38">
@@ -13714,22 +13963,22 @@
         <v>27.1210867326524</v>
       </c>
       <c r="AG124">
-        <v>2371.9</v>
+        <v>0.5785009824709282</v>
       </c>
       <c r="AH124">
-        <v>0.5785009824709282</v>
+        <v>0.4284006890940036</v>
       </c>
       <c r="AI124">
-        <v>0.4284006890940036</v>
+        <v>-0.151977</v>
       </c>
       <c r="AJ124">
-        <v>-0.151977</v>
+        <v>-0.398379</v>
       </c>
       <c r="AK124">
-        <v>-0.398379</v>
-      </c>
-      <c r="AL124">
         <v>-2.640940000000001</v>
+      </c>
+      <c r="AL124" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:38">
@@ -13827,22 +14076,22 @@
         <v>29.6714820409688</v>
       </c>
       <c r="AG125">
-        <v>913</v>
+        <v>0.6665449801859565</v>
       </c>
       <c r="AH125">
-        <v>0.6665449801859565</v>
+        <v>0.3137602511729643</v>
       </c>
       <c r="AI125">
-        <v>0.3137602511729643</v>
+        <v>-0.07646300000000006</v>
       </c>
       <c r="AJ125">
-        <v>-0.07646300000000006</v>
+        <v>-0.1959900000000001</v>
       </c>
       <c r="AK125">
-        <v>-0.1959900000000001</v>
-      </c>
-      <c r="AL125">
         <v>-2.337202999999999</v>
+      </c>
+      <c r="AL125" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:38">
@@ -13940,22 +14189,22 @@
         <v>30.9625405355437</v>
       </c>
       <c r="AG126">
-        <v>1137.8</v>
+        <v>0.8710155833891512</v>
       </c>
       <c r="AH126">
-        <v>0.8710155833891512</v>
+        <v>0.4313030277804585</v>
       </c>
       <c r="AI126">
-        <v>0.4313030277804585</v>
+        <v>-0.2619549999999999</v>
       </c>
       <c r="AJ126">
-        <v>-0.2619549999999999</v>
+        <v>-0.484917</v>
       </c>
       <c r="AK126">
-        <v>-0.484917</v>
-      </c>
-      <c r="AL126">
         <v>-1.975007000000002</v>
+      </c>
+      <c r="AL126" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:38">
@@ -14047,22 +14296,22 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AG127">
-        <v>1774.7</v>
+        <v>0.8354810251881977</v>
       </c>
       <c r="AH127">
-        <v>0.8354810251881977</v>
+        <v>0.4064439867725593</v>
       </c>
       <c r="AI127">
-        <v>0.4064439867725593</v>
+        <v>-0.127688</v>
       </c>
       <c r="AJ127">
-        <v>-0.127688</v>
+        <v>-0.691114</v>
       </c>
       <c r="AK127">
-        <v>-0.691114</v>
-      </c>
-      <c r="AL127">
         <v>-1.714066000000001</v>
+      </c>
+      <c r="AL127" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:38">
@@ -14153,20 +14402,23 @@
       <c r="AC128">
         <v>52.32</v>
       </c>
+      <c r="AG128">
+        <v>0.3566457645811721</v>
+      </c>
       <c r="AH128">
-        <v>0.3566457645811721</v>
+        <v>0.4071669921962648</v>
       </c>
       <c r="AI128">
-        <v>0.4071669921962648</v>
+        <v>-0.3338650000000001</v>
       </c>
       <c r="AJ128">
-        <v>-0.3338650000000001</v>
+        <v>0.03968399999999983</v>
       </c>
       <c r="AK128">
-        <v>0.03968399999999983</v>
-      </c>
-      <c r="AL128">
         <v>-0.001059000000001475</v>
+      </c>
+      <c r="AL128" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:38">
@@ -14257,20 +14509,23 @@
       <c r="AC129">
         <v>43.64</v>
       </c>
+      <c r="AG129">
+        <v>0.3663741745635178</v>
+      </c>
       <c r="AH129">
-        <v>0.3663741745635178</v>
+        <v>0.3723589739930198</v>
       </c>
       <c r="AI129">
-        <v>0.3723589739930198</v>
+        <v>-0.32433</v>
       </c>
       <c r="AJ129">
-        <v>-0.32433</v>
+        <v>0.02757999999999994</v>
       </c>
       <c r="AK129">
-        <v>0.02757999999999994</v>
-      </c>
-      <c r="AL129">
         <v>-0.0005230000000011614</v>
+      </c>
+      <c r="AL129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:38">
@@ -14361,19 +14616,22 @@
       <c r="AC130">
         <v>54.13</v>
       </c>
+      <c r="AG130">
+        <v>0.381808017980202</v>
+      </c>
       <c r="AH130">
-        <v>0.381808017980202</v>
+        <v>0.3628947883145788</v>
       </c>
       <c r="AI130">
-        <v>0.3628947883145788</v>
+        <v>-0.3501179999999999</v>
       </c>
       <c r="AJ130">
-        <v>-0.3501179999999999</v>
+        <v>0.03689299999999984</v>
       </c>
       <c r="AK130">
-        <v>0.03689299999999984</v>
-      </c>
-      <c r="AL130">
+        <v>0</v>
+      </c>
+      <c r="AL130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14465,20 +14723,23 @@
       <c r="AC131">
         <v>71.34</v>
       </c>
+      <c r="AG131">
+        <v>0.2815052294872931</v>
+      </c>
       <c r="AH131">
-        <v>0.2815052294872931</v>
+        <v>0.1710352899776737</v>
       </c>
       <c r="AI131">
-        <v>0.1710352899776737</v>
+        <v>-0.158091</v>
       </c>
       <c r="AJ131">
-        <v>-0.158091</v>
+        <v>0.06719999999999993</v>
       </c>
       <c r="AK131">
-        <v>0.06719999999999993</v>
-      </c>
-      <c r="AL131">
         <v>0.0008739999999995973</v>
+      </c>
+      <c r="AL131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:38">
@@ -14569,20 +14830,23 @@
       <c r="AC132">
         <v>64.3</v>
       </c>
+      <c r="AG132">
+        <v>0.2843454172039643</v>
+      </c>
       <c r="AH132">
-        <v>0.2843454172039643</v>
+        <v>0.1627037917747354</v>
       </c>
       <c r="AI132">
-        <v>0.1627037917747354</v>
+        <v>-0.163003</v>
       </c>
       <c r="AJ132">
-        <v>-0.163003</v>
+        <v>0.05985499999999999</v>
       </c>
       <c r="AK132">
-        <v>0.05985499999999999</v>
-      </c>
-      <c r="AL132">
         <v>-0.0003680000000017003</v>
+      </c>
+      <c r="AL132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:38">
@@ -14673,19 +14937,22 @@
       <c r="AC133">
         <v>41.96</v>
       </c>
+      <c r="AG133">
+        <v>0.2338433020822233</v>
+      </c>
       <c r="AH133">
-        <v>0.2338433020822233</v>
+        <v>0.1584243984808682</v>
       </c>
       <c r="AI133">
-        <v>0.1584243984808682</v>
+        <v>-0.151724</v>
       </c>
       <c r="AJ133">
-        <v>-0.151724</v>
+        <v>0.03295099999999995</v>
       </c>
       <c r="AK133">
-        <v>0.03295099999999995</v>
-      </c>
-      <c r="AL133">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14777,20 +15044,23 @@
       <c r="AC134">
         <v>70.86</v>
       </c>
+      <c r="AG134">
+        <v>0.2532526778058514</v>
+      </c>
       <c r="AH134">
-        <v>0.2532526778058514</v>
+        <v>0.1460475604657164</v>
       </c>
       <c r="AI134">
-        <v>0.1460475604657164</v>
+        <v>-0.1569149999999999</v>
       </c>
       <c r="AJ134">
-        <v>-0.1569149999999999</v>
+        <v>0.05568099999999987</v>
       </c>
       <c r="AK134">
-        <v>0.05568099999999987</v>
-      </c>
-      <c r="AL134">
         <v>-0.0005779999999973029</v>
+      </c>
+      <c r="AL134" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:38">
@@ -14881,20 +15151,23 @@
       <c r="AC135">
         <v>100.93</v>
       </c>
+      <c r="AG135">
+        <v>0.2988870806002533</v>
+      </c>
       <c r="AH135">
-        <v>0.2988870806002533</v>
+        <v>0.17311120912468</v>
       </c>
       <c r="AI135">
-        <v>0.17311120912468</v>
+        <v>-0.1026010000000002</v>
       </c>
       <c r="AJ135">
-        <v>-0.1026010000000002</v>
+        <v>0.09332399999999996</v>
       </c>
       <c r="AK135">
-        <v>0.09332399999999996</v>
-      </c>
-      <c r="AL135">
         <v>0.0003749999999982379</v>
+      </c>
+      <c r="AL135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:38">
@@ -14985,20 +15258,23 @@
       <c r="AC136">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG136">
+        <v>0.1500378188863966</v>
+      </c>
       <c r="AH136">
-        <v>0.1500378188863966</v>
+        <v>0.1135831396712924</v>
       </c>
       <c r="AI136">
-        <v>0.1135831396712924</v>
+        <v>0.202882</v>
       </c>
       <c r="AJ136">
-        <v>0.202882</v>
+        <v>0.3441130000000001</v>
       </c>
       <c r="AK136">
-        <v>0.3441130000000001</v>
-      </c>
-      <c r="AL136">
         <v>0.0004629999999998802</v>
+      </c>
+      <c r="AL136" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:38">
@@ -15095,20 +15371,23 @@
       <c r="AF137">
         <v>11.6684130766311</v>
       </c>
+      <c r="AG137">
+        <v>0.105018518367814</v>
+      </c>
       <c r="AH137">
-        <v>0.105018518367814</v>
+        <v>0.06478231453898417</v>
       </c>
       <c r="AI137">
-        <v>0.06478231453898417</v>
+        <v>0.1685619999999999</v>
       </c>
       <c r="AJ137">
-        <v>0.1685619999999999</v>
+        <v>0.161697</v>
       </c>
       <c r="AK137">
-        <v>0.161697</v>
-      </c>
-      <c r="AL137">
         <v>-0.0003170000000007889</v>
+      </c>
+      <c r="AL137" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:38">
@@ -15205,20 +15484,23 @@
       <c r="AF138">
         <v>11.9784847026855</v>
       </c>
+      <c r="AG138">
+        <v>0.1099174657380804</v>
+      </c>
       <c r="AH138">
-        <v>0.1099174657380804</v>
+        <v>0.03305035091308207</v>
       </c>
       <c r="AI138">
-        <v>0.03305035091308207</v>
+        <v>0.216096</v>
       </c>
       <c r="AJ138">
-        <v>0.216096</v>
+        <v>0.141199</v>
       </c>
       <c r="AK138">
-        <v>0.141199</v>
-      </c>
-      <c r="AL138">
         <v>-0.0009410000000009688</v>
+      </c>
+      <c r="AL138" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:38">
@@ -15315,20 +15597,23 @@
       <c r="AF139">
         <v>11.8855616228225</v>
       </c>
+      <c r="AG139">
+        <v>0.09768871548329933</v>
+      </c>
       <c r="AH139">
-        <v>0.09768871548329933</v>
+        <v>0.04585014028122186</v>
       </c>
       <c r="AI139">
-        <v>0.04585014028122186</v>
+        <v>0.2330309999999999</v>
       </c>
       <c r="AJ139">
-        <v>0.2330309999999999</v>
+        <v>0.147297</v>
       </c>
       <c r="AK139">
-        <v>0.147297</v>
-      </c>
-      <c r="AL139">
         <v>0.0002049999999993446</v>
+      </c>
+      <c r="AL139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:38">
@@ -15425,20 +15710,23 @@
       <c r="AF140">
         <v>11.7783778069365</v>
       </c>
+      <c r="AG140">
+        <v>0.1264268830218466</v>
+      </c>
       <c r="AH140">
-        <v>0.1264268830218466</v>
+        <v>0.05959112496226492</v>
       </c>
       <c r="AI140">
-        <v>0.05959112496226492</v>
+        <v>0.153516</v>
       </c>
       <c r="AJ140">
-        <v>0.153516</v>
+        <v>0.056759</v>
       </c>
       <c r="AK140">
-        <v>0.056759</v>
-      </c>
-      <c r="AL140">
         <v>-0.0008489999999987674</v>
+      </c>
+      <c r="AL140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:38">
@@ -15535,20 +15823,23 @@
       <c r="AF141">
         <v>11.7162477369852</v>
       </c>
+      <c r="AG141">
+        <v>0.1432972959592655</v>
+      </c>
       <c r="AH141">
-        <v>0.1432972959592655</v>
+        <v>0.09881669354990105</v>
       </c>
       <c r="AI141">
-        <v>0.09881669354990105</v>
+        <v>0.167231</v>
       </c>
       <c r="AJ141">
-        <v>0.167231</v>
+        <v>0.08671899999999999</v>
       </c>
       <c r="AK141">
-        <v>0.08671899999999999</v>
-      </c>
-      <c r="AL141">
         <v>-0.0006370000000011089</v>
+      </c>
+      <c r="AL141" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:38">
@@ -15645,20 +15936,23 @@
       <c r="AF142">
         <v>11.118681180436</v>
       </c>
+      <c r="AG142">
+        <v>0.07687045496819339</v>
+      </c>
       <c r="AH142">
-        <v>0.07687045496819339</v>
+        <v>0.1069343835269604</v>
       </c>
       <c r="AI142">
-        <v>0.1069343835269604</v>
+        <v>0.2545200000000001</v>
       </c>
       <c r="AJ142">
-        <v>0.2545200000000001</v>
+        <v>0.46373</v>
       </c>
       <c r="AK142">
-        <v>0.46373</v>
-      </c>
-      <c r="AL142">
         <v>-0.0001460000000008677</v>
+      </c>
+      <c r="AL142" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:38">
@@ -15755,20 +16049,23 @@
       <c r="AF143">
         <v>12.6596673834992</v>
       </c>
+      <c r="AG143">
+        <v>0.1611004944935874</v>
+      </c>
       <c r="AH143">
-        <v>0.1611004944935874</v>
+        <v>0.06645147809885275</v>
       </c>
       <c r="AI143">
-        <v>0.06645147809885275</v>
+        <v>0.218564</v>
       </c>
       <c r="AJ143">
-        <v>0.218564</v>
+        <v>0.1215590000000001</v>
       </c>
       <c r="AK143">
-        <v>0.1215590000000001</v>
-      </c>
-      <c r="AL143">
         <v>0.0001390000000007774</v>
+      </c>
+      <c r="AL143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:38">
@@ -15865,20 +16162,23 @@
       <c r="AF144">
         <v>12.8936854888585</v>
       </c>
+      <c r="AG144">
+        <v>0.1758219166940297</v>
+      </c>
       <c r="AH144">
-        <v>0.1758219166940297</v>
+        <v>0.1408352471936424</v>
       </c>
       <c r="AI144">
-        <v>0.1408352471936424</v>
+        <v>0.192809</v>
       </c>
       <c r="AJ144">
-        <v>0.192809</v>
+        <v>0.141786</v>
       </c>
       <c r="AK144">
-        <v>0.141786</v>
-      </c>
-      <c r="AL144">
         <v>0.0005139999999990152</v>
+      </c>
+      <c r="AL144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:38">
@@ -15975,20 +16275,23 @@
       <c r="AF145">
         <v>12.8498936023601</v>
       </c>
+      <c r="AG145">
+        <v>0.1653920422472224</v>
+      </c>
       <c r="AH145">
-        <v>0.1653920422472224</v>
+        <v>0.1675260079550339</v>
       </c>
       <c r="AI145">
-        <v>0.1675260079550339</v>
+        <v>0.2610709999999999</v>
       </c>
       <c r="AJ145">
-        <v>0.2610709999999999</v>
+        <v>0.3627610000000001</v>
       </c>
       <c r="AK145">
-        <v>0.3627610000000001</v>
-      </c>
-      <c r="AL145">
         <v>0.0004530000000002588</v>
+      </c>
+      <c r="AL145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:38">
@@ -16079,20 +16382,23 @@
       <c r="AC146">
         <v>52.32</v>
       </c>
+      <c r="AG146">
+        <v>0.1767433168105416</v>
+      </c>
       <c r="AH146">
-        <v>0.1767433168105416</v>
+        <v>0.07368900847641113</v>
       </c>
       <c r="AI146">
-        <v>0.07368900847641113</v>
+        <v>0.02912700000000013</v>
       </c>
       <c r="AJ146">
-        <v>0.02912700000000013</v>
+        <v>0.339063</v>
       </c>
       <c r="AK146">
-        <v>0.339063</v>
-      </c>
-      <c r="AL146">
         <v>-0.000793000000001598</v>
+      </c>
+      <c r="AL146" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:38">
@@ -16183,20 +16489,23 @@
       <c r="AC147">
         <v>43.64</v>
       </c>
+      <c r="AG147">
+        <v>0.2884103320441938</v>
+      </c>
       <c r="AH147">
-        <v>0.2884103320441938</v>
+        <v>0.2559556686226093</v>
       </c>
       <c r="AI147">
-        <v>0.2559556686226093</v>
+        <v>0.02422100000000005</v>
       </c>
       <c r="AJ147">
-        <v>0.02422100000000005</v>
+        <v>0.25674</v>
       </c>
       <c r="AK147">
-        <v>0.25674</v>
-      </c>
-      <c r="AL147">
         <v>-0.0003129999999984534</v>
+      </c>
+      <c r="AL147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:38">
@@ -16287,20 +16596,23 @@
       <c r="AC148">
         <v>54.13</v>
       </c>
+      <c r="AG148">
+        <v>0.2874941940275127</v>
+      </c>
       <c r="AH148">
-        <v>0.2874941940275127</v>
+        <v>0.3097028324805222</v>
       </c>
       <c r="AI148">
-        <v>0.3097028324805222</v>
+        <v>0.02816200000000002</v>
       </c>
       <c r="AJ148">
-        <v>0.02816200000000002</v>
+        <v>0.2837769999999999</v>
       </c>
       <c r="AK148">
-        <v>0.2837769999999999</v>
-      </c>
-      <c r="AL148">
         <v>0.0002049999999975682</v>
+      </c>
+      <c r="AL148" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:38">
@@ -16391,20 +16703,23 @@
       <c r="AC149">
         <v>71.34</v>
       </c>
+      <c r="AG149">
+        <v>0.2748639125176683</v>
+      </c>
       <c r="AH149">
-        <v>0.2748639125176683</v>
+        <v>0.3495918812774854</v>
       </c>
       <c r="AI149">
-        <v>0.3495918812774854</v>
+        <v>0.031833</v>
       </c>
       <c r="AJ149">
-        <v>0.031833</v>
+        <v>0.3592399999999999</v>
       </c>
       <c r="AK149">
-        <v>0.3592399999999999</v>
-      </c>
-      <c r="AL149">
         <v>-0.0003500000000009607</v>
+      </c>
+      <c r="AL149" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:38">
@@ -16495,20 +16810,23 @@
       <c r="AC150">
         <v>64.3</v>
       </c>
+      <c r="AG150">
+        <v>0.2970284442573063</v>
+      </c>
       <c r="AH150">
-        <v>0.2970284442573063</v>
+        <v>0.3520665115809507</v>
       </c>
       <c r="AI150">
-        <v>0.3520665115809507</v>
+        <v>0.02842300000000009</v>
       </c>
       <c r="AJ150">
-        <v>0.02842300000000009</v>
+        <v>0.3516000000000001</v>
       </c>
       <c r="AK150">
-        <v>0.3516000000000001</v>
-      </c>
-      <c r="AL150">
         <v>0.0001469999999983429</v>
+      </c>
+      <c r="AL150" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:38">
@@ -16599,20 +16917,23 @@
       <c r="AC151">
         <v>41.96</v>
       </c>
+      <c r="AG151">
+        <v>0.468382628469653</v>
+      </c>
       <c r="AH151">
-        <v>0.468382628469653</v>
+        <v>0.2109641410587131</v>
       </c>
       <c r="AI151">
-        <v>0.2109641410587131</v>
+        <v>0.01824700000000001</v>
       </c>
       <c r="AJ151">
-        <v>0.01824700000000001</v>
+        <v>0.184061</v>
       </c>
       <c r="AK151">
-        <v>0.184061</v>
-      </c>
-      <c r="AL151">
         <v>0.001018000000001962</v>
+      </c>
+      <c r="AL151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:38">
@@ -16703,20 +17024,23 @@
       <c r="AC152">
         <v>70.86</v>
       </c>
+      <c r="AG152">
+        <v>0.3637490586941644</v>
+      </c>
       <c r="AH152">
-        <v>0.3637490586941644</v>
+        <v>0.2772441126692647</v>
       </c>
       <c r="AI152">
-        <v>0.2772441126692647</v>
+        <v>0.1622440000000001</v>
       </c>
       <c r="AJ152">
-        <v>0.1622440000000001</v>
+        <v>0.3317300000000001</v>
       </c>
       <c r="AK152">
-        <v>0.3317300000000001</v>
-      </c>
-      <c r="AL152">
         <v>-0.0003700000000002035</v>
+      </c>
+      <c r="AL152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:38">
@@ -16807,20 +17131,23 @@
       <c r="AC153">
         <v>100.93</v>
       </c>
+      <c r="AG153">
+        <v>0.3452415990971049</v>
+      </c>
       <c r="AH153">
-        <v>0.3452415990971049</v>
+        <v>0.343194983815264</v>
       </c>
       <c r="AI153">
-        <v>0.343194983815264</v>
+        <v>0.286817</v>
       </c>
       <c r="AJ153">
-        <v>0.286817</v>
+        <v>0.582884</v>
       </c>
       <c r="AK153">
-        <v>0.582884</v>
-      </c>
-      <c r="AL153">
         <v>-0.0004720000000020264</v>
+      </c>
+      <c r="AL153" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:38">
@@ -16911,20 +17238,23 @@
       <c r="AC154">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG154">
+        <v>0.6401472226534571</v>
+      </c>
       <c r="AH154">
-        <v>0.6401472226534571</v>
+        <v>0.1315782742575437</v>
       </c>
       <c r="AI154">
-        <v>0.1315782742575437</v>
+        <v>0.150244</v>
       </c>
       <c r="AJ154">
-        <v>0.150244</v>
+        <v>0.09068900000000002</v>
       </c>
       <c r="AK154">
-        <v>0.09068900000000002</v>
-      </c>
-      <c r="AL154">
         <v>-0.0002880000000011762</v>
+      </c>
+      <c r="AL154" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:38">
@@ -17021,20 +17351,23 @@
       <c r="AF155">
         <v>23.363155171353</v>
       </c>
+      <c r="AG155">
+        <v>0.08398503082391079</v>
+      </c>
       <c r="AH155">
-        <v>0.08398503082391079</v>
+        <v>0.03066297673707395</v>
       </c>
       <c r="AI155">
-        <v>0.03066297673707395</v>
+        <v>0.322663</v>
       </c>
       <c r="AJ155">
-        <v>0.322663</v>
+        <v>0.416246</v>
       </c>
       <c r="AK155">
-        <v>0.416246</v>
-      </c>
-      <c r="AL155">
         <v>0.001124999999998266</v>
+      </c>
+      <c r="AL155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:38">
@@ -17125,20 +17458,23 @@
       <c r="AC156">
         <v>43.64</v>
       </c>
+      <c r="AG156">
+        <v>0.08675921246856487</v>
+      </c>
       <c r="AH156">
-        <v>0.08675921246856487</v>
+        <v>0.08262569622794662</v>
       </c>
       <c r="AI156">
-        <v>0.08262569622794662</v>
+        <v>0.3470599999999999</v>
       </c>
       <c r="AJ156">
-        <v>0.3470599999999999</v>
+        <v>0.372474</v>
       </c>
       <c r="AK156">
-        <v>0.372474</v>
-      </c>
-      <c r="AL156">
         <v>0.0002609999999982904</v>
+      </c>
+      <c r="AL156" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:38">
@@ -17229,20 +17565,23 @@
       <c r="AC157">
         <v>54.13</v>
       </c>
+      <c r="AG157">
+        <v>0.09373368485523932</v>
+      </c>
       <c r="AH157">
-        <v>0.09373368485523932</v>
+        <v>0.1236966344945768</v>
       </c>
       <c r="AI157">
-        <v>0.1236966344945768</v>
+        <v>0.308845</v>
       </c>
       <c r="AJ157">
-        <v>0.308845</v>
+        <v>0.37936</v>
       </c>
       <c r="AK157">
-        <v>0.37936</v>
-      </c>
-      <c r="AL157">
         <v>0.0009599999999991837</v>
+      </c>
+      <c r="AL157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:38">
@@ -17333,20 +17672,23 @@
       <c r="AC158">
         <v>71.34</v>
       </c>
+      <c r="AG158">
+        <v>0.09381075445727499</v>
+      </c>
       <c r="AH158">
-        <v>0.09381075445727499</v>
+        <v>0.07869768673062702</v>
       </c>
       <c r="AI158">
-        <v>0.07869768673062702</v>
+        <v>0.2978430000000001</v>
       </c>
       <c r="AJ158">
-        <v>0.2978430000000001</v>
+        <v>0.363009</v>
       </c>
       <c r="AK158">
-        <v>0.363009</v>
-      </c>
-      <c r="AL158">
         <v>0.0001250000000005969</v>
+      </c>
+      <c r="AL158" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:38">
@@ -17437,20 +17779,23 @@
       <c r="AC159">
         <v>64.3</v>
       </c>
+      <c r="AG159">
+        <v>0.1168143671833313</v>
+      </c>
       <c r="AH159">
-        <v>0.1168143671833313</v>
+        <v>0.1408749973401882</v>
       </c>
       <c r="AI159">
-        <v>0.1408749973401882</v>
+        <v>0.280926</v>
       </c>
       <c r="AJ159">
-        <v>0.280926</v>
+        <v>0.3581129999999999</v>
       </c>
       <c r="AK159">
-        <v>0.3581129999999999</v>
-      </c>
-      <c r="AL159">
         <v>6.199999999978445E-05</v>
+      </c>
+      <c r="AL159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:38">
@@ -17547,20 +17892,23 @@
       <c r="AF160">
         <v>22.2099126100845</v>
       </c>
+      <c r="AG160">
+        <v>0.08354707441961179</v>
+      </c>
       <c r="AH160">
-        <v>0.08354707441961179</v>
+        <v>0.1557414382253728</v>
       </c>
       <c r="AI160">
-        <v>0.1557414382253728</v>
+        <v>0.3722460000000001</v>
       </c>
       <c r="AJ160">
-        <v>0.3722460000000001</v>
+        <v>0.377078</v>
       </c>
       <c r="AK160">
-        <v>0.377078</v>
-      </c>
-      <c r="AL160">
         <v>5.999999999950489E-05</v>
+      </c>
+      <c r="AL160" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:38">
@@ -17651,20 +17999,23 @@
       <c r="AC161">
         <v>70.86</v>
       </c>
+      <c r="AG161">
+        <v>0.1385337003096474</v>
+      </c>
       <c r="AH161">
-        <v>0.1385337003096474</v>
+        <v>0.07441932572105685</v>
       </c>
       <c r="AI161">
-        <v>0.07441932572105685</v>
+        <v>0.3112229999999999</v>
       </c>
       <c r="AJ161">
-        <v>0.3112229999999999</v>
+        <v>0.3517380000000001</v>
       </c>
       <c r="AK161">
-        <v>0.3517380000000001</v>
-      </c>
-      <c r="AL161">
         <v>-5.799999999922534E-05</v>
+      </c>
+      <c r="AL161" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:38">
@@ -17755,20 +18106,23 @@
       <c r="AC162">
         <v>100.93</v>
       </c>
+      <c r="AG162">
+        <v>0.1832369927057003</v>
+      </c>
       <c r="AH162">
-        <v>0.1832369927057003</v>
+        <v>0.1051548361218553</v>
       </c>
       <c r="AI162">
-        <v>0.1051548361218553</v>
+        <v>0.152067</v>
       </c>
       <c r="AJ162">
-        <v>0.152067</v>
+        <v>0.32443</v>
       </c>
       <c r="AK162">
-        <v>0.32443</v>
-      </c>
-      <c r="AL162">
         <v>0.0006970000000023902</v>
+      </c>
+      <c r="AL162" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:38">
@@ -17859,20 +18213,23 @@
       <c r="AC163">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG163">
+        <v>0.166376353668052</v>
+      </c>
       <c r="AH163">
-        <v>0.166376353668052</v>
+        <v>0.02422084458999872</v>
       </c>
       <c r="AI163">
-        <v>0.02422084458999872</v>
+        <v>0.1726850000000001</v>
       </c>
       <c r="AJ163">
-        <v>0.1726850000000001</v>
+        <v>0.3958539999999999</v>
       </c>
       <c r="AK163">
-        <v>0.3958539999999999</v>
-      </c>
-      <c r="AL163">
         <v>0.0004640000000009081</v>
+      </c>
+      <c r="AL163" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:38">
@@ -17963,19 +18320,22 @@
       <c r="AC164">
         <v>52.32</v>
       </c>
+      <c r="AG164">
+        <v>0.002512519360252321</v>
+      </c>
       <c r="AH164">
-        <v>0.002512519360252321</v>
+        <v>0.7425094123932052</v>
       </c>
       <c r="AI164">
-        <v>0.7425094123932052</v>
+        <v>0.5675779999999999</v>
       </c>
       <c r="AJ164">
-        <v>0.5675779999999999</v>
+        <v>0.431307</v>
       </c>
       <c r="AK164">
-        <v>0.431307</v>
-      </c>
-      <c r="AL164">
+        <v>0</v>
+      </c>
+      <c r="AL164" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18067,19 +18427,22 @@
       <c r="AC165">
         <v>43.64</v>
       </c>
+      <c r="AG165">
+        <v>0.01976115029129286</v>
+      </c>
       <c r="AH165">
-        <v>0.01976115029129286</v>
+        <v>0.5451367349911772</v>
       </c>
       <c r="AI165">
-        <v>0.5451367349911772</v>
+        <v>0.3814890000000001</v>
       </c>
       <c r="AJ165">
-        <v>0.3814890000000001</v>
+        <v>0.270439</v>
       </c>
       <c r="AK165">
-        <v>0.270439</v>
-      </c>
-      <c r="AL165">
+        <v>0</v>
+      </c>
+      <c r="AL165" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18171,19 +18534,22 @@
       <c r="AC166">
         <v>54.13</v>
       </c>
+      <c r="AG166">
+        <v>0.02729375376008817</v>
+      </c>
       <c r="AH166">
-        <v>0.02729375376008817</v>
+        <v>0.5903325177499943</v>
       </c>
       <c r="AI166">
-        <v>0.5903325177499943</v>
+        <v>0.3735270000000001</v>
       </c>
       <c r="AJ166">
-        <v>0.3735270000000001</v>
+        <v>0.240491</v>
       </c>
       <c r="AK166">
-        <v>0.240491</v>
-      </c>
-      <c r="AL166">
+        <v>0</v>
+      </c>
+      <c r="AL166" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18275,19 +18641,22 @@
       <c r="AC167">
         <v>71.34</v>
       </c>
+      <c r="AG167">
+        <v>0.03582862390022516</v>
+      </c>
       <c r="AH167">
-        <v>0.03582862390022516</v>
+        <v>0.3942434298284644</v>
       </c>
       <c r="AI167">
-        <v>0.3942434298284644</v>
+        <v>0.280968</v>
       </c>
       <c r="AJ167">
-        <v>0.280968</v>
+        <v>0.101148</v>
       </c>
       <c r="AK167">
-        <v>0.101148</v>
-      </c>
-      <c r="AL167">
+        <v>0</v>
+      </c>
+      <c r="AL167" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18379,19 +18748,22 @@
       <c r="AC168">
         <v>64.3</v>
       </c>
+      <c r="AG168">
+        <v>0.0554137583224202</v>
+      </c>
       <c r="AH168">
-        <v>0.0554137583224202</v>
+        <v>0.4159173949601593</v>
       </c>
       <c r="AI168">
-        <v>0.4159173949601593</v>
+        <v>0.07359000000000004</v>
       </c>
       <c r="AJ168">
-        <v>0.07359000000000004</v>
+        <v>-0.05151300000000003</v>
       </c>
       <c r="AK168">
-        <v>-0.05151300000000003</v>
-      </c>
-      <c r="AL168">
+        <v>0</v>
+      </c>
+      <c r="AL168" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18483,19 +18855,22 @@
       <c r="AC169">
         <v>41.96</v>
       </c>
+      <c r="AG169">
+        <v>0.02847998171111813</v>
+      </c>
       <c r="AH169">
-        <v>0.02847998171111813</v>
+        <v>0.2587236547105496</v>
       </c>
       <c r="AI169">
-        <v>0.2587236547105496</v>
+        <v>0.22895</v>
       </c>
       <c r="AJ169">
-        <v>0.22895</v>
+        <v>0.135674</v>
       </c>
       <c r="AK169">
-        <v>0.135674</v>
-      </c>
-      <c r="AL169">
+        <v>0</v>
+      </c>
+      <c r="AL169" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18587,19 +18962,22 @@
       <c r="AC170">
         <v>70.86</v>
       </c>
+      <c r="AG170">
+        <v>0.06297597425574923</v>
+      </c>
       <c r="AH170">
-        <v>0.06297597425574923</v>
+        <v>0.4484279392268828</v>
       </c>
       <c r="AI170">
-        <v>0.4484279392268828</v>
+        <v>0.2106089999999999</v>
       </c>
       <c r="AJ170">
-        <v>0.2106089999999999</v>
+        <v>0.03934400000000005</v>
       </c>
       <c r="AK170">
-        <v>0.03934400000000005</v>
-      </c>
-      <c r="AL170">
+        <v>0</v>
+      </c>
+      <c r="AL170" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18691,19 +19069,22 @@
       <c r="AC171">
         <v>100.93</v>
       </c>
+      <c r="AG171">
+        <v>0.07010885224408266</v>
+      </c>
       <c r="AH171">
-        <v>0.07010885224408266</v>
+        <v>0.4809924005622156</v>
       </c>
       <c r="AI171">
-        <v>0.4809924005622156</v>
+        <v>0.193952</v>
       </c>
       <c r="AJ171">
-        <v>0.193952</v>
+        <v>-0.100726</v>
       </c>
       <c r="AK171">
-        <v>-0.100726</v>
-      </c>
-      <c r="AL171">
+        <v>0</v>
+      </c>
+      <c r="AL171" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18795,19 +19176,22 @@
       <c r="AC172">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG172">
+        <v>0.05724440618133777</v>
+      </c>
       <c r="AH172">
-        <v>0.05724440618133777</v>
+        <v>0.4089569337364639</v>
       </c>
       <c r="AI172">
-        <v>0.4089569337364639</v>
+        <v>0.205815</v>
       </c>
       <c r="AJ172">
-        <v>0.205815</v>
+        <v>0.05454100000000006</v>
       </c>
       <c r="AK172">
-        <v>0.05454100000000006</v>
-      </c>
-      <c r="AL172">
+        <v>0</v>
+      </c>
+      <c r="AL172" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18908,20 +19292,23 @@
       <c r="AF173">
         <v>26.0434729497215</v>
       </c>
+      <c r="AG173">
+        <v>0.2284745911354167</v>
+      </c>
       <c r="AH173">
-        <v>0.2284745911354167</v>
+        <v>0.1721840676964483</v>
       </c>
       <c r="AI173">
-        <v>0.1721840676964483</v>
+        <v>0.552594</v>
       </c>
       <c r="AJ173">
-        <v>0.552594</v>
+        <v>0.527532</v>
       </c>
       <c r="AK173">
-        <v>0.527532</v>
-      </c>
-      <c r="AL173">
         <v>-0.001165000000000305</v>
+      </c>
+      <c r="AL173" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:38">
@@ -19021,20 +19408,23 @@
       <c r="AF174">
         <v>26.8205974834377</v>
       </c>
+      <c r="AG174">
+        <v>0.2694047184702383</v>
+      </c>
       <c r="AH174">
-        <v>0.2694047184702383</v>
+        <v>0.1957180558810933</v>
       </c>
       <c r="AI174">
-        <v>0.1957180558810933</v>
+        <v>0.513759</v>
       </c>
       <c r="AJ174">
-        <v>0.513759</v>
+        <v>0.4648709999999999</v>
       </c>
       <c r="AK174">
-        <v>0.4648709999999999</v>
-      </c>
-      <c r="AL174">
         <v>-5.299999999763827E-05</v>
+      </c>
+      <c r="AL174" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:38">
@@ -19134,20 +19524,23 @@
       <c r="AF175">
         <v>27.7646551590305</v>
       </c>
+      <c r="AG175">
+        <v>0.2685276997434527</v>
+      </c>
       <c r="AH175">
-        <v>0.2685276997434527</v>
+        <v>0.321461730642123</v>
       </c>
       <c r="AI175">
-        <v>0.321461730642123</v>
+        <v>0.523873</v>
       </c>
       <c r="AJ175">
-        <v>0.523873</v>
+        <v>0.4966710000000001</v>
       </c>
       <c r="AK175">
-        <v>0.4966710000000001</v>
-      </c>
-      <c r="AL175">
         <v>-0.000256000000000256</v>
+      </c>
+      <c r="AL175" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:38">
@@ -19244,20 +19637,23 @@
       <c r="AF176">
         <v>28.956310897592</v>
       </c>
+      <c r="AG176">
+        <v>0.42535877034795</v>
+      </c>
       <c r="AH176">
-        <v>0.42535877034795</v>
+        <v>0.3860945717983041</v>
       </c>
       <c r="AI176">
-        <v>0.3860945717983041</v>
+        <v>0.6145510000000001</v>
       </c>
       <c r="AJ176">
-        <v>0.6145510000000001</v>
+        <v>0.5632569999999999</v>
       </c>
       <c r="AK176">
-        <v>0.5632569999999999</v>
-      </c>
-      <c r="AL176">
         <v>0.0005860000000019738</v>
+      </c>
+      <c r="AL176" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:38">
@@ -19357,20 +19753,23 @@
       <c r="AF177">
         <v>28.6261738973365</v>
       </c>
+      <c r="AG177">
+        <v>0.3984018073166344</v>
+      </c>
       <c r="AH177">
-        <v>0.3984018073166344</v>
+        <v>0.3759290672695663</v>
       </c>
       <c r="AI177">
-        <v>0.3759290672695663</v>
+        <v>0.5864830000000001</v>
       </c>
       <c r="AJ177">
-        <v>0.5864830000000001</v>
+        <v>0.5840310000000001</v>
       </c>
       <c r="AK177">
-        <v>0.5840310000000001</v>
-      </c>
-      <c r="AL177">
         <v>0.0001839999999972974</v>
+      </c>
+      <c r="AL177" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:38">
@@ -19470,20 +19869,23 @@
       <c r="AF178">
         <v>26.937333176305</v>
       </c>
+      <c r="AG178">
+        <v>0.1631999444747454</v>
+      </c>
       <c r="AH178">
-        <v>0.1631999444747454</v>
+        <v>0.1572137663847738</v>
       </c>
       <c r="AI178">
-        <v>0.1572137663847738</v>
+        <v>0.603206</v>
       </c>
       <c r="AJ178">
-        <v>0.603206</v>
+        <v>0.566684</v>
       </c>
       <c r="AK178">
-        <v>0.566684</v>
-      </c>
-      <c r="AL178">
         <v>0.0004419999999996094</v>
+      </c>
+      <c r="AL178" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:38">
@@ -19574,20 +19976,23 @@
       <c r="AC179">
         <v>70.86</v>
       </c>
+      <c r="AG179">
+        <v>0.2569729556191575</v>
+      </c>
       <c r="AH179">
-        <v>0.2569729556191575</v>
+        <v>0.1788439567380756</v>
       </c>
       <c r="AI179">
-        <v>0.1788439567380756</v>
+        <v>0.50374</v>
       </c>
       <c r="AJ179">
-        <v>0.50374</v>
+        <v>0.4583369999999999</v>
       </c>
       <c r="AK179">
-        <v>0.4583369999999999</v>
-      </c>
-      <c r="AL179">
         <v>-0.0002320000000040068</v>
+      </c>
+      <c r="AL179" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:38">
@@ -19678,20 +20083,23 @@
       <c r="AC180">
         <v>100.93</v>
       </c>
+      <c r="AG180">
+        <v>0.359308873435062</v>
+      </c>
       <c r="AH180">
-        <v>0.359308873435062</v>
+        <v>0.2832841957376163</v>
       </c>
       <c r="AI180">
-        <v>0.2832841957376163</v>
+        <v>0.526769</v>
       </c>
       <c r="AJ180">
-        <v>0.526769</v>
+        <v>0.579667</v>
       </c>
       <c r="AK180">
-        <v>0.579667</v>
-      </c>
-      <c r="AL180">
         <v>0.0008570000000034383</v>
+      </c>
+      <c r="AL180" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:38">
@@ -19782,20 +20190,23 @@
       <c r="AC181">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG181">
+        <v>0.3301068042326465</v>
+      </c>
       <c r="AH181">
-        <v>0.3301068042326465</v>
+        <v>0.2306604755891775</v>
       </c>
       <c r="AI181">
-        <v>0.2306604755891775</v>
+        <v>0.4716079999999999</v>
       </c>
       <c r="AJ181">
-        <v>0.4716079999999999</v>
+        <v>0.6585830000000001</v>
       </c>
       <c r="AK181">
-        <v>0.6585830000000001</v>
-      </c>
-      <c r="AL181">
         <v>0.0004629999999998802</v>
+      </c>
+      <c r="AL181" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:38">
@@ -19874,14 +20285,17 @@
       <c r="AF182">
         <v>34.3048945637454</v>
       </c>
+      <c r="AI182">
+        <v>-0.02149299999999998</v>
+      </c>
       <c r="AJ182">
-        <v>-0.02149299999999998</v>
+        <v>-0.01667799999999997</v>
       </c>
       <c r="AK182">
-        <v>-0.01667799999999997</v>
-      </c>
-      <c r="AL182">
         <v>-0.0003180000000000405</v>
+      </c>
+      <c r="AL182" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:38">
@@ -19960,14 +20374,17 @@
       <c r="AF183">
         <v>28.1318859186068</v>
       </c>
+      <c r="AI183">
+        <v>-0.01667599999999991</v>
+      </c>
       <c r="AJ183">
-        <v>-0.01667599999999991</v>
+        <v>-0.01235200000000003</v>
       </c>
       <c r="AK183">
-        <v>-0.01235200000000003</v>
-      </c>
-      <c r="AL183">
         <v>0.0001049999999978013</v>
+      </c>
+      <c r="AL183" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:38">
@@ -20046,14 +20463,17 @@
       <c r="AF184">
         <v>26.299301993104</v>
       </c>
+      <c r="AI184">
+        <v>-0.01484400000000008</v>
+      </c>
       <c r="AJ184">
-        <v>-0.01484400000000008</v>
+        <v>-0.01209400000000005</v>
       </c>
       <c r="AK184">
-        <v>-0.01209400000000005</v>
-      </c>
-      <c r="AL184">
         <v>0.0005109999999994841</v>
+      </c>
+      <c r="AL184" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:38">
@@ -20126,14 +20546,17 @@
       <c r="AC185">
         <v>71.34</v>
       </c>
+      <c r="AI185">
+        <v>-0.01304099999999997</v>
+      </c>
       <c r="AJ185">
-        <v>-0.01304099999999997</v>
+        <v>-0.010494</v>
       </c>
       <c r="AK185">
-        <v>-0.010494</v>
-      </c>
-      <c r="AL185">
         <v>7.499999999893703E-05</v>
+      </c>
+      <c r="AL185" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:38">
@@ -20206,14 +20629,17 @@
       <c r="AC186">
         <v>64.3</v>
       </c>
+      <c r="AI186">
+        <v>-0.008539999999999992</v>
+      </c>
       <c r="AJ186">
-        <v>-0.008539999999999992</v>
+        <v>-0.007730999999999932</v>
       </c>
       <c r="AK186">
-        <v>-0.007730999999999932</v>
-      </c>
-      <c r="AL186">
         <v>7.399999999790907E-05</v>
+      </c>
+      <c r="AL186" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:38">
@@ -20292,14 +20718,17 @@
       <c r="AF187">
         <v>28.4590147448871</v>
       </c>
+      <c r="AI187">
+        <v>-0.004216999999999915</v>
+      </c>
       <c r="AJ187">
-        <v>-0.004216999999999915</v>
+        <v>-0.003817999999999988</v>
       </c>
       <c r="AK187">
-        <v>-0.003817999999999988</v>
-      </c>
-      <c r="AL187">
         <v>-0.000484000000000151</v>
+      </c>
+      <c r="AL187" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:38">
@@ -20366,14 +20795,17 @@
       <c r="AC188">
         <v>70.86</v>
       </c>
+      <c r="AI188">
+        <v>0</v>
+      </c>
       <c r="AJ188">
         <v>0</v>
       </c>
       <c r="AK188">
-        <v>0</v>
-      </c>
-      <c r="AL188">
         <v>-0.0001160000000055561</v>
+      </c>
+      <c r="AL188" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:38">
@@ -20440,14 +20872,17 @@
       <c r="AC189">
         <v>100.93</v>
       </c>
+      <c r="AI189">
+        <v>0.01367800000000008</v>
+      </c>
       <c r="AJ189">
-        <v>0.01367800000000008</v>
+        <v>0.01238199999999989</v>
       </c>
       <c r="AK189">
-        <v>0.01238199999999989</v>
-      </c>
-      <c r="AL189">
         <v>-7.499999999538431E-05</v>
+      </c>
+      <c r="AL189" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:38">
@@ -20514,14 +20949,17 @@
       <c r="AC190">
         <v>82.48999999999999</v>
       </c>
+      <c r="AI190">
+        <v>0.01791200000000004</v>
+      </c>
       <c r="AJ190">
-        <v>0.01791200000000004</v>
+        <v>0.01297199999999998</v>
       </c>
       <c r="AK190">
-        <v>0.01297199999999998</v>
-      </c>
-      <c r="AL190">
         <v>0.0009360000000029345</v>
+      </c>
+      <c r="AL190" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:38">
@@ -20618,20 +21056,23 @@
       <c r="AF191">
         <v>19.7095456938961</v>
       </c>
+      <c r="AG191">
+        <v>0.1462679491850953</v>
+      </c>
       <c r="AH191">
-        <v>0.1462679491850953</v>
+        <v>0.3174370660436578</v>
       </c>
       <c r="AI191">
-        <v>0.3174370660436578</v>
+        <v>0.3851330000000001</v>
       </c>
       <c r="AJ191">
-        <v>0.3851330000000001</v>
+        <v>0.3826850000000001</v>
       </c>
       <c r="AK191">
-        <v>0.3826850000000001</v>
-      </c>
-      <c r="AL191">
         <v>-0.001058000000000447</v>
+      </c>
+      <c r="AL191" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:38">
@@ -20728,20 +21169,23 @@
       <c r="AF192">
         <v>20.1305432828484</v>
       </c>
+      <c r="AG192">
+        <v>0.1504102461140645</v>
+      </c>
       <c r="AH192">
-        <v>0.1504102461140645</v>
+        <v>0.3117551353580435</v>
       </c>
       <c r="AI192">
-        <v>0.3117551353580435</v>
+        <v>0.3770469999999999</v>
       </c>
       <c r="AJ192">
-        <v>0.3770469999999999</v>
+        <v>0.488712</v>
       </c>
       <c r="AK192">
-        <v>0.488712</v>
-      </c>
-      <c r="AL192">
         <v>-0.0005230000000011614</v>
+      </c>
+      <c r="AL192" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:38">
@@ -20838,19 +21282,22 @@
       <c r="AF193">
         <v>19.4078532828264</v>
       </c>
+      <c r="AG193">
+        <v>0.1305017186056938</v>
+      </c>
       <c r="AH193">
-        <v>0.1305017186056938</v>
+        <v>0.3097270612724199</v>
       </c>
       <c r="AI193">
-        <v>0.3097270612724199</v>
+        <v>0.4579550000000001</v>
       </c>
       <c r="AJ193">
-        <v>0.4579550000000001</v>
+        <v>0.5591769999999999</v>
       </c>
       <c r="AK193">
-        <v>0.5591769999999999</v>
-      </c>
-      <c r="AL193">
+        <v>0</v>
+      </c>
+      <c r="AL193" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20942,20 +21389,23 @@
       <c r="AC194">
         <v>71.34</v>
       </c>
+      <c r="AG194">
+        <v>0.1484761584336482</v>
+      </c>
       <c r="AH194">
-        <v>0.1484761584336482</v>
+        <v>0.2881158629886019</v>
       </c>
       <c r="AI194">
-        <v>0.2881158629886019</v>
+        <v>0.472494</v>
       </c>
       <c r="AJ194">
-        <v>0.472494</v>
+        <v>0.6042789999999999</v>
       </c>
       <c r="AK194">
-        <v>0.6042789999999999</v>
-      </c>
-      <c r="AL194">
         <v>0.0009359999999993818</v>
+      </c>
+      <c r="AL194" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:38">
@@ -21046,20 +21496,23 @@
       <c r="AC195">
         <v>64.3</v>
       </c>
+      <c r="AG195">
+        <v>0.1655301124298607</v>
+      </c>
       <c r="AH195">
-        <v>0.1655301124298607</v>
+        <v>0.2576196934920843</v>
       </c>
       <c r="AI195">
-        <v>0.2576196934920843</v>
+        <v>0.531384</v>
       </c>
       <c r="AJ195">
-        <v>0.531384</v>
+        <v>0.643064</v>
       </c>
       <c r="AK195">
-        <v>0.643064</v>
-      </c>
-      <c r="AL195">
         <v>-0.0003069999999993911</v>
+      </c>
+      <c r="AL195" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:38">
@@ -21150,19 +21603,22 @@
       <c r="AC196">
         <v>41.96</v>
       </c>
+      <c r="AG196">
+        <v>0.1495272175829236</v>
+      </c>
       <c r="AH196">
-        <v>0.1495272175829236</v>
+        <v>0.233465127725727</v>
       </c>
       <c r="AI196">
-        <v>0.233465127725727</v>
+        <v>0.6280979999999999</v>
       </c>
       <c r="AJ196">
-        <v>0.6280979999999999</v>
+        <v>0.660381</v>
       </c>
       <c r="AK196">
-        <v>0.660381</v>
-      </c>
-      <c r="AL196">
+        <v>0</v>
+      </c>
+      <c r="AL196" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21254,20 +21710,23 @@
       <c r="AC197">
         <v>70.86</v>
       </c>
+      <c r="AG197">
+        <v>0.1802907635768551</v>
+      </c>
       <c r="AH197">
-        <v>0.1802907635768551</v>
+        <v>0.1613949918742637</v>
       </c>
       <c r="AI197">
-        <v>0.1613949918742637</v>
+        <v>0.433802</v>
       </c>
       <c r="AJ197">
-        <v>0.433802</v>
+        <v>0.5013840000000001</v>
       </c>
       <c r="AK197">
-        <v>0.5013840000000001</v>
-      </c>
-      <c r="AL197">
         <v>-0.0002899999999996794</v>
+      </c>
+      <c r="AL197" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:38">
@@ -21358,20 +21817,23 @@
       <c r="AC198">
         <v>100.93</v>
       </c>
+      <c r="AG198">
+        <v>0.2410425722331098</v>
+      </c>
       <c r="AH198">
-        <v>0.2410425722331098</v>
+        <v>0.1203121389865423</v>
       </c>
       <c r="AI198">
-        <v>0.1203121389865423</v>
+        <v>0.3568280000000001</v>
       </c>
       <c r="AJ198">
-        <v>0.3568280000000001</v>
+        <v>0.4330920000000001</v>
       </c>
       <c r="AK198">
-        <v>0.4330920000000001</v>
-      </c>
-      <c r="AL198">
         <v>0.0006699999999995043</v>
+      </c>
+      <c r="AL198" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:38">
@@ -21462,20 +21924,23 @@
       <c r="AC199">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG199">
+        <v>0.1770016776307124</v>
+      </c>
       <c r="AH199">
-        <v>0.1770016776307124</v>
+        <v>0.1584052763547052</v>
       </c>
       <c r="AI199">
-        <v>0.1584052763547052</v>
+        <v>0.477618</v>
       </c>
       <c r="AJ199">
-        <v>0.477618</v>
+        <v>0.6914030000000001</v>
       </c>
       <c r="AK199">
-        <v>0.6914030000000001</v>
-      </c>
-      <c r="AL199">
         <v>0.0003860000000024399</v>
+      </c>
+      <c r="AL199" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:38">
@@ -21573,22 +22038,22 @@
         <v>18.3681968714647</v>
       </c>
       <c r="AG200">
-        <v>250.9</v>
+        <v>0.609777513848424</v>
       </c>
       <c r="AH200">
-        <v>0.609777513848424</v>
+        <v>0.1339302282785785</v>
       </c>
       <c r="AI200">
-        <v>0.1339302282785785</v>
+        <v>0.204116</v>
       </c>
       <c r="AJ200">
-        <v>0.204116</v>
+        <v>0.3892650000000001</v>
       </c>
       <c r="AK200">
-        <v>0.3892650000000001</v>
-      </c>
-      <c r="AL200">
         <v>0.02402599999999921</v>
+      </c>
+      <c r="AL200" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:38">
@@ -21686,22 +22151,22 @@
         <v>19.1915888785393</v>
       </c>
       <c r="AG201">
-        <v>303.7</v>
+        <v>0.689670825989018</v>
       </c>
       <c r="AH201">
-        <v>0.689670825989018</v>
+        <v>0.1588439473995372</v>
       </c>
       <c r="AI201">
-        <v>0.1588439473995372</v>
+        <v>0.1954999999999999</v>
       </c>
       <c r="AJ201">
-        <v>0.1954999999999999</v>
+        <v>0.316087</v>
       </c>
       <c r="AK201">
-        <v>0.316087</v>
-      </c>
-      <c r="AL201">
         <v>0.02205299999999966</v>
+      </c>
+      <c r="AL201" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:38">
@@ -21799,22 +22264,22 @@
         <v>19.4469058462512</v>
       </c>
       <c r="AG202">
-        <v>256</v>
+        <v>0.6442564720267496</v>
       </c>
       <c r="AH202">
-        <v>0.6442564720267496</v>
+        <v>0.1883684635980547</v>
       </c>
       <c r="AI202">
-        <v>0.1883684635980547</v>
+        <v>0.2285170000000001</v>
       </c>
       <c r="AJ202">
-        <v>0.2285170000000001</v>
+        <v>0.36588</v>
       </c>
       <c r="AK202">
-        <v>0.36588</v>
-      </c>
-      <c r="AL202">
         <v>0.01765300000000281</v>
+      </c>
+      <c r="AL202" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:38">
@@ -21912,22 +22377,22 @@
         <v>18.3342427407296</v>
       </c>
       <c r="AG203">
-        <v>272.2</v>
+        <v>0.6515684491594819</v>
       </c>
       <c r="AH203">
-        <v>0.6515684491594819</v>
+        <v>0.2449643303945926</v>
       </c>
       <c r="AI203">
-        <v>0.2449643303945926</v>
+        <v>0.256392</v>
       </c>
       <c r="AJ203">
-        <v>0.256392</v>
+        <v>0.3315649999999999</v>
       </c>
       <c r="AK203">
-        <v>0.3315649999999999</v>
-      </c>
-      <c r="AL203">
         <v>-0.0005990000000011264</v>
+      </c>
+      <c r="AL203" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:38">
@@ -22028,22 +22493,22 @@
         <v>18.5191670625259</v>
       </c>
       <c r="AG204">
-        <v>318.3</v>
+        <v>0.5072426124578199</v>
       </c>
       <c r="AH204">
-        <v>0.5072426124578199</v>
+        <v>0.09719047864641431</v>
       </c>
       <c r="AI204">
-        <v>0.09719047864641431</v>
+        <v>0.3699140000000001</v>
       </c>
       <c r="AJ204">
-        <v>0.3699140000000001</v>
+        <v>0.4690000000000001</v>
       </c>
       <c r="AK204">
-        <v>0.4690000000000001</v>
-      </c>
-      <c r="AL204">
         <v>-1.668980000000001</v>
+      </c>
+      <c r="AL204" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:38">
@@ -22144,22 +22609,22 @@
         <v>18.6445328298003</v>
       </c>
       <c r="AG205">
-        <v>474.5</v>
+        <v>0.3959599241498478</v>
       </c>
       <c r="AH205">
-        <v>0.3959599241498478</v>
+        <v>0.08381267692197662</v>
       </c>
       <c r="AI205">
-        <v>0.08381267692197662</v>
+        <v>0.4215579999999999</v>
       </c>
       <c r="AJ205">
-        <v>0.4215579999999999</v>
+        <v>0.501712</v>
       </c>
       <c r="AK205">
-        <v>0.501712</v>
-      </c>
-      <c r="AL205">
         <v>0.0006299999999992423</v>
+      </c>
+      <c r="AL205" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:38">
@@ -22260,22 +22725,22 @@
         <v>18.3430886486889</v>
       </c>
       <c r="AG206">
-        <v>354.2</v>
+        <v>0.5464290055379426</v>
       </c>
       <c r="AH206">
-        <v>0.5464290055379426</v>
+        <v>0.1855129205662513</v>
       </c>
       <c r="AI206">
-        <v>0.1855129205662513</v>
+        <v>0.2738380000000001</v>
       </c>
       <c r="AJ206">
-        <v>0.2738380000000001</v>
+        <v>0.397416</v>
       </c>
       <c r="AK206">
-        <v>0.397416</v>
-      </c>
-      <c r="AL206">
         <v>-5.439218</v>
+      </c>
+      <c r="AL206" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:38">
@@ -22376,22 +22841,22 @@
         <v>19.2711611449441</v>
       </c>
       <c r="AG207">
-        <v>403.8</v>
+        <v>0.9126818206176207</v>
       </c>
       <c r="AH207">
-        <v>0.9126818206176207</v>
+        <v>0.2054494460870481</v>
       </c>
       <c r="AI207">
-        <v>0.2054494460870481</v>
+        <v>0.01491599999999993</v>
       </c>
       <c r="AJ207">
-        <v>0.01491599999999993</v>
+        <v>0.09117799999999998</v>
       </c>
       <c r="AK207">
-        <v>0.09117799999999998</v>
-      </c>
-      <c r="AL207">
         <v>-20.55665</v>
+      </c>
+      <c r="AL207" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:38">
@@ -22492,22 +22957,22 @@
         <v>19.0449981034342</v>
       </c>
       <c r="AG208">
-        <v>377.3</v>
+        <v>0.5807002676063495</v>
       </c>
       <c r="AH208">
-        <v>0.5807002676063495</v>
+        <v>0.06891872110030096</v>
       </c>
       <c r="AI208">
-        <v>0.06891872110030096</v>
+        <v>0.3461799999999999</v>
       </c>
       <c r="AJ208">
-        <v>0.3461799999999999</v>
+        <v>0.5570259999999999</v>
       </c>
       <c r="AK208">
-        <v>0.5570259999999999</v>
-      </c>
-      <c r="AL208">
         <v>0.925259999999998</v>
+      </c>
+      <c r="AL208" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:38">
@@ -22604,20 +23069,23 @@
       <c r="AF209">
         <v>16.7280500642775</v>
       </c>
+      <c r="AG209">
+        <v>0.03759231048167294</v>
+      </c>
       <c r="AH209">
-        <v>0.03759231048167294</v>
+        <v>0.004786776862769876</v>
       </c>
       <c r="AI209">
-        <v>0.004786776862769876</v>
+        <v>0.3460930000000001</v>
       </c>
       <c r="AJ209">
-        <v>0.3460930000000001</v>
+        <v>0.2886529999999999</v>
       </c>
       <c r="AK209">
-        <v>0.2886529999999999</v>
-      </c>
-      <c r="AL209">
         <v>-0.0001980000000010307</v>
+      </c>
+      <c r="AL209" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:38">
@@ -22714,20 +23182,23 @@
       <c r="AF210">
         <v>17.3827290426753</v>
       </c>
+      <c r="AG210">
+        <v>0.04099477282534929</v>
+      </c>
       <c r="AH210">
-        <v>0.04099477282534929</v>
+        <v>0</v>
       </c>
       <c r="AI210">
-        <v>0</v>
+        <v>0.3774219999999999</v>
       </c>
       <c r="AJ210">
-        <v>0.3774219999999999</v>
+        <v>0.271904</v>
       </c>
       <c r="AK210">
-        <v>0.271904</v>
-      </c>
-      <c r="AL210">
         <v>-0.0002610000000018431</v>
+      </c>
+      <c r="AL210" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:38">
@@ -22824,20 +23295,23 @@
       <c r="AF211">
         <v>17.8258154423666</v>
       </c>
+      <c r="AG211">
+        <v>0.0270324770713714</v>
+      </c>
       <c r="AH211">
-        <v>0.0270324770713714</v>
+        <v>0.07682535187662018</v>
       </c>
       <c r="AI211">
-        <v>0.07682535187662018</v>
+        <v>0.478664</v>
       </c>
       <c r="AJ211">
-        <v>0.478664</v>
+        <v>0.429569</v>
       </c>
       <c r="AK211">
-        <v>0.429569</v>
-      </c>
-      <c r="AL211">
         <v>-0.001086999999998284</v>
+      </c>
+      <c r="AL211" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:38">
@@ -22934,20 +23408,23 @@
       <c r="AF212">
         <v>16.9620048772188</v>
       </c>
+      <c r="AG212">
+        <v>0.04831572401735952</v>
+      </c>
       <c r="AH212">
-        <v>0.04831572401735952</v>
+        <v>0.0382672445842051</v>
       </c>
       <c r="AI212">
-        <v>0.0382672445842051</v>
+        <v>0.332342</v>
       </c>
       <c r="AJ212">
-        <v>0.332342</v>
+        <v>0.225992</v>
       </c>
       <c r="AK212">
-        <v>0.225992</v>
-      </c>
-      <c r="AL212">
         <v>0.0004369999999980223</v>
+      </c>
+      <c r="AL212" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:38">
@@ -23044,20 +23521,23 @@
       <c r="AF213">
         <v>18.8466464658517</v>
       </c>
+      <c r="AG213">
+        <v>0.05479898347597643</v>
+      </c>
       <c r="AH213">
-        <v>0.05479898347597643</v>
+        <v>0.04819162096409524</v>
       </c>
       <c r="AI213">
-        <v>0.04819162096409524</v>
+        <v>0.3166579999999999</v>
       </c>
       <c r="AJ213">
-        <v>0.3166579999999999</v>
+        <v>0.234299</v>
       </c>
       <c r="AK213">
-        <v>0.234299</v>
-      </c>
-      <c r="AL213">
         <v>-0.0001230000000020937</v>
+      </c>
+      <c r="AL213" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:38">
@@ -23154,20 +23634,23 @@
       <c r="AF214">
         <v>18.4889521054397</v>
       </c>
+      <c r="AG214">
+        <v>0.0277834977957687</v>
+      </c>
       <c r="AH214">
-        <v>0.0277834977957687</v>
+        <v>0.02900776625465974</v>
       </c>
       <c r="AI214">
-        <v>0.02900776625465974</v>
+        <v>0.4119510000000001</v>
       </c>
       <c r="AJ214">
-        <v>0.4119510000000001</v>
+        <v>0.299613</v>
       </c>
       <c r="AK214">
-        <v>0.299613</v>
-      </c>
-      <c r="AL214">
         <v>0.0001210000000000377</v>
+      </c>
+      <c r="AL214" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:38">
@@ -23264,20 +23747,23 @@
       <c r="AF215">
         <v>20.5214773588265</v>
       </c>
+      <c r="AG215">
+        <v>0.05738071631222737</v>
+      </c>
       <c r="AH215">
-        <v>0.05738071631222737</v>
+        <v>0.09025575419107425</v>
       </c>
       <c r="AI215">
-        <v>0.09025575419107425</v>
+        <v>0.369835</v>
       </c>
       <c r="AJ215">
-        <v>0.369835</v>
+        <v>0.252471</v>
       </c>
       <c r="AK215">
-        <v>0.252471</v>
-      </c>
-      <c r="AL215">
         <v>-0.0006950000000003342</v>
+      </c>
+      <c r="AL215" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:38">
@@ -23374,20 +23860,23 @@
       <c r="AF216">
         <v>21.5053904884945</v>
       </c>
+      <c r="AG216">
+        <v>0.09165079808209134</v>
+      </c>
       <c r="AH216">
-        <v>0.09165079808209134</v>
+        <v>0.1222635457170345</v>
       </c>
       <c r="AI216">
-        <v>0.1222635457170345</v>
+        <v>0.285185</v>
       </c>
       <c r="AJ216">
-        <v>0.285185</v>
+        <v>0.1443670000000001</v>
       </c>
       <c r="AK216">
-        <v>0.1443670000000001</v>
-      </c>
-      <c r="AL216">
         <v>-0.0006430000000001712</v>
+      </c>
+      <c r="AL216" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:38">
@@ -23484,20 +23973,23 @@
       <c r="AF217">
         <v>21.5078651205282</v>
       </c>
+      <c r="AG217">
+        <v>0.05035375620632591</v>
+      </c>
       <c r="AH217">
-        <v>0.05035375620632591</v>
+        <v>0.1825241351809133</v>
       </c>
       <c r="AI217">
-        <v>0.1825241351809133</v>
+        <v>0.403795</v>
       </c>
       <c r="AJ217">
-        <v>0.403795</v>
+        <v>0.4376569999999999</v>
       </c>
       <c r="AK217">
-        <v>0.4376569999999999</v>
-      </c>
-      <c r="AL217">
         <v>-0.0002569999999977313</v>
+      </c>
+      <c r="AL217" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:38">
@@ -23594,20 +24086,23 @@
       <c r="AF218">
         <v>12.8142247025193</v>
       </c>
+      <c r="AG218">
+        <v>0.5202316416106539</v>
+      </c>
       <c r="AH218">
-        <v>0.5202316416106539</v>
+        <v>0.03781157870499591</v>
       </c>
       <c r="AI218">
-        <v>0.03781157870499591</v>
+        <v>0.131308</v>
       </c>
       <c r="AJ218">
-        <v>0.131308</v>
+        <v>0.1451030000000001</v>
       </c>
       <c r="AK218">
-        <v>0.1451030000000001</v>
-      </c>
-      <c r="AL218">
         <v>0.0008069999999982258</v>
+      </c>
+      <c r="AL218" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:38">
@@ -23704,20 +24199,23 @@
       <c r="AF219">
         <v>12.6851464174451</v>
       </c>
+      <c r="AG219">
+        <v>0.5197897252299571</v>
+      </c>
       <c r="AH219">
-        <v>0.5197897252299571</v>
+        <v>0.02889384911771291</v>
       </c>
       <c r="AI219">
-        <v>0.02889384911771291</v>
+        <v>0.154761</v>
       </c>
       <c r="AJ219">
-        <v>0.154761</v>
+        <v>0.1300199999999999</v>
       </c>
       <c r="AK219">
-        <v>0.1300199999999999</v>
-      </c>
-      <c r="AL219">
         <v>0.001084999999999781</v>
+      </c>
+      <c r="AL219" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:38">
@@ -23814,20 +24312,23 @@
       <c r="AF220">
         <v>13.4436093989475</v>
       </c>
+      <c r="AG220">
+        <v>0.5267592575473012</v>
+      </c>
       <c r="AH220">
-        <v>0.5267592575473012</v>
+        <v>0.0197962558855542</v>
       </c>
       <c r="AI220">
-        <v>0.0197962558855542</v>
+        <v>0.155626</v>
       </c>
       <c r="AJ220">
-        <v>0.155626</v>
+        <v>0.1338009999999999</v>
       </c>
       <c r="AK220">
-        <v>0.1338009999999999</v>
-      </c>
-      <c r="AL220">
         <v>0.000537000000001342</v>
+      </c>
+      <c r="AL220" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:38">
@@ -23924,20 +24425,23 @@
       <c r="AF221">
         <v>13.1867976123542</v>
       </c>
+      <c r="AG221">
+        <v>0.5476271963469707</v>
+      </c>
       <c r="AH221">
-        <v>0.5476271963469707</v>
+        <v>0.01941437799357783</v>
       </c>
       <c r="AI221">
-        <v>0.01941437799357783</v>
+        <v>0.151922</v>
       </c>
       <c r="AJ221">
-        <v>0.151922</v>
+        <v>0.116667</v>
       </c>
       <c r="AK221">
-        <v>0.116667</v>
-      </c>
-      <c r="AL221">
         <v>-0.000174999999998704</v>
+      </c>
+      <c r="AL221" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:38">
@@ -24034,20 +24538,23 @@
       <c r="AF222">
         <v>11.8306567007958</v>
       </c>
+      <c r="AG222">
+        <v>0.5794281360619824</v>
+      </c>
       <c r="AH222">
-        <v>0.5794281360619824</v>
+        <v>0.01952621488989904</v>
       </c>
       <c r="AI222">
-        <v>0.01952621488989904</v>
+        <v>0.14398</v>
       </c>
       <c r="AJ222">
-        <v>0.14398</v>
+        <v>0.1208159999999999</v>
       </c>
       <c r="AK222">
-        <v>0.1208159999999999</v>
-      </c>
-      <c r="AL222">
         <v>0.0006740000000000634</v>
+      </c>
+      <c r="AL222" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:38">
@@ -24144,20 +24651,23 @@
       <c r="AF223">
         <v>11.5147047797974</v>
       </c>
+      <c r="AG223">
+        <v>0.328172976061916</v>
+      </c>
       <c r="AH223">
-        <v>0.328172976061916</v>
+        <v>0.02887880915540048</v>
       </c>
       <c r="AI223">
-        <v>0.02887880915540048</v>
+        <v>0.199085</v>
       </c>
       <c r="AJ223">
-        <v>0.199085</v>
+        <v>0.15008</v>
       </c>
       <c r="AK223">
-        <v>0.15008</v>
-      </c>
-      <c r="AL223">
         <v>-0.0004849999999994026</v>
+      </c>
+      <c r="AL223" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:38">
@@ -24254,20 +24764,23 @@
       <c r="AF224">
         <v>11.1554031256111</v>
       </c>
+      <c r="AG224">
+        <v>0.4460314594719466</v>
+      </c>
       <c r="AH224">
-        <v>0.4460314594719466</v>
+        <v>0.02291116911401116</v>
       </c>
       <c r="AI224">
-        <v>0.02291116911401116</v>
+        <v>0.176597</v>
       </c>
       <c r="AJ224">
-        <v>0.176597</v>
+        <v>0.1386660000000001</v>
       </c>
       <c r="AK224">
-        <v>0.1386660000000001</v>
-      </c>
-      <c r="AL224">
         <v>0.0005319999999997549</v>
+      </c>
+      <c r="AL224" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:38">
@@ -24358,20 +24871,23 @@
       <c r="AC225">
         <v>100.93</v>
       </c>
+      <c r="AG225">
+        <v>0.6199293258299089</v>
+      </c>
       <c r="AH225">
-        <v>0.6199293258299089</v>
+        <v>0.02177830731665444</v>
       </c>
       <c r="AI225">
-        <v>0.02177830731665444</v>
+        <v>0.06175099999999989</v>
       </c>
       <c r="AJ225">
-        <v>0.06175099999999989</v>
+        <v>0.05767299999999997</v>
       </c>
       <c r="AK225">
-        <v>0.05767299999999997</v>
-      </c>
-      <c r="AL225">
         <v>0.000589000000001505</v>
+      </c>
+      <c r="AL225" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:38">
@@ -24462,20 +24978,23 @@
       <c r="AC226">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG226">
+        <v>0.5752674105252583</v>
+      </c>
       <c r="AH226">
-        <v>0.5752674105252583</v>
+        <v>0.02217908096770543</v>
       </c>
       <c r="AI226">
-        <v>0.02217908096770543</v>
+        <v>0.113116</v>
       </c>
       <c r="AJ226">
-        <v>0.113116</v>
+        <v>0.267528</v>
       </c>
       <c r="AK226">
-        <v>0.267528</v>
-      </c>
-      <c r="AL226">
         <v>8.300000000005525E-05</v>
+      </c>
+      <c r="AL226" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:38">
@@ -24576,22 +25095,22 @@
         <v>19.679565807863</v>
       </c>
       <c r="AG227">
-        <v>200.7</v>
+        <v>0.2751526610515737</v>
       </c>
       <c r="AH227">
-        <v>0.2751526610515737</v>
+        <v>0.0232454807871235</v>
       </c>
       <c r="AI227">
-        <v>0.0232454807871235</v>
+        <v>0.257593</v>
       </c>
       <c r="AJ227">
-        <v>0.257593</v>
+        <v>0.290084</v>
       </c>
       <c r="AK227">
-        <v>0.290084</v>
-      </c>
-      <c r="AL227">
         <v>0.0005289999999984474</v>
+      </c>
+      <c r="AL227" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:38">
@@ -24692,22 +25211,22 @@
         <v>18.2765652206734</v>
       </c>
       <c r="AG228">
-        <v>199.9</v>
+        <v>0.3256002683712015</v>
       </c>
       <c r="AH228">
-        <v>0.3256002683712015</v>
+        <v>0.03297019320839905</v>
       </c>
       <c r="AI228">
-        <v>0.03297019320839905</v>
+        <v>0.1911619999999999</v>
       </c>
       <c r="AJ228">
-        <v>0.1911619999999999</v>
+        <v>0.2616649999999999</v>
       </c>
       <c r="AK228">
-        <v>0.2616649999999999</v>
-      </c>
-      <c r="AL228">
         <v>-0.0009150000000008873</v>
+      </c>
+      <c r="AL228" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:38">
@@ -24808,22 +25327,22 @@
         <v>17.8234033989894</v>
       </c>
       <c r="AG229">
-        <v>145</v>
+        <v>0.3144286352107324</v>
       </c>
       <c r="AH229">
-        <v>0.3144286352107324</v>
+        <v>0.005531466305832361</v>
       </c>
       <c r="AI229">
-        <v>0.005531466305832361</v>
+        <v>0.226419</v>
       </c>
       <c r="AJ229">
-        <v>0.226419</v>
+        <v>0.303399</v>
       </c>
       <c r="AK229">
-        <v>0.303399</v>
-      </c>
-      <c r="AL229">
         <v>-0.0001029999999992981</v>
+      </c>
+      <c r="AL229" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:38">
@@ -24924,22 +25443,22 @@
         <v>19.0379642707319</v>
       </c>
       <c r="AG230">
-        <v>147.2</v>
+        <v>0.3225366394704361</v>
       </c>
       <c r="AH230">
-        <v>0.3225366394704361</v>
+        <v>7.555426101250339E-07</v>
       </c>
       <c r="AI230">
-        <v>7.555426101250339E-07</v>
+        <v>0.2723260000000001</v>
       </c>
       <c r="AJ230">
-        <v>0.2723260000000001</v>
+        <v>0.282706</v>
       </c>
       <c r="AK230">
-        <v>0.282706</v>
-      </c>
-      <c r="AL230">
         <v>-0.0005000000000006111</v>
+      </c>
+      <c r="AL230" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:38">
@@ -25040,22 +25559,22 @@
         <v>19.5290026661565</v>
       </c>
       <c r="AG231">
-        <v>128.7</v>
+        <v>0.3042837054632178</v>
       </c>
       <c r="AH231">
-        <v>0.3042837054632178</v>
+        <v>0.0001748521211360533</v>
       </c>
       <c r="AI231">
-        <v>0.0001748521211360533</v>
+        <v>0.3299789999999999</v>
       </c>
       <c r="AJ231">
-        <v>0.3299789999999999</v>
+        <v>0.3529589999999999</v>
       </c>
       <c r="AK231">
-        <v>0.3529589999999999</v>
-      </c>
-      <c r="AL231">
         <v>-0.0008590000000001652</v>
+      </c>
+      <c r="AL231" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:38">
@@ -25156,22 +25675,22 @@
         <v>18.0501223065786</v>
       </c>
       <c r="AG232">
-        <v>173.4</v>
+        <v>0.1547306627728198</v>
       </c>
       <c r="AH232">
-        <v>0.1547306627728198</v>
+        <v>1.558633768261944E-06</v>
       </c>
       <c r="AI232">
-        <v>1.558633768261944E-06</v>
+        <v>0.425968</v>
       </c>
       <c r="AJ232">
-        <v>0.425968</v>
+        <v>0.466083</v>
       </c>
       <c r="AK232">
-        <v>0.466083</v>
-      </c>
-      <c r="AL232">
         <v>-0.0005090000000009809</v>
+      </c>
+      <c r="AL232" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:38">
@@ -25272,22 +25791,22 @@
         <v>20.6771966687553</v>
       </c>
       <c r="AG233">
-        <v>165.4</v>
+        <v>0.3208627151578587</v>
       </c>
       <c r="AH233">
-        <v>0.3208627151578587</v>
+        <v>7.704001022449429E-07</v>
       </c>
       <c r="AI233">
-        <v>7.704001022449429E-07</v>
+        <v>0.263538</v>
       </c>
       <c r="AJ233">
-        <v>0.263538</v>
+        <v>0.3122760000000001</v>
       </c>
       <c r="AK233">
-        <v>0.3122760000000001</v>
-      </c>
-      <c r="AL233">
         <v>-0.0004399999999993298</v>
+      </c>
+      <c r="AL233" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:38">
@@ -25379,22 +25898,22 @@
         <v>100.93</v>
       </c>
       <c r="AG234">
-        <v>208.9</v>
+        <v>0.3996484754000921</v>
       </c>
       <c r="AH234">
-        <v>0.3996484754000921</v>
+        <v>0.03247080052512659</v>
       </c>
       <c r="AI234">
-        <v>0.03247080052512659</v>
+        <v>0.2958780000000001</v>
       </c>
       <c r="AJ234">
-        <v>0.2958780000000001</v>
+        <v>0.159267</v>
       </c>
       <c r="AK234">
-        <v>0.159267</v>
-      </c>
-      <c r="AL234">
         <v>0.0009209999999999496</v>
+      </c>
+      <c r="AL234" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:38">
@@ -25486,22 +26005,22 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AG235">
-        <v>183.9</v>
+        <v>0.3281661013348033</v>
       </c>
       <c r="AH235">
-        <v>0.3281661013348033</v>
+        <v>0.02749600258255697</v>
       </c>
       <c r="AI235">
-        <v>0.02749600258255697</v>
+        <v>0.2792910000000001</v>
       </c>
       <c r="AJ235">
-        <v>0.2792910000000001</v>
+        <v>0.459943</v>
       </c>
       <c r="AK235">
-        <v>0.459943</v>
-      </c>
-      <c r="AL235">
         <v>0.0002879999999993998</v>
+      </c>
+      <c r="AL235" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:38">
@@ -25568,14 +26087,17 @@
       <c r="AC236">
         <v>52.32</v>
       </c>
+      <c r="AI236">
+        <v>0.1805310000000001</v>
+      </c>
       <c r="AJ236">
-        <v>0.1805310000000001</v>
+        <v>0.08796800000000005</v>
       </c>
       <c r="AK236">
-        <v>0.08796800000000005</v>
-      </c>
-      <c r="AL236">
         <v>-5.300000000119098E-05</v>
+      </c>
+      <c r="AL236" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:38">
@@ -25642,14 +26164,17 @@
       <c r="AC237">
         <v>43.64</v>
       </c>
+      <c r="AI237">
+        <v>0.156406</v>
+      </c>
       <c r="AJ237">
-        <v>0.156406</v>
+        <v>0.06642799999999993</v>
       </c>
       <c r="AK237">
-        <v>0.06642799999999993</v>
-      </c>
-      <c r="AL237">
         <v>-0.0003139999999994814</v>
+      </c>
+      <c r="AL237" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:38">
@@ -25716,14 +26241,17 @@
       <c r="AC238">
         <v>54.13</v>
       </c>
+      <c r="AI238">
+        <v>0.148888</v>
+      </c>
       <c r="AJ238">
-        <v>0.148888</v>
+        <v>0.05840400000000001</v>
       </c>
       <c r="AK238">
-        <v>0.05840400000000001</v>
-      </c>
-      <c r="AL238">
         <v>0.001024000000001024</v>
+      </c>
+      <c r="AL238" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:38">
@@ -25796,14 +26324,17 @@
       <c r="AC239">
         <v>71.34</v>
       </c>
+      <c r="AI239">
+        <v>0.1425739999999999</v>
+      </c>
       <c r="AJ239">
-        <v>0.1425739999999999</v>
+        <v>0.04405700000000001</v>
       </c>
       <c r="AK239">
-        <v>0.04405700000000001</v>
-      </c>
-      <c r="AL239">
         <v>0.0007120000000000459</v>
+      </c>
+      <c r="AL239" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:38">
@@ -25876,14 +26407,17 @@
       <c r="AC240">
         <v>64.3</v>
       </c>
+      <c r="AI240">
+        <v>0.1522709999999999</v>
+      </c>
       <c r="AJ240">
-        <v>0.1522709999999999</v>
+        <v>0.05345299999999997</v>
       </c>
       <c r="AK240">
-        <v>0.05345299999999997</v>
-      </c>
-      <c r="AL240">
         <v>-0.0005270000000017205</v>
+      </c>
+      <c r="AL240" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:38">
@@ -25956,14 +26490,17 @@
       <c r="AC241">
         <v>41.96</v>
       </c>
+      <c r="AI241">
+        <v>0.179935</v>
+      </c>
       <c r="AJ241">
-        <v>0.179935</v>
+        <v>0.08044800000000002</v>
       </c>
       <c r="AK241">
-        <v>0.08044800000000002</v>
-      </c>
-      <c r="AL241">
         <v>-0.0009690000000013299</v>
+      </c>
+      <c r="AL241" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:38">
@@ -26030,14 +26567,17 @@
       <c r="AC242">
         <v>70.86</v>
       </c>
+      <c r="AI242">
+        <v>0.157776</v>
+      </c>
       <c r="AJ242">
-        <v>0.157776</v>
+        <v>0.06243999999999994</v>
       </c>
       <c r="AK242">
-        <v>0.06243999999999994</v>
-      </c>
-      <c r="AL242">
         <v>5.800000000277805E-05</v>
+      </c>
+      <c r="AL242" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:38">
@@ -26104,14 +26644,17 @@
       <c r="AC243">
         <v>100.93</v>
       </c>
+      <c r="AI243">
+        <v>0.1662939999999999</v>
+      </c>
       <c r="AJ243">
-        <v>0.1662939999999999</v>
+        <v>0.185689</v>
       </c>
       <c r="AK243">
-        <v>0.185689</v>
-      </c>
-      <c r="AL243">
         <v>0.0003590000000031068</v>
+      </c>
+      <c r="AL243" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:38">
@@ -26178,14 +26721,17 @@
       <c r="AC244">
         <v>82.48999999999999</v>
       </c>
+      <c r="AI244">
+        <v>0.15856</v>
+      </c>
       <c r="AJ244">
-        <v>0.15856</v>
+        <v>0.281907</v>
       </c>
       <c r="AK244">
-        <v>0.281907</v>
-      </c>
-      <c r="AL244">
         <v>0.0001489999999968461</v>
+      </c>
+      <c r="AL244" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:38">
@@ -26282,20 +26828,23 @@
       <c r="AF245">
         <v>17.358483664503</v>
       </c>
+      <c r="AG245">
+        <v>0.03535054451848996</v>
+      </c>
       <c r="AH245">
-        <v>0.03535054451848996</v>
+        <v>3.444002225606987E-05</v>
       </c>
       <c r="AI245">
-        <v>3.444002225606987E-05</v>
+        <v>0.488876</v>
       </c>
       <c r="AJ245">
-        <v>0.488876</v>
+        <v>0.5545609999999999</v>
       </c>
       <c r="AK245">
-        <v>0.5545609999999999</v>
-      </c>
-      <c r="AL245">
         <v>-0.0002650000000024022</v>
+      </c>
+      <c r="AL245" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:38">
@@ -26392,20 +26941,23 @@
       <c r="AF246">
         <v>16.8648796628618</v>
       </c>
+      <c r="AG246">
+        <v>0.05849336057717551</v>
+      </c>
       <c r="AH246">
-        <v>0.05849336057717551</v>
+        <v>1.780311090793937E-05</v>
       </c>
       <c r="AI246">
-        <v>1.780311090793937E-05</v>
+        <v>0.435701</v>
       </c>
       <c r="AJ246">
-        <v>0.435701</v>
+        <v>0.430381</v>
       </c>
       <c r="AK246">
-        <v>0.430381</v>
-      </c>
-      <c r="AL246">
         <v>0.0005230000000011614</v>
+      </c>
+      <c r="AL246" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:38">
@@ -26502,19 +27054,22 @@
       <c r="AF247">
         <v>17.4431333716598</v>
       </c>
+      <c r="AG247">
+        <v>0.1174756752080819</v>
+      </c>
       <c r="AH247">
-        <v>0.1174756752080819</v>
+        <v>1.55027537936132E-05</v>
       </c>
       <c r="AI247">
-        <v>1.55027537936132E-05</v>
+        <v>0.31508</v>
       </c>
       <c r="AJ247">
-        <v>0.31508</v>
+        <v>0.306879</v>
       </c>
       <c r="AK247">
-        <v>0.306879</v>
-      </c>
-      <c r="AL247">
+        <v>0</v>
+      </c>
+      <c r="AL247" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26612,20 +27167,23 @@
       <c r="AF248">
         <v>17.3317797902031</v>
       </c>
+      <c r="AG248">
+        <v>0.1425405054541917</v>
+      </c>
       <c r="AH248">
-        <v>0.1425405054541917</v>
+        <v>1.352677181850324E-05</v>
       </c>
       <c r="AI248">
-        <v>1.352677181850324E-05</v>
+        <v>0.2967329999999999</v>
       </c>
       <c r="AJ248">
-        <v>0.2967329999999999</v>
+        <v>0.234596</v>
       </c>
       <c r="AK248">
-        <v>0.234596</v>
-      </c>
-      <c r="AL248">
         <v>-0.0002490000000001658</v>
+      </c>
+      <c r="AL248" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:38">
@@ -26722,20 +27280,23 @@
       <c r="AF249">
         <v>17.5461211473444</v>
       </c>
+      <c r="AG249">
+        <v>0.1502305633689002</v>
+      </c>
       <c r="AH249">
-        <v>0.1502305633689002</v>
+        <v>2.808476703038831E-05</v>
       </c>
       <c r="AI249">
-        <v>2.808476703038831E-05</v>
+        <v>0.3232060000000001</v>
       </c>
       <c r="AJ249">
-        <v>0.3232060000000001</v>
+        <v>0.278634</v>
       </c>
       <c r="AK249">
-        <v>0.278634</v>
-      </c>
-      <c r="AL249">
         <v>-0.0002460000000006346</v>
+      </c>
+      <c r="AL249" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:38">
@@ -26832,19 +27393,22 @@
       <c r="AF250">
         <v>16.7319714533199</v>
       </c>
+      <c r="AG250">
+        <v>0.09492718247131303</v>
+      </c>
       <c r="AH250">
-        <v>0.09492718247131303</v>
+        <v>5.52342335677627E-05</v>
       </c>
       <c r="AI250">
-        <v>5.52342335677627E-05</v>
+        <v>0.397674</v>
       </c>
       <c r="AJ250">
-        <v>0.397674</v>
+        <v>0.355267</v>
       </c>
       <c r="AK250">
-        <v>0.355267</v>
-      </c>
-      <c r="AL250">
+        <v>0</v>
+      </c>
+      <c r="AL250" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26942,19 +27506,22 @@
       <c r="AF251">
         <v>16.8868520553405</v>
       </c>
+      <c r="AG251">
+        <v>0.2331577763995551</v>
+      </c>
       <c r="AH251">
-        <v>0.2331577763995551</v>
+        <v>1.729407467115461E-05</v>
       </c>
       <c r="AI251">
-        <v>1.729407467115461E-05</v>
+        <v>0.199298</v>
       </c>
       <c r="AJ251">
-        <v>0.199298</v>
+        <v>0.2373160000000001</v>
       </c>
       <c r="AK251">
-        <v>0.2373160000000001</v>
-      </c>
-      <c r="AL251">
+        <v>0</v>
+      </c>
+      <c r="AL251" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27052,20 +27619,23 @@
       <c r="AF252">
         <v>17.3957386518946</v>
       </c>
+      <c r="AG252">
+        <v>0.2503260212487441</v>
+      </c>
       <c r="AH252">
-        <v>0.2503260212487441</v>
+        <v>2.654175182525783E-05</v>
       </c>
       <c r="AI252">
-        <v>2.654175182525783E-05</v>
+        <v>0.1302729999999999</v>
       </c>
       <c r="AJ252">
-        <v>0.1302729999999999</v>
+        <v>0.1283880000000001</v>
       </c>
       <c r="AK252">
-        <v>0.1283880000000001</v>
-      </c>
-      <c r="AL252">
         <v>-0.0001069999999998572</v>
+      </c>
+      <c r="AL252" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:38">
@@ -27162,20 +27732,23 @@
       <c r="AF253">
         <v>17.5729662059172</v>
       </c>
+      <c r="AG253">
+        <v>0.2179783652738688</v>
+      </c>
       <c r="AH253">
-        <v>0.2179783652738688</v>
+        <v>0.1274171590392364</v>
       </c>
       <c r="AI253">
-        <v>0.1274171590392364</v>
+        <v>0.04636311423865269</v>
       </c>
       <c r="AJ253">
-        <v>0.04636311423865269</v>
+        <v>0.433995749828384</v>
       </c>
       <c r="AK253">
-        <v>0.433995749828384</v>
-      </c>
-      <c r="AL253">
         <v>0.000309000000001447</v>
+      </c>
+      <c r="AL253" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:38">
@@ -27275,20 +27848,23 @@
       <c r="AF254">
         <v>20.8150431413365</v>
       </c>
+      <c r="AG254">
+        <v>0.1661485828646336</v>
+      </c>
       <c r="AH254">
-        <v>0.1661485828646336</v>
+        <v>0.1570384589918767</v>
       </c>
       <c r="AI254">
-        <v>0.1570384589918767</v>
+        <v>0.1330570000000001</v>
       </c>
       <c r="AJ254">
-        <v>0.1330570000000001</v>
+        <v>0.18354</v>
       </c>
       <c r="AK254">
-        <v>0.18354</v>
-      </c>
-      <c r="AL254">
         <v>-0.0004759999999990328</v>
+      </c>
+      <c r="AL254" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:38">
@@ -27388,20 +27964,23 @@
       <c r="AF255">
         <v>23.6888663993406</v>
       </c>
+      <c r="AG255">
+        <v>0.1903584250202927</v>
+      </c>
       <c r="AH255">
-        <v>0.1903584250202927</v>
+        <v>0.1626838800014739</v>
       </c>
       <c r="AI255">
-        <v>0.1626838800014739</v>
+        <v>0.1697759999999999</v>
       </c>
       <c r="AJ255">
-        <v>0.1697759999999999</v>
+        <v>0.1355970000000001</v>
       </c>
       <c r="AK255">
-        <v>0.1355970000000001</v>
-      </c>
-      <c r="AL255">
         <v>0.0001560000000004891</v>
+      </c>
+      <c r="AL255" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:38">
@@ -27501,20 +28080,23 @@
       <c r="AF256">
         <v>25.0974253686368</v>
       </c>
+      <c r="AG256">
+        <v>0.1734023782230545</v>
+      </c>
       <c r="AH256">
-        <v>0.1734023782230545</v>
+        <v>0.1085810298561201</v>
       </c>
       <c r="AI256">
-        <v>0.1085810298561201</v>
+        <v>0.1705690000000001</v>
       </c>
       <c r="AJ256">
-        <v>0.1705690000000001</v>
+        <v>0.130138</v>
       </c>
       <c r="AK256">
-        <v>0.130138</v>
-      </c>
-      <c r="AL256">
         <v>0.0007680000000007681</v>
+      </c>
+      <c r="AL256" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:38">
@@ -27614,20 +28196,23 @@
       <c r="AF257">
         <v>24.9488391040262</v>
       </c>
+      <c r="AG257">
+        <v>0.1876659072047775</v>
+      </c>
       <c r="AH257">
-        <v>0.1876659072047775</v>
+        <v>0.1569067129441017</v>
       </c>
       <c r="AI257">
-        <v>0.1569067129441017</v>
+        <v>0.2017850000000001</v>
       </c>
       <c r="AJ257">
-        <v>0.2017850000000001</v>
+        <v>0.153987</v>
       </c>
       <c r="AK257">
-        <v>0.153987</v>
-      </c>
-      <c r="AL257">
         <v>0.0004249999999998977</v>
+      </c>
+      <c r="AL257" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:38">
@@ -27727,20 +28312,23 @@
       <c r="AF258">
         <v>24.1024004190298</v>
       </c>
+      <c r="AG258">
+        <v>0.2311784088477672</v>
+      </c>
       <c r="AH258">
-        <v>0.2311784088477672</v>
+        <v>0.1676909011547341</v>
       </c>
       <c r="AI258">
-        <v>0.1676909011547341</v>
+        <v>0.152454</v>
       </c>
       <c r="AJ258">
-        <v>0.152454</v>
+        <v>0.151245</v>
       </c>
       <c r="AK258">
-        <v>0.151245</v>
-      </c>
-      <c r="AL258">
         <v>-0.0008090000000002817</v>
+      </c>
+      <c r="AL258" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:38">
@@ -27840,20 +28428,23 @@
       <c r="AF259">
         <v>23.5586663397695</v>
       </c>
+      <c r="AG259">
+        <v>0.1625644623022341</v>
+      </c>
       <c r="AH259">
-        <v>0.1625644623022341</v>
+        <v>0.08336284738311188</v>
       </c>
       <c r="AI259">
-        <v>0.08336284738311188</v>
+        <v>0.219016</v>
       </c>
       <c r="AJ259">
-        <v>0.219016</v>
+        <v>0.17552</v>
       </c>
       <c r="AK259">
-        <v>0.17552</v>
-      </c>
-      <c r="AL259">
         <v>-0.0007270000000012544</v>
+      </c>
+      <c r="AL259" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:38">
@@ -27953,20 +28544,23 @@
       <c r="AF260">
         <v>28.5747339991475</v>
       </c>
+      <c r="AG260">
+        <v>0.2386546551606226</v>
+      </c>
       <c r="AH260">
-        <v>0.2386546551606226</v>
+        <v>0.1283615023389027</v>
       </c>
       <c r="AI260">
-        <v>0.1283615023389027</v>
+        <v>0.2118349999999999</v>
       </c>
       <c r="AJ260">
-        <v>0.2118349999999999</v>
+        <v>0.1688580000000001</v>
       </c>
       <c r="AK260">
-        <v>0.1688580000000001</v>
-      </c>
-      <c r="AL260">
         <v>0.0001159999999984507</v>
+      </c>
+      <c r="AL260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:38">
@@ -28066,20 +28660,23 @@
       <c r="AF261">
         <v>28.191923971419</v>
       </c>
+      <c r="AG261">
+        <v>0.3452747394036751</v>
+      </c>
       <c r="AH261">
-        <v>0.3452747394036751</v>
+        <v>0.1630451783077943</v>
       </c>
       <c r="AI261">
-        <v>0.1630451783077943</v>
+        <v>0.06659799999999994</v>
       </c>
       <c r="AJ261">
-        <v>0.06659799999999994</v>
+        <v>0.0594610000000001</v>
       </c>
       <c r="AK261">
-        <v>0.0594610000000001</v>
-      </c>
-      <c r="AL261">
         <v>0.0008259999999964407</v>
+      </c>
+      <c r="AL261" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:38">
@@ -28179,20 +28776,23 @@
       <c r="AF262">
         <v>26.0511443955415</v>
       </c>
+      <c r="AG262">
+        <v>0.290760709544443</v>
+      </c>
       <c r="AH262">
-        <v>0.290760709544443</v>
+        <v>0.2130923956548238</v>
       </c>
       <c r="AI262">
-        <v>0.2130923956548238</v>
+        <v>0.212802</v>
       </c>
       <c r="AJ262">
-        <v>0.212802</v>
+        <v>0.3595459999999999</v>
       </c>
       <c r="AK262">
-        <v>0.3595459999999999</v>
-      </c>
-      <c r="AL262">
         <v>-9.999999999621423E-06</v>
+      </c>
+      <c r="AL262" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:38">
@@ -28265,14 +28865,17 @@
       <c r="AC263">
         <v>52.32</v>
       </c>
+      <c r="AI263">
+        <v>0.6916370000000001</v>
+      </c>
       <c r="AJ263">
-        <v>0.6916370000000001</v>
+        <v>0.2262380000000001</v>
       </c>
       <c r="AK263">
-        <v>0.2262380000000001</v>
-      </c>
-      <c r="AL263">
         <v>0.000397000000001313</v>
+      </c>
+      <c r="AL263" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:38">
@@ -28345,14 +28948,17 @@
       <c r="AC264">
         <v>43.64</v>
       </c>
+      <c r="AI264">
+        <v>0.453898</v>
+      </c>
       <c r="AJ264">
-        <v>0.453898</v>
+        <v>0.335762</v>
       </c>
       <c r="AK264">
-        <v>0.335762</v>
-      </c>
-      <c r="AL264">
         <v>-0.0001309999999996592</v>
+      </c>
+      <c r="AL264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:38">
@@ -28425,14 +29031,17 @@
       <c r="AC265">
         <v>54.13</v>
       </c>
+      <c r="AI265">
+        <v>0.2438069999999999</v>
+      </c>
       <c r="AJ265">
-        <v>0.2438069999999999</v>
+        <v>0.2033940000000001</v>
       </c>
       <c r="AK265">
-        <v>0.2033940000000001</v>
-      </c>
-      <c r="AL265">
         <v>0.000384000000000384</v>
+      </c>
+      <c r="AL265" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:38">
@@ -28505,14 +29114,17 @@
       <c r="AC266">
         <v>71.34</v>
       </c>
+      <c r="AI266">
+        <v>0.246162</v>
+      </c>
       <c r="AJ266">
-        <v>0.246162</v>
+        <v>0.209789</v>
       </c>
       <c r="AK266">
-        <v>0.209789</v>
-      </c>
-      <c r="AL266">
         <v>-0.0004989999999995831</v>
+      </c>
+      <c r="AL266" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:38">
@@ -28585,14 +29197,17 @@
       <c r="AC267">
         <v>64.3</v>
       </c>
+      <c r="AI267">
+        <v>0.2644859999999999</v>
+      </c>
       <c r="AJ267">
-        <v>0.2644859999999999</v>
+        <v>0.210959</v>
       </c>
       <c r="AK267">
-        <v>0.210959</v>
-      </c>
-      <c r="AL267">
         <v>-0.0001230000000003173</v>
+      </c>
+      <c r="AL267" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:38">
@@ -28665,14 +29280,17 @@
       <c r="AC268">
         <v>41.96</v>
       </c>
+      <c r="AI268">
+        <v>0.43801</v>
+      </c>
       <c r="AJ268">
-        <v>0.43801</v>
+        <v>0.38764</v>
       </c>
       <c r="AK268">
-        <v>0.38764</v>
-      </c>
-      <c r="AL268">
         <v>-0.0001210000000000377</v>
+      </c>
+      <c r="AL268" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:38">
@@ -28739,14 +29357,17 @@
       <c r="AC269">
         <v>70.86</v>
       </c>
+      <c r="AI269">
+        <v>0.175181</v>
+      </c>
       <c r="AJ269">
-        <v>0.175181</v>
+        <v>0.1388630000000001</v>
       </c>
       <c r="AK269">
-        <v>0.1388630000000001</v>
-      </c>
-      <c r="AL269">
         <v>0.000116000000000227</v>
+      </c>
+      <c r="AL269" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:38">
@@ -28813,14 +29434,17 @@
       <c r="AC270">
         <v>100.93</v>
       </c>
+      <c r="AI270">
+        <v>0.04551400000000005</v>
+      </c>
       <c r="AJ270">
-        <v>0.04551400000000005</v>
+        <v>-0.188594</v>
       </c>
       <c r="AK270">
-        <v>-0.188594</v>
-      </c>
-      <c r="AL270">
         <v>0.0004289999999986804</v>
+      </c>
+      <c r="AL270" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:38">
@@ -28887,14 +29511,17 @@
       <c r="AC271">
         <v>82.48999999999999</v>
       </c>
+      <c r="AI271">
+        <v>0.2947609999999999</v>
+      </c>
       <c r="AJ271">
-        <v>0.2947609999999999</v>
+        <v>0.325188</v>
       </c>
       <c r="AK271">
-        <v>0.325188</v>
-      </c>
-      <c r="AL271">
         <v>-0.0003089999999996706</v>
+      </c>
+      <c r="AL271" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="272" spans="1:38">
@@ -28991,20 +29618,23 @@
       <c r="AF272">
         <v>35.8629396068095</v>
       </c>
+      <c r="AG272">
+        <v>2.028157475950026</v>
+      </c>
       <c r="AH272">
-        <v>2.028157475950026</v>
+        <v>0.3805981439602975</v>
       </c>
       <c r="AI272">
-        <v>0.3805981439602975</v>
+        <v>-0.407962</v>
       </c>
       <c r="AJ272">
-        <v>-0.407962</v>
+        <v>-0.391595</v>
       </c>
       <c r="AK272">
-        <v>-0.391595</v>
-      </c>
-      <c r="AL272">
         <v>-6.600000000034356E-05</v>
+      </c>
+      <c r="AL272" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:38">
@@ -29101,20 +29731,23 @@
       <c r="AF273">
         <v>31.2390699061462</v>
       </c>
+      <c r="AG273">
+        <v>1.616877699388077</v>
+      </c>
       <c r="AH273">
-        <v>1.616877699388077</v>
+        <v>0.3234984773343716</v>
       </c>
       <c r="AI273">
-        <v>0.3234984773343716</v>
+        <v>-0.435322</v>
       </c>
       <c r="AJ273">
-        <v>-0.435322</v>
+        <v>-0.214619</v>
       </c>
       <c r="AK273">
-        <v>-0.214619</v>
-      </c>
-      <c r="AL273">
         <v>0.001142999999999006</v>
+      </c>
+      <c r="AL273" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:38">
@@ -29211,20 +29844,23 @@
       <c r="AF274">
         <v>28.7268899879201</v>
       </c>
+      <c r="AG274">
+        <v>1.578568247367318</v>
+      </c>
       <c r="AH274">
-        <v>1.578568247367318</v>
+        <v>0.3161968289068067</v>
       </c>
       <c r="AI274">
-        <v>0.3161968289068067</v>
+        <v>-0.445091</v>
       </c>
       <c r="AJ274">
-        <v>-0.445091</v>
+        <v>-0.17516</v>
       </c>
       <c r="AK274">
-        <v>-0.17516</v>
-      </c>
-      <c r="AL274">
         <v>-0.00032000000000032</v>
+      </c>
+      <c r="AL274" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:38">
@@ -29321,20 +29957,23 @@
       <c r="AF275">
         <v>29.5653403216796</v>
       </c>
+      <c r="AG275">
+        <v>1.604963512678892</v>
+      </c>
       <c r="AH275">
-        <v>1.604963512678892</v>
+        <v>0.3418478040105268</v>
       </c>
       <c r="AI275">
-        <v>0.3418478040105268</v>
+        <v>-0.4599009999999999</v>
       </c>
       <c r="AJ275">
-        <v>-0.4599009999999999</v>
+        <v>-0.2399720000000001</v>
       </c>
       <c r="AK275">
-        <v>-0.2399720000000001</v>
-      </c>
-      <c r="AL275">
         <v>0.0003120000000009782</v>
+      </c>
+      <c r="AL275" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:38">
@@ -29431,20 +30070,23 @@
       <c r="AF276">
         <v>24.2635768758849</v>
       </c>
+      <c r="AG276">
+        <v>1.361651655999269</v>
+      </c>
       <c r="AH276">
-        <v>1.361651655999269</v>
+        <v>0.2610359888168643</v>
       </c>
       <c r="AI276">
-        <v>0.2610359888168643</v>
+        <v>-0.45081</v>
       </c>
       <c r="AJ276">
-        <v>-0.45081</v>
+        <v>-0.1837190000000001</v>
       </c>
       <c r="AK276">
-        <v>-0.1837190000000001</v>
-      </c>
-      <c r="AL276">
         <v>-0.000460000000000349</v>
+      </c>
+      <c r="AL276" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:38">
@@ -29535,20 +30177,23 @@
       <c r="AC277">
         <v>41.96</v>
       </c>
+      <c r="AG277">
+        <v>1.310573340877859</v>
+      </c>
       <c r="AH277">
-        <v>1.310573340877859</v>
+        <v>0.3069733596216745</v>
       </c>
       <c r="AI277">
-        <v>0.3069733596216745</v>
+        <v>-0.373044</v>
       </c>
       <c r="AJ277">
-        <v>-0.373044</v>
+        <v>0.05163100000000004</v>
       </c>
       <c r="AK277">
-        <v>0.05163100000000004</v>
-      </c>
-      <c r="AL277">
         <v>-0.0001510000000006784</v>
+      </c>
+      <c r="AL277" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:38">
@@ -29639,20 +30284,23 @@
       <c r="AC278">
         <v>70.86</v>
       </c>
+      <c r="AG278">
+        <v>1.298569481201671</v>
+      </c>
       <c r="AH278">
-        <v>1.298569481201671</v>
+        <v>0.3373121770717954</v>
       </c>
       <c r="AI278">
-        <v>0.3373121770717954</v>
+        <v>-0.380457</v>
       </c>
       <c r="AJ278">
-        <v>-0.380457</v>
+        <v>-0.176928</v>
       </c>
       <c r="AK278">
-        <v>-0.176928</v>
-      </c>
-      <c r="AL278">
         <v>-0.0002890000000004278</v>
+      </c>
+      <c r="AL278" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:38">
@@ -29743,20 +30391,23 @@
       <c r="AC279">
         <v>100.93</v>
       </c>
+      <c r="AG279">
+        <v>1.418571512548388</v>
+      </c>
       <c r="AH279">
-        <v>1.418571512548388</v>
+        <v>0.374172012507753</v>
       </c>
       <c r="AI279">
-        <v>0.374172012507753</v>
+        <v>-0.417647</v>
       </c>
       <c r="AJ279">
-        <v>-0.417647</v>
+        <v>-0.443288</v>
       </c>
       <c r="AK279">
-        <v>-0.443288</v>
-      </c>
-      <c r="AL279">
         <v>-0.0004010000000000957</v>
+      </c>
+      <c r="AL279" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:38">
@@ -29847,20 +30498,23 @@
       <c r="AC280">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG280">
+        <v>1.211500267054534</v>
+      </c>
       <c r="AH280">
-        <v>1.211500267054534</v>
+        <v>0.2883044699808264</v>
       </c>
       <c r="AI280">
-        <v>0.2883044699808264</v>
+        <v>-0.3005009999999999</v>
       </c>
       <c r="AJ280">
-        <v>-0.3005009999999999</v>
+        <v>-0.06514900000000001</v>
       </c>
       <c r="AK280">
-        <v>-0.06514900000000001</v>
-      </c>
-      <c r="AL280">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AL280" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:38">
@@ -29957,20 +30611,23 @@
       <c r="AF281">
         <v>28.1236212798537</v>
       </c>
+      <c r="AG281">
+        <v>0.00880014618397759</v>
+      </c>
       <c r="AH281">
-        <v>0.00880014618397759</v>
+        <v>0</v>
       </c>
       <c r="AI281">
-        <v>0</v>
+        <v>1.088807</v>
       </c>
       <c r="AJ281">
-        <v>1.088807</v>
+        <v>0.926332</v>
       </c>
       <c r="AK281">
-        <v>0.926332</v>
-      </c>
-      <c r="AL281">
         <v>37.75129687252389</v>
+      </c>
+      <c r="AL281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:38">
@@ -30067,20 +30724,23 @@
       <c r="AF282">
         <v>33.1100434313663</v>
       </c>
+      <c r="AG282">
+        <v>0.01876950507112284</v>
+      </c>
       <c r="AH282">
-        <v>0.01876950507112284</v>
+        <v>0</v>
       </c>
       <c r="AI282">
-        <v>0</v>
+        <v>1.06037</v>
       </c>
       <c r="AJ282">
-        <v>1.06037</v>
+        <v>0.86624</v>
       </c>
       <c r="AK282">
-        <v>0.86624</v>
-      </c>
-      <c r="AL282">
         <v>29.532947</v>
+      </c>
+      <c r="AL282" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:38">
@@ -30177,20 +30837,23 @@
       <c r="AF283">
         <v>29.7075109246204</v>
       </c>
+      <c r="AG283">
+        <v>0.02061962035927803</v>
+      </c>
       <c r="AH283">
-        <v>0.02061962035927803</v>
+        <v>0</v>
       </c>
       <c r="AI283">
-        <v>0</v>
+        <v>1.167784</v>
       </c>
       <c r="AJ283">
-        <v>1.167784</v>
+        <v>0.8679480000000001</v>
       </c>
       <c r="AK283">
-        <v>0.8679480000000001</v>
-      </c>
-      <c r="AL283">
         <v>22.504141</v>
+      </c>
+      <c r="AL283" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:38">
@@ -30287,20 +30950,23 @@
       <c r="AF284">
         <v>31.3533848442693</v>
       </c>
+      <c r="AG284">
+        <v>0.09579150785841301</v>
+      </c>
       <c r="AH284">
-        <v>0.09579150785841301</v>
+        <v>0</v>
       </c>
       <c r="AI284">
-        <v>0</v>
+        <v>1.168922</v>
       </c>
       <c r="AJ284">
-        <v>1.168922</v>
+        <v>0.6064890000000001</v>
       </c>
       <c r="AK284">
-        <v>0.6064890000000001</v>
-      </c>
-      <c r="AL284">
         <v>31.314246</v>
+      </c>
+      <c r="AL284" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:38">
@@ -30397,20 +31063,23 @@
       <c r="AF285">
         <v>30.6396644583495</v>
       </c>
+      <c r="AG285">
+        <v>0.1891882650418396</v>
+      </c>
       <c r="AH285">
-        <v>0.1891882650418396</v>
+        <v>0</v>
       </c>
       <c r="AI285">
-        <v>0</v>
+        <v>1.015053</v>
       </c>
       <c r="AJ285">
-        <v>1.015053</v>
+        <v>0.466685</v>
       </c>
       <c r="AK285">
-        <v>0.466685</v>
-      </c>
-      <c r="AL285">
         <v>32.600897</v>
+      </c>
+      <c r="AL285" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:38">
@@ -30507,20 +31176,23 @@
       <c r="AF286">
         <v>30.8483157882517</v>
       </c>
+      <c r="AG286">
+        <v>0.1325931364910255</v>
+      </c>
       <c r="AH286">
-        <v>0.1325931364910255</v>
+        <v>0</v>
       </c>
       <c r="AI286">
-        <v>0</v>
+        <v>0.9599989999999999</v>
       </c>
       <c r="AJ286">
-        <v>0.9599989999999999</v>
+        <v>0.504648</v>
       </c>
       <c r="AK286">
-        <v>0.504648</v>
-      </c>
-      <c r="AL286">
         <v>22.407505</v>
+      </c>
+      <c r="AL286" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:38">
@@ -30617,20 +31289,23 @@
       <c r="AF287">
         <v>29.1017733541657</v>
       </c>
+      <c r="AG287">
+        <v>0.3647370911312941</v>
+      </c>
       <c r="AH287">
-        <v>0.3647370911312941</v>
+        <v>0.01747808587627843</v>
       </c>
       <c r="AI287">
-        <v>0.01747808587627843</v>
+        <v>0.8033259999999999</v>
       </c>
       <c r="AJ287">
-        <v>0.8033259999999999</v>
+        <v>0.330532</v>
       </c>
       <c r="AK287">
-        <v>0.330532</v>
-      </c>
-      <c r="AL287">
         <v>21.758862</v>
+      </c>
+      <c r="AL287" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:38">
@@ -30727,20 +31402,23 @@
       <c r="AF288">
         <v>29.6888696320693</v>
       </c>
+      <c r="AG288">
+        <v>0.4442138399730595</v>
+      </c>
       <c r="AH288">
-        <v>0.4442138399730595</v>
+        <v>0.02246260907214744</v>
       </c>
       <c r="AI288">
-        <v>0.02246260907214744</v>
+        <v>0.738556</v>
       </c>
       <c r="AJ288">
-        <v>0.738556</v>
+        <v>0.209941</v>
       </c>
       <c r="AK288">
-        <v>0.209941</v>
-      </c>
-      <c r="AL288">
         <v>21.759343</v>
+      </c>
+      <c r="AL288" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:38">
@@ -30837,20 +31515,23 @@
       <c r="AF289">
         <v>30.8302778846325</v>
       </c>
+      <c r="AG289">
+        <v>0.2503279557553382</v>
+      </c>
       <c r="AH289">
-        <v>0.2503279557553382</v>
+        <v>0</v>
       </c>
       <c r="AI289">
-        <v>0</v>
+        <v>0.9304650000000001</v>
       </c>
       <c r="AJ289">
-        <v>0.9304650000000001</v>
+        <v>0.5772629999999999</v>
       </c>
       <c r="AK289">
-        <v>0.5772629999999999</v>
-      </c>
-      <c r="AL289">
         <v>21.758398</v>
+      </c>
+      <c r="AL289" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:38">
@@ -30947,20 +31628,23 @@
       <c r="AF290">
         <v>24.4295333615859</v>
       </c>
+      <c r="AG290">
+        <v>0.375300181165998</v>
+      </c>
       <c r="AH290">
-        <v>0.375300181165998</v>
+        <v>0.02784575731552617</v>
       </c>
       <c r="AI290">
-        <v>0.02784575731552617</v>
+        <v>-0.01977899999999999</v>
       </c>
       <c r="AJ290">
-        <v>-0.01977899999999999</v>
+        <v>-0.01322999999999996</v>
       </c>
       <c r="AK290">
-        <v>-0.01322999999999996</v>
-      </c>
-      <c r="AL290">
         <v>-0.0005290000000002237</v>
+      </c>
+      <c r="AL290" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:38">
@@ -31057,20 +31741,23 @@
       <c r="AF291">
         <v>26.9523610264621</v>
       </c>
+      <c r="AG291">
+        <v>0.3162291293130229</v>
+      </c>
       <c r="AH291">
-        <v>0.3162291293130229</v>
+        <v>0.02585182378810599</v>
       </c>
       <c r="AI291">
-        <v>0.02585182378810599</v>
+        <v>-0.01502400000000004</v>
       </c>
       <c r="AJ291">
-        <v>-0.01502400000000004</v>
+        <v>-0.01045200000000002</v>
       </c>
       <c r="AK291">
-        <v>-0.01045200000000002</v>
-      </c>
-      <c r="AL291">
         <v>-0.0004580000000018458</v>
+      </c>
+      <c r="AL291" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:38">
@@ -31167,20 +31854,23 @@
       <c r="AF292">
         <v>25.5657309854272</v>
       </c>
+      <c r="AG292">
+        <v>0.2851266880708015</v>
+      </c>
       <c r="AH292">
-        <v>0.2851266880708015</v>
+        <v>0.02213250607091861</v>
       </c>
       <c r="AI292">
-        <v>0.02213250607091861</v>
+        <v>-0.01323999999999992</v>
       </c>
       <c r="AJ292">
-        <v>-0.01323999999999992</v>
+        <v>-0.01023299999999994</v>
       </c>
       <c r="AK292">
-        <v>-0.01023299999999994</v>
-      </c>
-      <c r="AL292">
         <v>-0.0008310000000015805</v>
+      </c>
+      <c r="AL292" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:38">
@@ -31271,20 +31961,23 @@
       <c r="AC293">
         <v>71.34</v>
       </c>
+      <c r="AG293">
+        <v>0.3363673435847722</v>
+      </c>
       <c r="AH293">
-        <v>0.3363673435847722</v>
+        <v>0.01927386553359571</v>
       </c>
       <c r="AI293">
-        <v>0.01927386553359571</v>
+        <v>-0.01148799999999994</v>
       </c>
       <c r="AJ293">
-        <v>-0.01148799999999994</v>
+        <v>-0.008740999999999999</v>
       </c>
       <c r="AK293">
-        <v>-0.008740999999999999</v>
-      </c>
-      <c r="AL293">
         <v>0.0007489999999990005</v>
+      </c>
+      <c r="AL293" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:38">
@@ -31375,20 +32068,23 @@
       <c r="AC294">
         <v>64.3</v>
       </c>
+      <c r="AG294">
+        <v>0.3258294205634602</v>
+      </c>
       <c r="AH294">
-        <v>0.3258294205634602</v>
+        <v>0.01177726037283843</v>
       </c>
       <c r="AI294">
-        <v>0.01177726037283843</v>
+        <v>-0.007051999999999947</v>
       </c>
       <c r="AJ294">
-        <v>-0.007051999999999947</v>
+        <v>-0.006132000000000026</v>
       </c>
       <c r="AK294">
-        <v>-0.006132000000000026</v>
-      </c>
-      <c r="AL294">
         <v>-0.0004300000000014848</v>
+      </c>
+      <c r="AL294" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:38">
@@ -31479,20 +32175,23 @@
       <c r="AC295">
         <v>41.96</v>
       </c>
+      <c r="AG295">
+        <v>0.386093303948417</v>
+      </c>
       <c r="AH295">
-        <v>0.386093303948417</v>
+        <v>0.006548875032852878</v>
       </c>
       <c r="AI295">
-        <v>0.006548875032852878</v>
+        <v>-0.004215999999999998</v>
       </c>
       <c r="AJ295">
-        <v>-0.004215999999999998</v>
+        <v>-0.003634000000000026</v>
       </c>
       <c r="AK295">
-        <v>-0.003634000000000026</v>
-      </c>
-      <c r="AL295">
         <v>-0.0008729999999985694</v>
+      </c>
+      <c r="AL295" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:38">
@@ -31583,8 +32282,11 @@
       <c r="AC296">
         <v>70.86</v>
       </c>
+      <c r="AG296">
+        <v>0.3904936405966725</v>
+      </c>
       <c r="AH296">
-        <v>0.3904936405966725</v>
+        <v>0</v>
       </c>
       <c r="AI296">
         <v>0</v>
@@ -31593,10 +32295,10 @@
         <v>0</v>
       </c>
       <c r="AK296">
-        <v>0</v>
-      </c>
-      <c r="AL296">
         <v>-0.0003700000000002035</v>
+      </c>
+      <c r="AL296" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:38">
@@ -31687,20 +32389,23 @@
       <c r="AC297">
         <v>100.93</v>
       </c>
+      <c r="AG297">
+        <v>0.3625964102769348</v>
+      </c>
       <c r="AH297">
-        <v>0.3625964102769348</v>
+        <v>0</v>
       </c>
       <c r="AI297">
-        <v>0</v>
+        <v>0.01367299999999982</v>
       </c>
       <c r="AJ297">
-        <v>0.01367299999999982</v>
+        <v>0.01178699999999999</v>
       </c>
       <c r="AK297">
-        <v>0.01178699999999999</v>
-      </c>
-      <c r="AL297">
         <v>-0.0004719999999984736</v>
+      </c>
+      <c r="AL297" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:38">
@@ -31791,20 +32496,23 @@
       <c r="AC298">
         <v>82.48999999999999</v>
       </c>
+      <c r="AG298">
+        <v>0.4032822978810752</v>
+      </c>
       <c r="AH298">
-        <v>0.4032822978810752</v>
+        <v>0</v>
       </c>
       <c r="AI298">
-        <v>0</v>
+        <v>0.01671200000000006</v>
       </c>
       <c r="AJ298">
-        <v>0.01671200000000006</v>
+        <v>0.01132</v>
       </c>
       <c r="AK298">
-        <v>0.01132</v>
-      </c>
-      <c r="AL298">
         <v>0.0008639999999999759</v>
+      </c>
+      <c r="AL298" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:38">
@@ -31896,22 +32604,22 @@
         <v>52.32</v>
       </c>
       <c r="AG299">
-        <v>2772.3</v>
+        <v>1.361934921437563</v>
       </c>
       <c r="AH299">
-        <v>1.361934921437563</v>
+        <v>0.4864411940372825</v>
       </c>
       <c r="AI299">
-        <v>0.4864411940372825</v>
+        <v>-0.8550610000000001</v>
       </c>
       <c r="AJ299">
-        <v>-0.8550610000000001</v>
+        <v>-0.631649</v>
       </c>
       <c r="AK299">
-        <v>-0.631649</v>
-      </c>
-      <c r="AL299">
         <v>-1.480095</v>
+      </c>
+      <c r="AL299" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:38">
@@ -32003,22 +32711,22 @@
         <v>43.64</v>
       </c>
       <c r="AG300">
-        <v>2750.6</v>
+        <v>1.096917363467532</v>
       </c>
       <c r="AH300">
-        <v>1.096917363467532</v>
+        <v>0.4392065458203723</v>
       </c>
       <c r="AI300">
-        <v>0.4392065458203723</v>
+        <v>-0.610769</v>
       </c>
       <c r="AJ300">
-        <v>-0.610769</v>
+        <v>-0.5340779999999999</v>
       </c>
       <c r="AK300">
-        <v>-0.5340779999999999</v>
-      </c>
-      <c r="AL300">
         <v>-0.8831199999999999</v>
+      </c>
+      <c r="AL300" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:38">
@@ -32110,22 +32818,22 @@
         <v>54.13</v>
       </c>
       <c r="AG301">
-        <v>2845</v>
+        <v>1.11715499189858</v>
       </c>
       <c r="AH301">
-        <v>1.11715499189858</v>
+        <v>0.5023971364392691</v>
       </c>
       <c r="AI301">
-        <v>0.5023971364392691</v>
+        <v>-0.698615</v>
       </c>
       <c r="AJ301">
-        <v>-0.698615</v>
+        <v>-0.622333</v>
       </c>
       <c r="AK301">
-        <v>-0.622333</v>
-      </c>
-      <c r="AL301">
         <v>-1.775022</v>
+      </c>
+      <c r="AL301" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:38">
@@ -32217,22 +32925,22 @@
         <v>71.34</v>
       </c>
       <c r="AG302">
-        <v>5162.6</v>
+        <v>1.149642408410487</v>
       </c>
       <c r="AH302">
-        <v>1.149642408410487</v>
+        <v>0.5868689528764367</v>
       </c>
       <c r="AI302">
-        <v>0.5868689528764367</v>
+        <v>-0.88832</v>
       </c>
       <c r="AJ302">
-        <v>-0.88832</v>
+        <v>-0.7612719999999999</v>
       </c>
       <c r="AK302">
-        <v>-0.7612719999999999</v>
-      </c>
-      <c r="AL302">
         <v>-5.1774</v>
+      </c>
+      <c r="AL302" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:38">
@@ -32324,22 +33032,22 @@
         <v>64.3</v>
       </c>
       <c r="AG303">
-        <v>9828.5</v>
+        <v>0.792500473871768</v>
       </c>
       <c r="AH303">
-        <v>0.792500473871768</v>
+        <v>0.5581682718599894</v>
       </c>
       <c r="AI303">
-        <v>0.5581682718599894</v>
+        <v>-0.849873</v>
       </c>
       <c r="AJ303">
-        <v>-0.849873</v>
+        <v>-0.700354</v>
       </c>
       <c r="AK303">
-        <v>-0.700354</v>
-      </c>
-      <c r="AL303">
         <v>-1.676290999999999</v>
+      </c>
+      <c r="AL303" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:38">
@@ -32431,22 +33139,22 @@
         <v>41.96</v>
       </c>
       <c r="AG304">
-        <v>23796.5</v>
+        <v>0.3598697166024167</v>
       </c>
       <c r="AH304">
-        <v>0.3598697166024167</v>
+        <v>0.4214135940761206</v>
       </c>
       <c r="AI304">
-        <v>0.4214135940761206</v>
+        <v>-0.589276</v>
       </c>
       <c r="AJ304">
-        <v>-0.589276</v>
+        <v>-0.463644</v>
       </c>
       <c r="AK304">
-        <v>-0.463644</v>
-      </c>
-      <c r="AL304">
         <v>-0.6349540000000005</v>
+      </c>
+      <c r="AL304" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:38">
@@ -32538,22 +33246,22 @@
         <v>70.86</v>
       </c>
       <c r="AG305">
-        <v>29062</v>
+        <v>0.38645416567327</v>
       </c>
       <c r="AH305">
-        <v>0.38645416567327</v>
+        <v>0.5405223483212397</v>
       </c>
       <c r="AI305">
-        <v>0.5405223483212397</v>
+        <v>-0.8607180000000001</v>
       </c>
       <c r="AJ305">
-        <v>-0.8607180000000001</v>
+        <v>-0.664289</v>
       </c>
       <c r="AK305">
-        <v>-0.664289</v>
-      </c>
-      <c r="AL305">
         <v>-1.937556000000001</v>
+      </c>
+      <c r="AL305" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:38">
@@ -32645,22 +33353,22 @@
         <v>100.93</v>
       </c>
       <c r="AG306">
-        <v>41978.9</v>
+        <v>0.5978481734576608</v>
       </c>
       <c r="AH306">
-        <v>0.5978481734576608</v>
+        <v>0.6086418481923677</v>
       </c>
       <c r="AI306">
-        <v>0.6086418481923677</v>
+        <v>-1.092241</v>
       </c>
       <c r="AJ306">
-        <v>-1.092241</v>
+        <v>-0.9460540000000001</v>
       </c>
       <c r="AK306">
-        <v>-0.9460540000000001</v>
-      </c>
-      <c r="AL306">
         <v>-1.937716</v>
+      </c>
+      <c r="AL306" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:38">
@@ -32752,22 +33460,22 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AG307">
-        <v>35109.8</v>
+        <v>0.4909768294336784</v>
       </c>
       <c r="AH307">
-        <v>0.4909768294336784</v>
+        <v>0.5532286232159824</v>
       </c>
       <c r="AI307">
-        <v>0.5532286232159824</v>
+        <v>-0.9194870000000001</v>
       </c>
       <c r="AJ307">
-        <v>-0.9194870000000001</v>
+        <v>-0.634479</v>
       </c>
       <c r="AK307">
-        <v>-0.634479</v>
-      </c>
-      <c r="AL307">
         <v>-1.938321</v>
+      </c>
+      <c r="AL307" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/panel_pais_anio.xlsx
+++ b/data/processed/panel_pais_anio.xlsx
@@ -893,6 +893,15 @@
       <c r="AC2">
         <v>52.32</v>
       </c>
+      <c r="AD2">
+        <v>-1.5</v>
+      </c>
+      <c r="AE2">
+        <v>74.2</v>
+      </c>
+      <c r="AF2">
+        <v>23.897997199527</v>
+      </c>
       <c r="AI2">
         <v>0.6346660000000001</v>
       </c>
@@ -976,6 +985,15 @@
       <c r="AC3">
         <v>43.64</v>
       </c>
+      <c r="AD3">
+        <v>-1.5</v>
+      </c>
+      <c r="AE3">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AF3">
+        <v>23.664061083824</v>
+      </c>
       <c r="AI3">
         <v>0.641451</v>
       </c>
@@ -1059,6 +1077,15 @@
       <c r="AC4">
         <v>54.13</v>
       </c>
+      <c r="AD4">
+        <v>-2.6</v>
+      </c>
+      <c r="AE4">
+        <v>75.8</v>
+      </c>
+      <c r="AF4">
+        <v>21.971289135942</v>
+      </c>
       <c r="AI4">
         <v>0.636995</v>
       </c>
@@ -1142,6 +1169,15 @@
       <c r="AC5">
         <v>71.34</v>
       </c>
+      <c r="AD5">
+        <v>-2.6</v>
+      </c>
+      <c r="AE5">
+        <v>73.3</v>
+      </c>
+      <c r="AF5">
+        <v>22.221713107356</v>
+      </c>
       <c r="AI5">
         <v>0.671455</v>
       </c>
@@ -1225,6 +1261,15 @@
       <c r="AC6">
         <v>64.3</v>
       </c>
+      <c r="AD6">
+        <v>-0.2</v>
+      </c>
+      <c r="AE6">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AF6">
+        <v>23.789750239214</v>
+      </c>
       <c r="AI6">
         <v>0.6840200000000001</v>
       </c>
@@ -1308,6 +1353,15 @@
       <c r="AC7">
         <v>41.96</v>
       </c>
+      <c r="AD7">
+        <v>-16.8</v>
+      </c>
+      <c r="AE7">
+        <v>116.3</v>
+      </c>
+      <c r="AF7">
+        <v>24.856368048573</v>
+      </c>
       <c r="AI7">
         <v>0.7618630000000001</v>
       </c>
@@ -1385,6 +1439,15 @@
       <c r="AC8">
         <v>70.86</v>
       </c>
+      <c r="AD8">
+        <v>-9.9</v>
+      </c>
+      <c r="AE8">
+        <v>109.7</v>
+      </c>
+      <c r="AF8">
+        <v>21.217848834359</v>
+      </c>
       <c r="AI8">
         <v>0.7449480000000001</v>
       </c>
@@ -1462,6 +1525,15 @@
       <c r="AC9">
         <v>100.93</v>
       </c>
+      <c r="AD9">
+        <v>-0.5</v>
+      </c>
+      <c r="AE9">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AF9">
+        <v>22.622022465937</v>
+      </c>
       <c r="AI9">
         <v>0.74829</v>
       </c>
@@ -1539,6 +1611,15 @@
       <c r="AC10">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD10">
+        <v>3</v>
+      </c>
+      <c r="AE10">
+        <v>80.3</v>
+      </c>
+      <c r="AF10">
+        <v>24.821835133372</v>
+      </c>
       <c r="AI10">
         <v>0.7407339999999999</v>
       </c>
@@ -1641,10 +1722,13 @@
         <v>52.32</v>
       </c>
       <c r="AD11">
-        <v>-3.39011034719535</v>
+        <v>-6</v>
+      </c>
+      <c r="AE11">
+        <v>52.6</v>
       </c>
       <c r="AF11">
-        <v>22.1490803040164</v>
+        <v>35.365772019338</v>
       </c>
       <c r="AG11">
         <v>0.9986617829592704</v>
@@ -1754,10 +1838,13 @@
         <v>43.64</v>
       </c>
       <c r="AD12">
-        <v>-5.33377782706346</v>
+        <v>-6.7</v>
+      </c>
+      <c r="AE12">
+        <v>53.1</v>
       </c>
       <c r="AF12">
-        <v>21.2567013071388</v>
+        <v>34.8673516945</v>
       </c>
       <c r="AG12">
         <v>0.8456930680351684</v>
@@ -1867,10 +1954,13 @@
         <v>54.13</v>
       </c>
       <c r="AD13">
-        <v>-5.51824569508007</v>
+        <v>-6.7</v>
+      </c>
+      <c r="AE13">
+        <v>57</v>
       </c>
       <c r="AF13">
-        <v>19.3371239744582</v>
+        <v>34.428112889621</v>
       </c>
       <c r="AG13">
         <v>0.7605615721708542</v>
@@ -1980,10 +2070,13 @@
         <v>71.34</v>
       </c>
       <c r="AD14">
-        <v>-5.33635226717988</v>
+        <v>-5.4</v>
+      </c>
+      <c r="AE14">
+        <v>85.2</v>
       </c>
       <c r="AF14">
-        <v>17.7024488717292</v>
+        <v>33.508062809874</v>
       </c>
       <c r="AG14">
         <v>0.864184420512183</v>
@@ -2093,10 +2186,13 @@
         <v>64.3</v>
       </c>
       <c r="AD15">
-        <v>-4.92889704924096</v>
+        <v>-4.4</v>
+      </c>
+      <c r="AE15">
+        <v>89.8</v>
       </c>
       <c r="AF15">
-        <v>17.7888990504455</v>
+        <v>33.684299956878</v>
       </c>
       <c r="AG15">
         <v>0.8013857314531383</v>
@@ -2206,10 +2302,13 @@
         <v>41.96</v>
       </c>
       <c r="AD16">
-        <v>-8.6954919523039</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="AE16">
+        <v>103.8</v>
       </c>
       <c r="AF16">
-        <v>17.4777322783093</v>
+        <v>33.805168381982</v>
       </c>
       <c r="AG16">
         <v>0.6219406994652591</v>
@@ -2319,10 +2418,13 @@
         <v>70.86</v>
       </c>
       <c r="AD17">
-        <v>-4.37239542495983</v>
+        <v>-4.3</v>
+      </c>
+      <c r="AE17">
+        <v>81</v>
       </c>
       <c r="AF17">
-        <v>18.0764989044589</v>
+        <v>33.550413326565</v>
       </c>
       <c r="AG17">
         <v>1.054314013380204</v>
@@ -2432,10 +2534,13 @@
         <v>100.93</v>
       </c>
       <c r="AD18">
-        <v>-4.42708731934181</v>
+        <v>-3.8</v>
+      </c>
+      <c r="AE18">
+        <v>84.3</v>
       </c>
       <c r="AF18">
-        <v>17.893195301026</v>
+        <v>33.806737762499</v>
       </c>
       <c r="AG18">
         <v>1.282986343283853</v>
@@ -2545,10 +2650,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD19">
-        <v>-3.59487367618527</v>
+        <v>-5.3</v>
+      </c>
+      <c r="AE19">
+        <v>154.6</v>
       </c>
       <c r="AF19">
-        <v>17.7753274051522</v>
+        <v>32.307759101982</v>
       </c>
       <c r="AG19">
         <v>1.021644018452963</v>
@@ -2639,6 +2747,15 @@
       <c r="AC20">
         <v>52.32</v>
       </c>
+      <c r="AD20">
+        <v>-2.4</v>
+      </c>
+      <c r="AE20">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AF20">
+        <v>22.414317846999</v>
+      </c>
       <c r="AI20">
         <v>0.7194199999999999</v>
       </c>
@@ -2722,6 +2839,15 @@
       <c r="AC21">
         <v>43.64</v>
       </c>
+      <c r="AD21">
+        <v>-0.1</v>
+      </c>
+      <c r="AE21">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AF21">
+        <v>23.640050741808</v>
+      </c>
       <c r="AI21">
         <v>0.8512500000000001</v>
       </c>
@@ -2805,6 +2931,15 @@
       <c r="AC22">
         <v>54.13</v>
       </c>
+      <c r="AD22">
+        <v>-2.7</v>
+      </c>
+      <c r="AE22">
+        <v>88.2</v>
+      </c>
+      <c r="AF22">
+        <v>19.833040146135</v>
+      </c>
       <c r="AI22">
         <v>0.7283490000000001</v>
       </c>
@@ -2888,6 +3023,15 @@
       <c r="AC23">
         <v>71.34</v>
       </c>
+      <c r="AD23">
+        <v>-2.4</v>
+      </c>
+      <c r="AE23">
+        <v>84.3</v>
+      </c>
+      <c r="AF23">
+        <v>19.108963704351</v>
+      </c>
       <c r="AI23">
         <v>0.6012479999999999</v>
       </c>
@@ -2971,6 +3115,15 @@
       <c r="AC24">
         <v>64.3</v>
       </c>
+      <c r="AD24">
+        <v>-3.6</v>
+      </c>
+      <c r="AE24">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF24">
+        <v>18.468756982544</v>
+      </c>
       <c r="AI24">
         <v>0.6439009999999999</v>
       </c>
@@ -3054,6 +3207,15 @@
       <c r="AC25">
         <v>41.96</v>
       </c>
+      <c r="AD25">
+        <v>-6.2</v>
+      </c>
+      <c r="AE25">
+        <v>100.5</v>
+      </c>
+      <c r="AF25">
+        <v>19.750362974167</v>
+      </c>
       <c r="AI25">
         <v>0.88332</v>
       </c>
@@ -3155,6 +3317,15 @@
       <c r="AC26">
         <v>70.86</v>
       </c>
+      <c r="AD26">
+        <v>-4.5</v>
+      </c>
+      <c r="AE26">
+        <v>93</v>
+      </c>
+      <c r="AF26">
+        <v>18.86600842353</v>
+      </c>
       <c r="AG26">
         <v>0.5720372261497413</v>
       </c>
@@ -3262,6 +3433,15 @@
       <c r="AC27">
         <v>100.93</v>
       </c>
+      <c r="AD27">
+        <v>-2.9</v>
+      </c>
+      <c r="AE27">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AF27">
+        <v>17.952924823252</v>
+      </c>
       <c r="AG27">
         <v>0.6715103964603115</v>
       </c>
@@ -3369,6 +3549,15 @@
       <c r="AC28">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD28">
+        <v>-1.7</v>
+      </c>
+      <c r="AE28">
+        <v>74.5</v>
+      </c>
+      <c r="AF28">
+        <v>16.695326097626</v>
+      </c>
       <c r="AG28">
         <v>0.4899296458964391</v>
       </c>
@@ -3477,13 +3666,13 @@
         <v>52.32</v>
       </c>
       <c r="AD29">
-        <v>-3.23821987412989</v>
+        <v>-3.3</v>
       </c>
       <c r="AE29">
-        <v>47.6225079407988</v>
+        <v>49.9</v>
       </c>
       <c r="AF29">
-        <v>14.6273782452524</v>
+        <v>15.075230484807</v>
       </c>
       <c r="AG29">
         <v>0.4560006036404706</v>
@@ -3593,13 +3782,13 @@
         <v>43.64</v>
       </c>
       <c r="AD30">
-        <v>-2.60907980439192</v>
+        <v>-2.6</v>
       </c>
       <c r="AE30">
-        <v>50.2046646297839</v>
+        <v>51.1</v>
       </c>
       <c r="AF30">
-        <v>16.7435935230496</v>
+        <v>16.747317985643</v>
       </c>
       <c r="AG30">
         <v>0.5174097130947023</v>
@@ -3709,13 +3898,13 @@
         <v>54.13</v>
       </c>
       <c r="AD31">
-        <v>-5.3083648775197</v>
+        <v>-6.1</v>
       </c>
       <c r="AE31">
-        <v>52.624565152769</v>
+        <v>54.6</v>
       </c>
       <c r="AF31">
-        <v>16.6326878235545</v>
+        <v>17.012789412406</v>
       </c>
       <c r="AG31">
         <v>0.8617648528569762</v>
@@ -3825,13 +4014,13 @@
         <v>71.34</v>
       </c>
       <c r="AD32">
-        <v>-3.23645001248128</v>
+        <v>-3.3</v>
       </c>
       <c r="AE32">
-        <v>56.5027068771842</v>
+        <v>61.5</v>
       </c>
       <c r="AF32">
-        <v>15.9117105591613</v>
+        <v>16.162863402244</v>
       </c>
       <c r="AG32">
         <v>0.6680470336684079</v>
@@ -3941,13 +4130,13 @@
         <v>64.3</v>
       </c>
       <c r="AD33">
-        <v>-1.65181140317843</v>
+        <v>-1.7</v>
       </c>
       <c r="AE33">
-        <v>56.6924606462303</v>
+        <v>60.3</v>
       </c>
       <c r="AF33">
-        <v>18.2742562325827</v>
+        <v>18.589552140907</v>
       </c>
       <c r="AG33">
         <v>0.594675810768165</v>
@@ -4057,13 +4246,13 @@
         <v>41.96</v>
       </c>
       <c r="AD34">
-        <v>-7.83218419986105</v>
+        <v>-7.1</v>
       </c>
       <c r="AE34">
-        <v>79.0414158203086</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AF34">
-        <v>20.1369104813185</v>
+        <v>17.651674669686</v>
       </c>
       <c r="AG34">
         <v>0.2614321247077997</v>
@@ -4173,13 +4362,13 @@
         <v>70.86</v>
       </c>
       <c r="AD35">
-        <v>-11.0938698263687</v>
+        <v>-11.9</v>
       </c>
       <c r="AE35">
-        <v>82.5398306524293</v>
+        <v>90.7</v>
       </c>
       <c r="AF35">
-        <v>15.8516580958711</v>
+        <v>17.020530658428</v>
       </c>
       <c r="AG35">
         <v>0.744087907693997</v>
@@ -4289,13 +4478,13 @@
         <v>100.93</v>
       </c>
       <c r="AD36">
-        <v>-5.19361424932359</v>
+        <v>-5.5</v>
       </c>
       <c r="AE36">
-        <v>77.6639776530748</v>
+        <v>84.7</v>
       </c>
       <c r="AF36">
-        <v>18.7489017543607</v>
+        <v>20.097953833585</v>
       </c>
       <c r="AG36">
         <v>1.025361325992459</v>
@@ -4405,13 +4594,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD37">
-        <v>-3.4954019304185</v>
+        <v>-3.7</v>
       </c>
       <c r="AE37">
-        <v>73.7303208143</v>
+        <v>78.3</v>
       </c>
       <c r="AF37">
-        <v>18.691039629894</v>
+        <v>19.565696801666</v>
       </c>
       <c r="AG37">
         <v>0.9544623982118635</v>
@@ -4521,10 +4710,13 @@
         <v>52.32</v>
       </c>
       <c r="AD38">
-        <v>-3.75341494678653</v>
+        <v>-5.1</v>
+      </c>
+      <c r="AE38">
+        <v>65.09999999999999</v>
       </c>
       <c r="AF38">
-        <v>22.1980924438071</v>
+        <v>22.804556916074</v>
       </c>
       <c r="AG38">
         <v>0.01616345087384453</v>
@@ -4634,10 +4826,13 @@
         <v>43.64</v>
       </c>
       <c r="AD39">
-        <v>-3.39757154965879</v>
+        <v>-4.5</v>
+      </c>
+      <c r="AE39">
+        <v>70.5</v>
       </c>
       <c r="AF39">
-        <v>22.4029818854459</v>
+        <v>23.1889107414</v>
       </c>
       <c r="AG39">
         <v>0.01696077064510215</v>
@@ -4747,10 +4942,13 @@
         <v>54.13</v>
       </c>
       <c r="AD40">
-        <v>-1.16349962472886</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE40">
+        <v>78.09999999999999</v>
       </c>
       <c r="AF40">
-        <v>23.8070928559695</v>
+        <v>24.188046292838</v>
       </c>
       <c r="AG40">
         <v>0.02259485649453168</v>
@@ -4859,6 +5057,15 @@
       <c r="AC41">
         <v>71.34</v>
       </c>
+      <c r="AD41">
+        <v>-1.4</v>
+      </c>
+      <c r="AE41">
+        <v>79</v>
+      </c>
+      <c r="AF41">
+        <v>25.564256569904</v>
+      </c>
       <c r="AG41">
         <v>0.02821093916367924</v>
       </c>
@@ -4966,6 +5173,15 @@
       <c r="AC42">
         <v>64.3</v>
       </c>
+      <c r="AD42">
+        <v>-2.9</v>
+      </c>
+      <c r="AE42">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="AF42">
+        <v>24.629948712771</v>
+      </c>
       <c r="AG42">
         <v>0.09555183267902002</v>
       </c>
@@ -5073,6 +5289,15 @@
       <c r="AC43">
         <v>41.96</v>
       </c>
+      <c r="AD43">
+        <v>-8.6</v>
+      </c>
+      <c r="AE43">
+        <v>103</v>
+      </c>
+      <c r="AF43">
+        <v>24.586732518503</v>
+      </c>
       <c r="AG43">
         <v>0.02374291669392448</v>
       </c>
@@ -5180,6 +5405,15 @@
       <c r="AC44">
         <v>70.86</v>
       </c>
+      <c r="AD44">
+        <v>-3.3</v>
+      </c>
+      <c r="AE44">
+        <v>82.2</v>
+      </c>
+      <c r="AF44">
+        <v>22.442181361961</v>
+      </c>
       <c r="AG44">
         <v>0.04773712955697176</v>
       </c>
@@ -5287,6 +5521,15 @@
       <c r="AC45">
         <v>100.93</v>
       </c>
+      <c r="AD45">
+        <v>-1</v>
+      </c>
+      <c r="AE45">
+        <v>66.8</v>
+      </c>
+      <c r="AF45">
+        <v>22.380845077985</v>
+      </c>
       <c r="AG45">
         <v>0.1614112318518836</v>
       </c>
@@ -5394,6 +5637,15 @@
       <c r="AC46">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD46">
+        <v>-2.4</v>
+      </c>
+      <c r="AE46">
+        <v>67.5</v>
+      </c>
+      <c r="AF46">
+        <v>23.368431003274</v>
+      </c>
       <c r="AG46">
         <v>0.1158677341079852</v>
       </c>
@@ -5501,6 +5753,15 @@
       <c r="AC47">
         <v>52.32</v>
       </c>
+      <c r="AD47">
+        <v>-5.8</v>
+      </c>
+      <c r="AE47">
+        <v>34</v>
+      </c>
+      <c r="AF47">
+        <v>31.202820521003</v>
+      </c>
       <c r="AG47">
         <v>0.339712184452695</v>
       </c>
@@ -5608,6 +5869,15 @@
       <c r="AC48">
         <v>43.64</v>
       </c>
+      <c r="AD48">
+        <v>-6</v>
+      </c>
+      <c r="AE48">
+        <v>38.2</v>
+      </c>
+      <c r="AF48">
+        <v>26.912766583408</v>
+      </c>
       <c r="AG48">
         <v>0.2815176868441289</v>
       </c>
@@ -5715,6 +5985,15 @@
       <c r="AC49">
         <v>54.13</v>
       </c>
+      <c r="AD49">
+        <v>-6.4</v>
+      </c>
+      <c r="AE49">
+        <v>41.9</v>
+      </c>
+      <c r="AF49">
+        <v>25.141716521227</v>
+      </c>
       <c r="AG49">
         <v>0.3505525893803847</v>
       </c>
@@ -5822,6 +6101,15 @@
       <c r="AC50">
         <v>71.34</v>
       </c>
+      <c r="AD50">
+        <v>-6.8</v>
+      </c>
+      <c r="AE50">
+        <v>44.2</v>
+      </c>
+      <c r="AF50">
+        <v>24.584680396171</v>
+      </c>
       <c r="AG50">
         <v>0.4594643788762242</v>
       </c>
@@ -5929,6 +6217,15 @@
       <c r="AC51">
         <v>64.3</v>
       </c>
+      <c r="AD51">
+        <v>-6</v>
+      </c>
+      <c r="AE51">
+        <v>48.9</v>
+      </c>
+      <c r="AF51">
+        <v>24.089524541762</v>
+      </c>
       <c r="AG51">
         <v>0.4144535761973656</v>
       </c>
@@ -6036,6 +6333,15 @@
       <c r="AC52">
         <v>41.96</v>
       </c>
+      <c r="AD52">
+        <v>-11</v>
+      </c>
+      <c r="AE52">
+        <v>67.5</v>
+      </c>
+      <c r="AF52">
+        <v>20.95223365009</v>
+      </c>
       <c r="AG52">
         <v>0.2367720133613741</v>
       </c>
@@ -6143,6 +6449,15 @@
       <c r="AC53">
         <v>70.86</v>
       </c>
+      <c r="AD53">
+        <v>-7.9</v>
+      </c>
+      <c r="AE53">
+        <v>68.7</v>
+      </c>
+      <c r="AF53">
+        <v>21.566382991637</v>
+      </c>
       <c r="AG53">
         <v>0.4934436730221975</v>
       </c>
@@ -6250,6 +6565,15 @@
       <c r="AC54">
         <v>100.93</v>
       </c>
+      <c r="AD54">
+        <v>-6.1</v>
+      </c>
+      <c r="AE54">
+        <v>69.2</v>
+      </c>
+      <c r="AF54">
+        <v>25.029699214225</v>
+      </c>
       <c r="AG54">
         <v>0.659263495616622</v>
       </c>
@@ -6357,6 +6681,15 @@
       <c r="AC55">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD55">
+        <v>-9.5</v>
+      </c>
+      <c r="AE55">
+        <v>78.3</v>
+      </c>
+      <c r="AF55">
+        <v>24.024941165444</v>
+      </c>
       <c r="AG55">
         <v>0.5289632395689846</v>
       </c>
@@ -6465,13 +6798,13 @@
         <v>52.32</v>
       </c>
       <c r="AD56">
-        <v>-8.03019066677877</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AE56">
-        <v>67.5375540307946</v>
+        <v>71.7</v>
       </c>
       <c r="AF56">
-        <v>25.8123252140431</v>
+        <v>36.909473687082</v>
       </c>
       <c r="AG56">
         <v>0.1989257779608123</v>
@@ -6581,13 +6914,13 @@
         <v>43.64</v>
       </c>
       <c r="AD57">
-        <v>-7.06027781099588</v>
+        <v>-8</v>
       </c>
       <c r="AE57">
-        <v>73.4188038019563</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AF57">
-        <v>26.173225388189</v>
+        <v>37.512310094404</v>
       </c>
       <c r="AG57">
         <v>0.1591596304688321</v>
@@ -6697,13 +7030,13 @@
         <v>54.13</v>
       </c>
       <c r="AD58">
-        <v>-7.7163015572921</v>
+        <v>-8</v>
       </c>
       <c r="AE58">
-        <v>83.6692026491606</v>
+        <v>82.7</v>
       </c>
       <c r="AF58">
-        <v>24.3609920782892</v>
+        <v>36.327653090882</v>
       </c>
       <c r="AG58">
         <v>0.1797728297184986</v>
@@ -6813,13 +7146,13 @@
         <v>71.34</v>
       </c>
       <c r="AD59">
-        <v>-6.78706251271256</v>
+        <v>-7</v>
       </c>
       <c r="AE59">
-        <v>86.6078841212333</v>
+        <v>84.8</v>
       </c>
       <c r="AF59">
-        <v>25.2724385286024</v>
+        <v>37.190521294663</v>
       </c>
       <c r="AG59">
         <v>0.1973861296504714</v>
@@ -6929,13 +7262,13 @@
         <v>64.3</v>
       </c>
       <c r="AD60">
-        <v>-5.30690433831975</v>
+        <v>-4.9</v>
       </c>
       <c r="AE60">
-        <v>92.5652531951269</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AF60">
-        <v>25.5600401306072</v>
+        <v>38.184350196019</v>
       </c>
       <c r="AG60">
         <v>0.2219138568021822</v>
@@ -7045,13 +7378,13 @@
         <v>41.96</v>
       </c>
       <c r="AD61">
-        <v>-12.4363388244923</v>
+        <v>-11.6</v>
       </c>
       <c r="AE61">
-        <v>98.7098819471851</v>
+        <v>96</v>
       </c>
       <c r="AF61">
-        <v>22.1948673455795</v>
+        <v>34.541533904004</v>
       </c>
       <c r="AG61">
         <v>0.2104521730849312</v>
@@ -7161,13 +7494,13 @@
         <v>70.86</v>
       </c>
       <c r="AD62">
-        <v>-4.53656203172015</v>
+        <v>-2.6</v>
       </c>
       <c r="AE62">
-        <v>85.011503676948</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AF62">
-        <v>24.6358299212806</v>
+        <v>37.740239873289</v>
       </c>
       <c r="AG62">
         <v>0.3168810523575522</v>
@@ -7277,13 +7610,13 @@
         <v>100.93</v>
       </c>
       <c r="AD63">
-        <v>-4.46637752028169</v>
+        <v>-4</v>
       </c>
       <c r="AE63">
-        <v>79.10232188803781</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AF63">
-        <v>26.9365134620331</v>
+        <v>39.48063525235</v>
       </c>
       <c r="AG63">
         <v>0.3182467318351081</v>
@@ -7393,13 +7726,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD64">
-        <v>-6.86868984803199</v>
+        <v>-7.7</v>
       </c>
       <c r="AE64">
-        <v>83.0317498523499</v>
+        <v>84</v>
       </c>
       <c r="AF64">
-        <v>25.3707484836752</v>
+        <v>37.596855335807</v>
       </c>
       <c r="AG64">
         <v>0.2723665450514142</v>
@@ -7509,13 +7842,13 @@
         <v>52.32</v>
       </c>
       <c r="AD65">
-        <v>-7.21373287821486</v>
+        <v>-7.6</v>
       </c>
       <c r="AE65">
-        <v>117.275144046752</v>
+        <v>122.5</v>
       </c>
       <c r="AF65">
-        <v>22.10491944754</v>
+        <v>21.584969805442</v>
       </c>
       <c r="AG65">
         <v>0.07019294620254873</v>
@@ -7625,13 +7958,13 @@
         <v>43.64</v>
       </c>
       <c r="AD66">
-        <v>-4.15237850244951</v>
+        <v>-4.5</v>
       </c>
       <c r="AE66">
-        <v>125.131136441335</v>
+        <v>127.1</v>
       </c>
       <c r="AF66">
-        <v>25.2273067617101</v>
+        <v>24.068724445941</v>
       </c>
       <c r="AG66">
         <v>0.07174090622302046</v>
@@ -7740,6 +8073,15 @@
       <c r="AC67">
         <v>54.13</v>
       </c>
+      <c r="AD67">
+        <v>-3.6</v>
+      </c>
+      <c r="AE67">
+        <v>134.6</v>
+      </c>
+      <c r="AF67">
+        <v>24.332693576263</v>
+      </c>
       <c r="AG67">
         <v>0.07904909281277159</v>
       </c>
@@ -7847,6 +8189,15 @@
       <c r="AC68">
         <v>71.34</v>
       </c>
+      <c r="AD68">
+        <v>-0.3</v>
+      </c>
+      <c r="AE68">
+        <v>107.2</v>
+      </c>
+      <c r="AF68">
+        <v>24.702934808592</v>
+      </c>
       <c r="AG68">
         <v>0.09899000424423764</v>
       </c>
@@ -7954,6 +8305,15 @@
       <c r="AC69">
         <v>64.3</v>
       </c>
+      <c r="AD69">
+        <v>2.9</v>
+      </c>
+      <c r="AE69">
+        <v>101.6</v>
+      </c>
+      <c r="AF69">
+        <v>25.069676010518</v>
+      </c>
       <c r="AG69">
         <v>0.1018087698090169</v>
       </c>
@@ -8061,6 +8421,15 @@
       <c r="AC70">
         <v>41.96</v>
       </c>
+      <c r="AD70">
+        <v>-4.2</v>
+      </c>
+      <c r="AE70">
+        <v>129.6</v>
+      </c>
+      <c r="AF70">
+        <v>26.379915113614</v>
+      </c>
       <c r="AG70">
         <v>0.06519171996221718</v>
       </c>
@@ -8168,6 +8537,15 @@
       <c r="AC71">
         <v>70.86</v>
       </c>
+      <c r="AD71">
+        <v>-3.9</v>
+      </c>
+      <c r="AE71">
+        <v>108.6</v>
+      </c>
+      <c r="AF71">
+        <v>23.243306079547</v>
+      </c>
       <c r="AG71">
         <v>0.09303799200012243</v>
       </c>
@@ -8275,6 +8653,15 @@
       <c r="AC72">
         <v>100.93</v>
       </c>
+      <c r="AD72">
+        <v>-1.7</v>
+      </c>
+      <c r="AE72">
+        <v>104</v>
+      </c>
+      <c r="AF72">
+        <v>25.171871081612</v>
+      </c>
       <c r="AG72">
         <v>0.1062319080492729</v>
       </c>
@@ -8382,6 +8769,15 @@
       <c r="AC73">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD73">
+        <v>-1.6</v>
+      </c>
+      <c r="AE73">
+        <v>104.1</v>
+      </c>
+      <c r="AF73">
+        <v>24.878825347417</v>
+      </c>
       <c r="AG73">
         <v>0.08077982507837604</v>
       </c>
@@ -8490,10 +8886,13 @@
         <v>52.32</v>
       </c>
       <c r="AD74">
-        <v>-2.14568328960442</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE74">
+        <v>17.4</v>
       </c>
       <c r="AF74">
-        <v>21.1423576597254</v>
+        <v>22.93943628365</v>
       </c>
       <c r="AG74">
         <v>0.7646415168135781</v>
@@ -8603,10 +9002,13 @@
         <v>43.64</v>
       </c>
       <c r="AD75">
-        <v>-2.73388798624091</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE75">
+        <v>21.1</v>
       </c>
       <c r="AF75">
-        <v>20.8570992758656</v>
+        <v>22.706036756175</v>
       </c>
       <c r="AG75">
         <v>0.8120319790686434</v>
@@ -8716,10 +9118,13 @@
         <v>54.13</v>
       </c>
       <c r="AD76">
-        <v>-2.55814767454965</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE76">
+        <v>23.7</v>
       </c>
       <c r="AF76">
-        <v>21.1680432165628</v>
+        <v>22.865089482107</v>
       </c>
       <c r="AG76">
         <v>0.7897740017971175</v>
@@ -8829,10 +9234,13 @@
         <v>71.34</v>
       </c>
       <c r="AD77">
-        <v>-1.7258596181872</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE77">
+        <v>25.8</v>
       </c>
       <c r="AF77">
-        <v>22.1740306166793</v>
+        <v>24.133439910433</v>
       </c>
       <c r="AG77">
         <v>0.7880594644948724</v>
@@ -8942,10 +9350,13 @@
         <v>64.3</v>
       </c>
       <c r="AD78">
-        <v>-2.84519500863434</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE78">
+        <v>28.3</v>
       </c>
       <c r="AF78">
-        <v>21.739927149931</v>
+        <v>23.766623207823</v>
       </c>
       <c r="AG78">
         <v>0.8162852585746241</v>
@@ -9055,10 +9466,13 @@
         <v>41.96</v>
       </c>
       <c r="AD79">
-        <v>-7.21904641164918</v>
+        <v>-7.1</v>
+      </c>
+      <c r="AE79">
+        <v>32.4</v>
       </c>
       <c r="AF79">
-        <v>19.9382667510933</v>
+        <v>21.99304272478</v>
       </c>
       <c r="AG79">
         <v>0.6512278306965467</v>
@@ -9168,10 +9582,13 @@
         <v>70.86</v>
       </c>
       <c r="AD80">
-        <v>-7.72312323783927</v>
+        <v>-7.5</v>
+      </c>
+      <c r="AE80">
+        <v>36.4</v>
       </c>
       <c r="AF80">
-        <v>24.1674095479002</v>
+        <v>26.090307464747</v>
       </c>
       <c r="AG80">
         <v>0.8021127799348304</v>
@@ -9281,10 +9698,13 @@
         <v>100.93</v>
       </c>
       <c r="AD81">
-        <v>1.13200004002418</v>
+        <v>1.4</v>
+      </c>
+      <c r="AE81">
+        <v>37.9</v>
       </c>
       <c r="AF81">
-        <v>26.0812426572599</v>
+        <v>28.085085664301</v>
       </c>
       <c r="AG81">
         <v>0.9157179348253978</v>
@@ -9394,10 +9814,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD82">
-        <v>-2.39074850027879</v>
+        <v>-2.3</v>
+      </c>
+      <c r="AE82">
+        <v>39.4</v>
       </c>
       <c r="AF82">
-        <v>22.9465317535315</v>
+        <v>25.122697922888</v>
       </c>
       <c r="AG82">
         <v>0.5884371595505187</v>
@@ -9507,13 +9930,13 @@
         <v>52.32</v>
       </c>
       <c r="AD83">
-        <v>-1.40738619185838</v>
+        <v>-3.5</v>
       </c>
       <c r="AE83">
-        <v>53.2785874737167</v>
+        <v>50.4</v>
       </c>
       <c r="AF83">
-        <v>24.1024162766989</v>
+        <v>27.757127825676</v>
       </c>
       <c r="AG83">
         <v>0.3256033943633691</v>
@@ -9623,13 +10046,13 @@
         <v>43.64</v>
       </c>
       <c r="AD84">
-        <v>-3.04286241958897</v>
+        <v>-2.3</v>
       </c>
       <c r="AE84">
-        <v>66.9071609125065</v>
+        <v>49.9</v>
       </c>
       <c r="AF84">
-        <v>24.2234212780588</v>
+        <v>27.719668486621</v>
       </c>
       <c r="AG84">
         <v>0.3625566077717619</v>
@@ -9739,13 +10162,13 @@
         <v>54.13</v>
       </c>
       <c r="AD85">
-        <v>-2.19824409588726</v>
+        <v>-2.5</v>
       </c>
       <c r="AE85">
-        <v>66.7272478472146</v>
+        <v>49.4</v>
       </c>
       <c r="AF85">
-        <v>22.5842861999584</v>
+        <v>26.824972175386</v>
       </c>
       <c r="AG85">
         <v>0.3630110123661155</v>
@@ -9855,13 +10278,13 @@
         <v>71.34</v>
       </c>
       <c r="AD86">
-        <v>-2.61320674678311</v>
+        <v>-4.7</v>
       </c>
       <c r="AE86">
-        <v>71.65057024810559</v>
+        <v>51.8</v>
       </c>
       <c r="AF86">
-        <v>23.4751871722398</v>
+        <v>29.990242298186</v>
       </c>
       <c r="AG86">
         <v>0.3916222384329775</v>
@@ -9971,13 +10394,13 @@
         <v>64.3</v>
       </c>
       <c r="AD87">
-        <v>-2.23798643665382</v>
+        <v>-3.5</v>
       </c>
       <c r="AE87">
-        <v>72.70387857708219</v>
+        <v>51</v>
       </c>
       <c r="AF87">
-        <v>25.575368512731</v>
+        <v>29.397056421943</v>
       </c>
       <c r="AG87">
         <v>0.4291959769269287</v>
@@ -10087,13 +10510,13 @@
         <v>41.96</v>
       </c>
       <c r="AD88">
-        <v>-8.515533579082881</v>
+        <v>-7.1</v>
       </c>
       <c r="AE88">
-        <v>91.1566069449736</v>
+        <v>65.3</v>
       </c>
       <c r="AF88">
-        <v>23.6871303712315</v>
+        <v>26.588116220092</v>
       </c>
       <c r="AG88">
         <v>0.3378370706526375</v>
@@ -10203,13 +10626,13 @@
         <v>70.86</v>
       </c>
       <c r="AD89">
-        <v>-7.65394474545161</v>
+        <v>-7.3</v>
       </c>
       <c r="AE89">
-        <v>80.4259616037106</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF89">
-        <v>24.1312117221098</v>
+        <v>27.198069120587</v>
       </c>
       <c r="AG89">
         <v>0.5242926420230365</v>
@@ -10319,13 +10742,13 @@
         <v>100.93</v>
       </c>
       <c r="AD90">
-        <v>-5.29929051233517</v>
+        <v>-6.4</v>
       </c>
       <c r="AE90">
-        <v>70.2611599864283</v>
+        <v>61.3</v>
       </c>
       <c r="AF90">
-        <v>25.4074707206706</v>
+        <v>27.727355990026</v>
       </c>
       <c r="AG90">
         <v>0.6921359170818548</v>
@@ -10435,13 +10858,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD91">
-        <v>-2.04098550110347</v>
+        <v>-2.9</v>
       </c>
       <c r="AE91">
-        <v>71.3312731896082</v>
+        <v>55.4</v>
       </c>
       <c r="AF91">
-        <v>28.4136914959886</v>
+        <v>32.170876746366</v>
       </c>
       <c r="AG91">
         <v>0.5357007914156112</v>
@@ -10550,8 +10973,14 @@
       <c r="AC92">
         <v>52.32</v>
       </c>
+      <c r="AD92">
+        <v>-5.5</v>
+      </c>
+      <c r="AE92">
+        <v>39.8</v>
+      </c>
       <c r="AF92">
-        <v>23.4572080583441</v>
+        <v>13.236865986922</v>
       </c>
       <c r="AG92">
         <v>0.2003440111794715</v>
@@ -10660,8 +11089,14 @@
       <c r="AC93">
         <v>43.64</v>
       </c>
+      <c r="AD93">
+        <v>-5.1</v>
+      </c>
+      <c r="AE93">
+        <v>44.1</v>
+      </c>
       <c r="AF93">
-        <v>24.0079934600948</v>
+        <v>13.661789188587</v>
       </c>
       <c r="AG93">
         <v>0.2541735171297335</v>
@@ -10770,8 +11205,14 @@
       <c r="AC94">
         <v>54.13</v>
       </c>
+      <c r="AD94">
+        <v>-5.9</v>
+      </c>
+      <c r="AE94">
+        <v>47.1</v>
+      </c>
       <c r="AF94">
-        <v>23.3185966619773</v>
+        <v>13.277753242279</v>
       </c>
       <c r="AG94">
         <v>0.2954108554916408</v>
@@ -10880,8 +11321,14 @@
       <c r="AC95">
         <v>71.34</v>
       </c>
+      <c r="AD95">
+        <v>-5.6</v>
+      </c>
+      <c r="AE95">
+        <v>51.7</v>
+      </c>
       <c r="AF95">
-        <v>24.3167782701782</v>
+        <v>13.203670943989</v>
       </c>
       <c r="AG95">
         <v>0.2883821074409657</v>
@@ -10991,10 +11438,13 @@
         <v>64.3</v>
       </c>
       <c r="AD96">
-        <v>-2.32627659299422</v>
+        <v>-6.6</v>
+      </c>
+      <c r="AE96">
+        <v>56.1</v>
       </c>
       <c r="AF96">
-        <v>27.5354175556737</v>
+        <v>14.924409769828</v>
       </c>
       <c r="AG96">
         <v>0.2992418878592031</v>
@@ -11104,10 +11554,13 @@
         <v>41.96</v>
       </c>
       <c r="AD97">
-        <v>-5.3522749947218</v>
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AE97">
+        <v>66.5</v>
       </c>
       <c r="AF97">
-        <v>27.1843242899476</v>
+        <v>13.821369167821</v>
       </c>
       <c r="AG97">
         <v>0.1654386167841267</v>
@@ -11217,10 +11670,13 @@
         <v>70.86</v>
       </c>
       <c r="AD98">
-        <v>-2.77815643267862</v>
+        <v>-5</v>
+      </c>
+      <c r="AE98">
+        <v>67</v>
       </c>
       <c r="AF98">
-        <v>28.2061355248318</v>
+        <v>15.537181736499</v>
       </c>
       <c r="AG98">
         <v>0.3435822906395561</v>
@@ -11330,10 +11786,13 @@
         <v>100.93</v>
       </c>
       <c r="AD99">
-        <v>-0.0522988947716759</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE99">
+        <v>61.4</v>
       </c>
       <c r="AF99">
-        <v>28.8914258324714</v>
+        <v>15.977331501279</v>
       </c>
       <c r="AG99">
         <v>0.3725200992630867</v>
@@ -11443,10 +11902,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD100">
-        <v>0.439026284006009</v>
+        <v>-3.2</v>
+      </c>
+      <c r="AE100">
+        <v>60.4</v>
       </c>
       <c r="AF100">
-        <v>29.3390402864479</v>
+        <v>15.085134819363</v>
       </c>
       <c r="AG100">
         <v>0.3036371620794919</v>
@@ -11537,6 +11999,15 @@
       <c r="AC101">
         <v>52.32</v>
       </c>
+      <c r="AD101">
+        <v>11.4</v>
+      </c>
+      <c r="AE101">
+        <v>68.2</v>
+      </c>
+      <c r="AF101">
+        <v>43.772499235694</v>
+      </c>
       <c r="AI101">
         <v>0.5370819999999999</v>
       </c>
@@ -11620,6 +12091,15 @@
       <c r="AC102">
         <v>43.64</v>
       </c>
+      <c r="AD102">
+        <v>11.6</v>
+      </c>
+      <c r="AE102">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AF102">
+        <v>59.62812145843</v>
+      </c>
       <c r="AI102">
         <v>0.5228489999999999</v>
       </c>
@@ -11703,6 +12183,15 @@
       <c r="AC103">
         <v>54.13</v>
       </c>
+      <c r="AD103">
+        <v>-3.3</v>
+      </c>
+      <c r="AE103">
+        <v>84.2</v>
+      </c>
+      <c r="AF103">
+        <v>50.713663033788</v>
+      </c>
       <c r="AI103">
         <v>0.520764</v>
       </c>
@@ -11786,6 +12275,15 @@
       <c r="AC104">
         <v>71.34</v>
       </c>
+      <c r="AD104">
+        <v>-17.2</v>
+      </c>
+      <c r="AE104">
+        <v>85.7</v>
+      </c>
+      <c r="AF104">
+        <v>46.246532215317</v>
+      </c>
       <c r="AI104">
         <v>0.5098010000000001</v>
       </c>
@@ -11869,6 +12367,15 @@
       <c r="AC105">
         <v>64.3</v>
       </c>
+      <c r="AD105">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="AE105">
+        <v>97.8</v>
+      </c>
+      <c r="AF105">
+        <v>39.561846238309</v>
+      </c>
       <c r="AI105">
         <v>0.4936690000000001</v>
       </c>
@@ -11952,6 +12459,15 @@
       <c r="AC106">
         <v>41.96</v>
       </c>
+      <c r="AD106">
+        <v>-7.5</v>
+      </c>
+      <c r="AE106">
+        <v>118.4</v>
+      </c>
+      <c r="AF106">
+        <v>59.229712246998</v>
+      </c>
       <c r="AI106">
         <v>0.5182259999999999</v>
       </c>
@@ -12053,6 +12569,15 @@
       <c r="AC107">
         <v>70.86</v>
       </c>
+      <c r="AD107">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AE107">
+        <v>116.3</v>
+      </c>
+      <c r="AF107">
+        <v>58.771622927148</v>
+      </c>
       <c r="AG107">
         <v>0.2150667197598824</v>
       </c>
@@ -12160,6 +12685,15 @@
       <c r="AC108">
         <v>100.93</v>
       </c>
+      <c r="AD108">
+        <v>-7.2</v>
+      </c>
+      <c r="AE108">
+        <v>110</v>
+      </c>
+      <c r="AF108">
+        <v>62.51442113462</v>
+      </c>
       <c r="AG108">
         <v>0.2326171490706407</v>
       </c>
@@ -12267,6 +12801,15 @@
       <c r="AC109">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD109">
+        <v>-4.5</v>
+      </c>
+      <c r="AE109">
+        <v>101.3</v>
+      </c>
+      <c r="AF109">
+        <v>60.306074773603</v>
+      </c>
       <c r="AG109">
         <v>0.1926922233347343</v>
       </c>
@@ -12375,10 +12918,13 @@
         <v>52.32</v>
       </c>
       <c r="AD110">
-        <v>-0.0137507698086695</v>
+        <v>0</v>
+      </c>
+      <c r="AE110">
+        <v>44.8</v>
       </c>
       <c r="AF110">
-        <v>14.5186216543802</v>
+        <v>16.694624294622</v>
       </c>
       <c r="AG110">
         <v>0.2369215651027185</v>
@@ -12488,10 +13034,13 @@
         <v>43.64</v>
       </c>
       <c r="AD111">
-        <v>-3.02646274607075</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE111">
+        <v>46.7</v>
       </c>
       <c r="AF111">
-        <v>14.827297566694</v>
+        <v>13.899066735488</v>
       </c>
       <c r="AG111">
         <v>0.2556994874684549</v>
@@ -12601,10 +13150,13 @@
         <v>54.13</v>
       </c>
       <c r="AD112">
-        <v>-3.38919282715608</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE112">
+        <v>49.5</v>
       </c>
       <c r="AF112">
-        <v>14.9920997503639</v>
+        <v>14.140596567288</v>
       </c>
       <c r="AG112">
         <v>0.2180222631220768</v>
@@ -12714,10 +13266,13 @@
         <v>71.34</v>
       </c>
       <c r="AD113">
-        <v>-2.43860550444748</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE113">
+        <v>50.8</v>
       </c>
       <c r="AF113">
-        <v>15.269462908084</v>
+        <v>14.284863256305</v>
       </c>
       <c r="AG113">
         <v>0.2725469395050613</v>
@@ -12827,10 +13382,13 @@
         <v>64.3</v>
       </c>
       <c r="AD114">
-        <v>-3.54751974530668</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE114">
+        <v>53.5</v>
       </c>
       <c r="AF114">
-        <v>15.5470600045533</v>
+        <v>14.363006832284</v>
       </c>
       <c r="AG114">
         <v>0.3979691196730002</v>
@@ -12940,10 +13498,13 @@
         <v>41.96</v>
       </c>
       <c r="AD115">
-        <v>-8.3098749631764</v>
+        <v>-7.9</v>
+      </c>
+      <c r="AE115">
+        <v>71.8</v>
       </c>
       <c r="AF115">
-        <v>14.8813590480588</v>
+        <v>14.240513311294</v>
       </c>
       <c r="AG115">
         <v>0.3934607016032607</v>
@@ -13053,10 +13614,13 @@
         <v>70.86</v>
       </c>
       <c r="AD116">
-        <v>-2.46543421523845</v>
+        <v>-2.9</v>
+      </c>
+      <c r="AE116">
+        <v>62.8</v>
       </c>
       <c r="AF116">
-        <v>16.4297863174204</v>
+        <v>15.498669615807</v>
       </c>
       <c r="AG116">
         <v>0.6242257713279917</v>
@@ -13166,10 +13730,13 @@
         <v>100.93</v>
       </c>
       <c r="AD117">
-        <v>-3.17762653492364</v>
+        <v>-3.2</v>
+      </c>
+      <c r="AE117">
+        <v>59.6</v>
       </c>
       <c r="AF117">
-        <v>16.3623217477379</v>
+        <v>15.273368095779</v>
       </c>
       <c r="AG117">
         <v>0.787853165816615</v>
@@ -13279,10 +13846,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD118">
-        <v>-3.38217585157086</v>
+        <v>-3.3</v>
+      </c>
+      <c r="AE118">
+        <v>60.5</v>
       </c>
       <c r="AF118">
-        <v>17.015284341071</v>
+        <v>15.845492390768</v>
       </c>
       <c r="AG118">
         <v>0.6711089089001835</v>
@@ -13392,10 +13962,13 @@
         <v>52.32</v>
       </c>
       <c r="AD119">
-        <v>-5.69774311670289</v>
+        <v>-6.9</v>
+      </c>
+      <c r="AE119">
+        <v>36.4</v>
       </c>
       <c r="AF119">
-        <v>30.8458833789351</v>
+        <v>37.221683948517</v>
       </c>
       <c r="AG119">
         <v>0.7198231545371626</v>
@@ -13505,10 +14078,13 @@
         <v>43.64</v>
       </c>
       <c r="AD120">
-        <v>-8.57164995739415</v>
+        <v>-10.3</v>
+      </c>
+      <c r="AE120">
+        <v>46.1</v>
       </c>
       <c r="AF120">
-        <v>28.6412079584013</v>
+        <v>33.835649828911</v>
       </c>
       <c r="AG120">
         <v>0.6968334263134307</v>
@@ -13618,10 +14194,13 @@
         <v>54.13</v>
       </c>
       <c r="AD121">
-        <v>-6.36519719285874</v>
+        <v>-5.8</v>
+      </c>
+      <c r="AE121">
+        <v>47.4</v>
       </c>
       <c r="AF121">
-        <v>27.9863154861129</v>
+        <v>34.71377480203</v>
       </c>
       <c r="AG121">
         <v>0.744794356753479</v>
@@ -13731,10 +14310,13 @@
         <v>71.34</v>
       </c>
       <c r="AD122">
-        <v>-3.52514850564392</v>
+        <v>-2.8</v>
+      </c>
+      <c r="AE122">
+        <v>49.5</v>
       </c>
       <c r="AF122">
-        <v>31.2062328120813</v>
+        <v>38.121948856836</v>
       </c>
       <c r="AG122">
         <v>0.7969343365391971</v>
@@ -13844,10 +14426,13 @@
         <v>64.3</v>
       </c>
       <c r="AD123">
-        <v>-4.27034595652833</v>
+        <v>-3.5</v>
+      </c>
+      <c r="AE123">
+        <v>52.1</v>
       </c>
       <c r="AF123">
-        <v>29.6599984642663</v>
+        <v>36.285547753875</v>
       </c>
       <c r="AG123">
         <v>0.7440816858162707</v>
@@ -13957,10 +14542,13 @@
         <v>41.96</v>
       </c>
       <c r="AD124">
-        <v>-7.49141811316719</v>
+        <v>-7.4</v>
+      </c>
+      <c r="AE124">
+        <v>63.6</v>
       </c>
       <c r="AF124">
-        <v>27.1210867326524</v>
+        <v>32.824706883009</v>
       </c>
       <c r="AG124">
         <v>0.5785009824709282</v>
@@ -14070,10 +14658,13 @@
         <v>70.86</v>
       </c>
       <c r="AD125">
-        <v>-2.90457512420842</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE125">
+        <v>61.8</v>
       </c>
       <c r="AF125">
-        <v>29.6714820409688</v>
+        <v>35.868237373976</v>
       </c>
       <c r="AG125">
         <v>0.6665449801859565</v>
@@ -14183,10 +14774,13 @@
         <v>100.93</v>
       </c>
       <c r="AD126">
-        <v>-0.0062162674566409</v>
+        <v>0</v>
+      </c>
+      <c r="AE126">
+        <v>57.2</v>
       </c>
       <c r="AF126">
-        <v>30.9625405355437</v>
+        <v>38.896372522219</v>
       </c>
       <c r="AG126">
         <v>0.8710155833891512</v>
@@ -14295,6 +14889,15 @@
       <c r="AC127">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD127">
+        <v>-3.5</v>
+      </c>
+      <c r="AE127">
+        <v>54.5</v>
+      </c>
+      <c r="AF127">
+        <v>36.077927677101</v>
+      </c>
       <c r="AG127">
         <v>0.8354810251881977</v>
       </c>
@@ -14402,6 +15005,15 @@
       <c r="AC128">
         <v>52.32</v>
       </c>
+      <c r="AD128">
+        <v>-0.8</v>
+      </c>
+      <c r="AE128">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="AF128">
+        <v>24.461028303516</v>
+      </c>
       <c r="AG128">
         <v>0.3566457645811721</v>
       </c>
@@ -14509,6 +15121,15 @@
       <c r="AC129">
         <v>43.64</v>
       </c>
+      <c r="AD129">
+        <v>2.7</v>
+      </c>
+      <c r="AE129">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF129">
+        <v>26.217607944237</v>
+      </c>
       <c r="AG129">
         <v>0.3663741745635178</v>
       </c>
@@ -14616,6 +15237,15 @@
       <c r="AC130">
         <v>54.13</v>
       </c>
+      <c r="AD130">
+        <v>3</v>
+      </c>
+      <c r="AE130">
+        <v>70.3</v>
+      </c>
+      <c r="AF130">
+        <v>25.602033976673</v>
+      </c>
       <c r="AG130">
         <v>0.381808017980202</v>
       </c>
@@ -14723,6 +15353,15 @@
       <c r="AC131">
         <v>71.34</v>
       </c>
+      <c r="AD131">
+        <v>4.9</v>
+      </c>
+      <c r="AE131">
+        <v>68.5</v>
+      </c>
+      <c r="AF131">
+        <v>26.99163574497</v>
+      </c>
       <c r="AG131">
         <v>0.2815052294872931</v>
       </c>
@@ -14830,6 +15469,15 @@
       <c r="AC132">
         <v>64.3</v>
       </c>
+      <c r="AD132">
+        <v>5</v>
+      </c>
+      <c r="AE132">
+        <v>62.7</v>
+      </c>
+      <c r="AF132">
+        <v>26.599858875091</v>
+      </c>
       <c r="AG132">
         <v>0.2843454172039643</v>
       </c>
@@ -14937,6 +15585,15 @@
       <c r="AC133">
         <v>41.96</v>
       </c>
+      <c r="AD133">
+        <v>-4.5</v>
+      </c>
+      <c r="AE133">
+        <v>89.5</v>
+      </c>
+      <c r="AF133">
+        <v>28.137350865431</v>
+      </c>
       <c r="AG133">
         <v>0.2338433020822233</v>
       </c>
@@ -15044,6 +15701,15 @@
       <c r="AC134">
         <v>70.86</v>
       </c>
+      <c r="AD134">
+        <v>0.3</v>
+      </c>
+      <c r="AE134">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AF134">
+        <v>31.587029727526</v>
+      </c>
       <c r="AG134">
         <v>0.2532526778058514</v>
       </c>
@@ -15151,6 +15817,15 @@
       <c r="AC135">
         <v>100.93</v>
       </c>
+      <c r="AD135">
+        <v>0.9</v>
+      </c>
+      <c r="AE135">
+        <v>79.3</v>
+      </c>
+      <c r="AF135">
+        <v>32.931708838352</v>
+      </c>
       <c r="AG135">
         <v>0.2988870806002533</v>
       </c>
@@ -15258,6 +15933,15 @@
       <c r="AC136">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD136">
+        <v>7.9</v>
+      </c>
+      <c r="AE136">
+        <v>74.5</v>
+      </c>
+      <c r="AF136">
+        <v>36.606647417346</v>
+      </c>
       <c r="AG136">
         <v>0.1500378188863966</v>
       </c>
@@ -15366,10 +16050,13 @@
         <v>52.32</v>
       </c>
       <c r="AD137">
-        <v>-1.47564487783448</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE137">
+        <v>24.8</v>
       </c>
       <c r="AF137">
-        <v>11.6684130766311</v>
+        <v>11.109482939281</v>
       </c>
       <c r="AG137">
         <v>0.105018518367814</v>
@@ -15479,10 +16166,13 @@
         <v>43.64</v>
       </c>
       <c r="AD138">
-        <v>-1.11021822656786</v>
+        <v>-1.1</v>
+      </c>
+      <c r="AE138">
+        <v>24.9</v>
       </c>
       <c r="AF138">
-        <v>11.9784847026855</v>
+        <v>11.455671291385</v>
       </c>
       <c r="AG138">
         <v>0.1099174657380804</v>
@@ -15592,10 +16282,13 @@
         <v>54.13</v>
       </c>
       <c r="AD139">
-        <v>-1.37831049093858</v>
+        <v>-1.4</v>
+      </c>
+      <c r="AE139">
+        <v>25.1</v>
       </c>
       <c r="AF139">
-        <v>11.8855616228225</v>
+        <v>11.393366495901</v>
       </c>
       <c r="AG139">
         <v>0.09768871548329933</v>
@@ -15705,10 +16398,13 @@
         <v>71.34</v>
       </c>
       <c r="AD140">
-        <v>-1.87503523800931</v>
+        <v>-1.9</v>
+      </c>
+      <c r="AE140">
+        <v>26.4</v>
       </c>
       <c r="AF140">
-        <v>11.7783778069365</v>
+        <v>11.306780002907</v>
       </c>
       <c r="AG140">
         <v>0.1264268830218466</v>
@@ -15818,10 +16514,13 @@
         <v>64.3</v>
       </c>
       <c r="AD141">
-        <v>-2.23511034211637</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE141">
+        <v>26.4</v>
       </c>
       <c r="AF141">
-        <v>11.7162477369852</v>
+        <v>11.205035569749</v>
       </c>
       <c r="AG141">
         <v>0.1432972959592655</v>
@@ -15931,10 +16630,13 @@
         <v>41.96</v>
       </c>
       <c r="AD142">
-        <v>-4.35589779033159</v>
+        <v>-4.9</v>
+      </c>
+      <c r="AE142">
+        <v>31.5</v>
       </c>
       <c r="AF142">
-        <v>11.118681180436</v>
+        <v>10.675427078131</v>
       </c>
       <c r="AG142">
         <v>0.07687045496819339</v>
@@ -16044,10 +16746,13 @@
         <v>70.86</v>
       </c>
       <c r="AD143">
-        <v>-1.14900209815134</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AE143">
+        <v>30.6</v>
       </c>
       <c r="AF143">
-        <v>12.6596673834992</v>
+        <v>12.30706957096</v>
       </c>
       <c r="AG143">
         <v>0.1611004944935874</v>
@@ -16157,10 +16862,13 @@
         <v>100.93</v>
       </c>
       <c r="AD144">
-        <v>-1.70787872719767</v>
+        <v>-1.7</v>
+      </c>
+      <c r="AE144">
+        <v>29</v>
       </c>
       <c r="AF144">
-        <v>12.8936854888585</v>
+        <v>12.571829383937</v>
       </c>
       <c r="AG144">
         <v>0.1758219166940297</v>
@@ -16270,10 +16978,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD145">
-        <v>-1.25751928033412</v>
+        <v>-1.3</v>
+      </c>
+      <c r="AE145">
+        <v>27.2</v>
       </c>
       <c r="AF145">
-        <v>12.8498936023601</v>
+        <v>12.480324589208</v>
       </c>
       <c r="AG145">
         <v>0.1653920422472224</v>
@@ -16382,6 +17093,15 @@
       <c r="AC146">
         <v>52.32</v>
       </c>
+      <c r="AD146">
+        <v>-0.7</v>
+      </c>
+      <c r="AE146">
+        <v>42.2</v>
+      </c>
+      <c r="AF146">
+        <v>20.991221398329</v>
+      </c>
       <c r="AG146">
         <v>0.1767433168105416</v>
       </c>
@@ -16489,6 +17209,15 @@
       <c r="AC147">
         <v>43.64</v>
       </c>
+      <c r="AD147">
+        <v>-3.2</v>
+      </c>
+      <c r="AE147">
+        <v>35.7</v>
+      </c>
+      <c r="AF147">
+        <v>21.970109225032</v>
+      </c>
       <c r="AG147">
         <v>0.2884103320441938</v>
       </c>
@@ -16596,6 +17325,15 @@
       <c r="AC148">
         <v>54.13</v>
       </c>
+      <c r="AD148">
+        <v>-3.1</v>
+      </c>
+      <c r="AE148">
+        <v>35.2</v>
+      </c>
+      <c r="AF148">
+        <v>23.168847424164</v>
+      </c>
       <c r="AG148">
         <v>0.2874941940275127</v>
       </c>
@@ -16703,6 +17441,15 @@
       <c r="AC149">
         <v>71.34</v>
       </c>
+      <c r="AD149">
+        <v>-2.5</v>
+      </c>
+      <c r="AE149">
+        <v>37.4</v>
+      </c>
+      <c r="AF149">
+        <v>25.035161994892</v>
+      </c>
       <c r="AG149">
         <v>0.2748639125176683</v>
       </c>
@@ -16810,6 +17557,15 @@
       <c r="AC150">
         <v>64.3</v>
       </c>
+      <c r="AD150">
+        <v>-2.5</v>
+      </c>
+      <c r="AE150">
+        <v>34.2</v>
+      </c>
+      <c r="AF150">
+        <v>25.609571776276</v>
+      </c>
       <c r="AG150">
         <v>0.2970284442573063</v>
       </c>
@@ -16917,6 +17673,15 @@
       <c r="AC151">
         <v>41.96</v>
       </c>
+      <c r="AD151">
+        <v>-7.8</v>
+      </c>
+      <c r="AE151">
+        <v>47.4</v>
+      </c>
+      <c r="AF151">
+        <v>22.762654689216</v>
+      </c>
       <c r="AG151">
         <v>0.468382628469653</v>
       </c>
@@ -17024,6 +17789,15 @@
       <c r="AC152">
         <v>70.86</v>
       </c>
+      <c r="AD152">
+        <v>-6.9</v>
+      </c>
+      <c r="AE152">
+        <v>38.9</v>
+      </c>
+      <c r="AF152">
+        <v>17.842383004857</v>
+      </c>
       <c r="AG152">
         <v>0.3637490586941644</v>
       </c>
@@ -17131,6 +17905,15 @@
       <c r="AC153">
         <v>100.93</v>
       </c>
+      <c r="AD153">
+        <v>-5.1</v>
+      </c>
+      <c r="AE153">
+        <v>24.8</v>
+      </c>
+      <c r="AF153">
+        <v>15.2871510974</v>
+      </c>
       <c r="AG153">
         <v>0.3452415990971049</v>
       </c>
@@ -17238,6 +18021,15 @@
       <c r="AC154">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD154">
+        <v>-5.6</v>
+      </c>
+      <c r="AE154">
+        <v>26.7</v>
+      </c>
+      <c r="AF154">
+        <v>18.080887555583</v>
+      </c>
       <c r="AG154">
         <v>0.6401472226534571</v>
       </c>
@@ -17346,10 +18138,13 @@
         <v>52.32</v>
       </c>
       <c r="AD155">
-        <v>-0.859334595922316</v>
+        <v>-0.8</v>
+      </c>
+      <c r="AE155">
+        <v>38.3</v>
       </c>
       <c r="AF155">
-        <v>23.363155171353</v>
+        <v>25.240786936311</v>
       </c>
       <c r="AG155">
         <v>0.08398503082391079</v>
@@ -17458,6 +18253,15 @@
       <c r="AC156">
         <v>43.64</v>
       </c>
+      <c r="AD156">
+        <v>-0.4</v>
+      </c>
+      <c r="AE156">
+        <v>39.4</v>
+      </c>
+      <c r="AF156">
+        <v>26.985198207163</v>
+      </c>
       <c r="AG156">
         <v>0.08675921246856487</v>
       </c>
@@ -17565,6 +18369,15 @@
       <c r="AC157">
         <v>54.13</v>
       </c>
+      <c r="AD157">
+        <v>-0.4</v>
+      </c>
+      <c r="AE157">
+        <v>41.3</v>
+      </c>
+      <c r="AF157">
+        <v>26.450147459269</v>
+      </c>
       <c r="AG157">
         <v>0.09373368485523932</v>
       </c>
@@ -17672,6 +18485,15 @@
       <c r="AC158">
         <v>71.34</v>
       </c>
+      <c r="AD158">
+        <v>0.2</v>
+      </c>
+      <c r="AE158">
+        <v>42.4</v>
+      </c>
+      <c r="AF158">
+        <v>26.353339161148</v>
+      </c>
       <c r="AG158">
         <v>0.09381075445727499</v>
       </c>
@@ -17779,6 +18601,15 @@
       <c r="AC159">
         <v>64.3</v>
       </c>
+      <c r="AD159">
+        <v>0.1</v>
+      </c>
+      <c r="AE159">
+        <v>43.3</v>
+      </c>
+      <c r="AF159">
+        <v>26.028244602868</v>
+      </c>
       <c r="AG159">
         <v>0.1168143671833313</v>
       </c>
@@ -17887,10 +18718,13 @@
         <v>41.96</v>
       </c>
       <c r="AD160">
-        <v>-4.52977692141499</v>
+        <v>-4.6</v>
+      </c>
+      <c r="AE160">
+        <v>53.5</v>
       </c>
       <c r="AF160">
-        <v>22.2099126100845</v>
+        <v>23.843404732402</v>
       </c>
       <c r="AG160">
         <v>0.08354707441961179</v>
@@ -17999,6 +18833,15 @@
       <c r="AC161">
         <v>70.86</v>
       </c>
+      <c r="AD161">
+        <v>-3.2</v>
+      </c>
+      <c r="AE161">
+        <v>52.7</v>
+      </c>
+      <c r="AF161">
+        <v>25.635293741444</v>
+      </c>
       <c r="AG161">
         <v>0.1385337003096474</v>
       </c>
@@ -18106,6 +18949,15 @@
       <c r="AC162">
         <v>100.93</v>
       </c>
+      <c r="AD162">
+        <v>1.6</v>
+      </c>
+      <c r="AE162">
+        <v>46.9</v>
+      </c>
+      <c r="AF162">
+        <v>25.612971300675</v>
+      </c>
       <c r="AG162">
         <v>0.1832369927057003</v>
       </c>
@@ -18213,6 +19065,15 @@
       <c r="AC163">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD163">
+        <v>-2</v>
+      </c>
+      <c r="AE163">
+        <v>41.7</v>
+      </c>
+      <c r="AF163">
+        <v>25.255379900969</v>
+      </c>
       <c r="AG163">
         <v>0.166376353668052</v>
       </c>
@@ -18320,6 +19181,15 @@
       <c r="AC164">
         <v>52.32</v>
       </c>
+      <c r="AD164">
+        <v>-1.5</v>
+      </c>
+      <c r="AE164">
+        <v>23.9</v>
+      </c>
+      <c r="AF164">
+        <v>11.275291030131</v>
+      </c>
       <c r="AG164">
         <v>0.002512519360252321</v>
       </c>
@@ -18427,6 +19297,15 @@
       <c r="AC165">
         <v>43.64</v>
       </c>
+      <c r="AD165">
+        <v>0.1</v>
+      </c>
+      <c r="AE165">
+        <v>24.4</v>
+      </c>
+      <c r="AF165">
+        <v>10.664629853207</v>
+      </c>
       <c r="AG165">
         <v>0.01976115029129286</v>
       </c>
@@ -18534,6 +19413,15 @@
       <c r="AC166">
         <v>54.13</v>
       </c>
+      <c r="AD166">
+        <v>-0.3</v>
+      </c>
+      <c r="AE166">
+        <v>22.5</v>
+      </c>
+      <c r="AF166">
+        <v>9.920365605589801</v>
+      </c>
       <c r="AG166">
         <v>0.02729375376008817</v>
       </c>
@@ -18641,6 +19529,15 @@
       <c r="AC167">
         <v>71.34</v>
       </c>
+      <c r="AD167">
+        <v>-1.1</v>
+      </c>
+      <c r="AE167">
+        <v>24.1</v>
+      </c>
+      <c r="AF167">
+        <v>10.136173560578</v>
+      </c>
       <c r="AG167">
         <v>0.03582862390022516</v>
       </c>
@@ -18748,6 +19645,15 @@
       <c r="AC168">
         <v>64.3</v>
       </c>
+      <c r="AD168">
+        <v>-2</v>
+      </c>
+      <c r="AE168">
+        <v>26.5</v>
+      </c>
+      <c r="AF168">
+        <v>7.593454585595</v>
+      </c>
       <c r="AG168">
         <v>0.0554137583224202</v>
       </c>
@@ -18855,6 +19761,15 @@
       <c r="AC169">
         <v>41.96</v>
       </c>
+      <c r="AD169">
+        <v>-2</v>
+      </c>
+      <c r="AE169">
+        <v>22.3</v>
+      </c>
+      <c r="AF169">
+        <v>7.9085409370117</v>
+      </c>
       <c r="AG169">
         <v>0.02847998171111813</v>
       </c>
@@ -18962,6 +19877,15 @@
       <c r="AC170">
         <v>70.86</v>
       </c>
+      <c r="AD170">
+        <v>-2.5</v>
+      </c>
+      <c r="AE170">
+        <v>28.4</v>
+      </c>
+      <c r="AF170">
+        <v>6.9644346691603</v>
+      </c>
       <c r="AG170">
         <v>0.06297597425574923</v>
       </c>
@@ -19069,6 +19993,15 @@
       <c r="AC171">
         <v>100.93</v>
       </c>
+      <c r="AD171">
+        <v>-1.8</v>
+      </c>
+      <c r="AE171">
+        <v>29.2</v>
+      </c>
+      <c r="AF171">
+        <v>6.5711787045591</v>
+      </c>
       <c r="AG171">
         <v>0.07010885224408266</v>
       </c>
@@ -19176,6 +20109,15 @@
       <c r="AC172">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD172">
+        <v>0.8</v>
+      </c>
+      <c r="AE172">
+        <v>27.8</v>
+      </c>
+      <c r="AF172">
+        <v>7.2247275580282</v>
+      </c>
       <c r="AG172">
         <v>0.05724440618133777</v>
       </c>
@@ -19284,13 +20226,13 @@
         <v>52.32</v>
       </c>
       <c r="AD173">
-        <v>-0.279020145129201</v>
+        <v>-0.3</v>
       </c>
       <c r="AE173">
-        <v>118.195358706681</v>
+        <v>115.9</v>
       </c>
       <c r="AF173">
-        <v>26.0434729497215</v>
+        <v>25.671429569049</v>
       </c>
       <c r="AG173">
         <v>0.2284745911354167</v>
@@ -19400,13 +20342,13 @@
         <v>43.64</v>
       </c>
       <c r="AD174">
-        <v>-0.186511889592285</v>
+        <v>-0.2</v>
       </c>
       <c r="AE174">
-        <v>115.889445482292</v>
+        <v>106.9</v>
       </c>
       <c r="AF174">
-        <v>26.8205974834377</v>
+        <v>26.289376696224</v>
       </c>
       <c r="AG174">
         <v>0.2694047184702383</v>
@@ -19516,13 +20458,13 @@
         <v>54.13</v>
       </c>
       <c r="AD175">
-        <v>0.431910680659726</v>
+        <v>0.4</v>
       </c>
       <c r="AE175">
-        <v>96.136723606367</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AF175">
-        <v>27.7646551590305</v>
+        <v>27.319581557165</v>
       </c>
       <c r="AG175">
         <v>0.2685276997434527</v>
@@ -19632,10 +20574,13 @@
         <v>71.34</v>
       </c>
       <c r="AD176">
-        <v>1.12272670993046</v>
+        <v>1.1</v>
+      </c>
+      <c r="AE176">
+        <v>88.3</v>
       </c>
       <c r="AF176">
-        <v>28.956310897592</v>
+        <v>28.637349286885</v>
       </c>
       <c r="AG176">
         <v>0.42535877034795</v>
@@ -19745,13 +20690,13 @@
         <v>64.3</v>
       </c>
       <c r="AD177">
-        <v>1.54581033725703</v>
+        <v>0.8</v>
       </c>
       <c r="AE177">
-        <v>85.7693465475141</v>
+        <v>87.7</v>
       </c>
       <c r="AF177">
-        <v>28.6261738973365</v>
+        <v>28.330537826376</v>
       </c>
       <c r="AG177">
         <v>0.3984018073166344</v>
@@ -19861,13 +20806,13 @@
         <v>41.96</v>
       </c>
       <c r="AD178">
-        <v>-2.83277548805149</v>
+        <v>-2.9</v>
       </c>
       <c r="AE178">
-        <v>97.86640033529891</v>
+        <v>101.3</v>
       </c>
       <c r="AF178">
-        <v>26.937333176305</v>
+        <v>27.260581190109</v>
       </c>
       <c r="AG178">
         <v>0.1631999444747454</v>
@@ -19976,6 +20921,15 @@
       <c r="AC179">
         <v>70.86</v>
       </c>
+      <c r="AD179">
+        <v>0.8</v>
+      </c>
+      <c r="AE179">
+        <v>86.3</v>
+      </c>
+      <c r="AF179">
+        <v>28.404488160425</v>
+      </c>
       <c r="AG179">
         <v>0.2569729556191575</v>
       </c>
@@ -20083,6 +21037,15 @@
       <c r="AC180">
         <v>100.93</v>
       </c>
+      <c r="AD180">
+        <v>0.3</v>
+      </c>
+      <c r="AE180">
+        <v>70.2</v>
+      </c>
+      <c r="AF180">
+        <v>27.378839663247</v>
+      </c>
       <c r="AG180">
         <v>0.359308873435062</v>
       </c>
@@ -20190,6 +21153,15 @@
       <c r="AC181">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD181">
+        <v>0</v>
+      </c>
+      <c r="AE181">
+        <v>66.5</v>
+      </c>
+      <c r="AF181">
+        <v>27.710601751009</v>
+      </c>
       <c r="AG181">
         <v>0.3301068042326465</v>
       </c>
@@ -20280,10 +21252,13 @@
         <v>52.32</v>
       </c>
       <c r="AD182">
-        <v>6.51808860514606</v>
+        <v>5.7</v>
+      </c>
+      <c r="AE182">
+        <v>62.2</v>
       </c>
       <c r="AF182">
-        <v>34.3048945637454</v>
+        <v>34.703991702319</v>
       </c>
       <c r="AI182">
         <v>-0.02149299999999998</v>
@@ -20369,10 +21344,13 @@
         <v>43.64</v>
       </c>
       <c r="AD183">
-        <v>1.76831309478703</v>
+        <v>3.8</v>
+      </c>
+      <c r="AE183">
+        <v>57.4</v>
       </c>
       <c r="AF183">
-        <v>28.1318859186068</v>
+        <v>29.82362319951</v>
       </c>
       <c r="AI183">
         <v>-0.01667599999999991</v>
@@ -20458,10 +21436,13 @@
         <v>54.13</v>
       </c>
       <c r="AD184">
-        <v>1.78531382277913</v>
+        <v>1.7</v>
+      </c>
+      <c r="AE184">
+        <v>56.2</v>
       </c>
       <c r="AF184">
-        <v>26.299301993104</v>
+        <v>27.212906893936</v>
       </c>
       <c r="AI184">
         <v>-0.01484400000000008</v>
@@ -20546,6 +21527,15 @@
       <c r="AC185">
         <v>71.34</v>
       </c>
+      <c r="AD185">
+        <v>1.8</v>
+      </c>
+      <c r="AE185">
+        <v>54.7</v>
+      </c>
+      <c r="AF185">
+        <v>36.049103011627</v>
+      </c>
       <c r="AI185">
         <v>-0.01304099999999997</v>
       </c>
@@ -20629,6 +21619,15 @@
       <c r="AC186">
         <v>64.3</v>
       </c>
+      <c r="AD186">
+        <v>-0.7</v>
+      </c>
+      <c r="AE186">
+        <v>57.2</v>
+      </c>
+      <c r="AF186">
+        <v>37.219744429045</v>
+      </c>
       <c r="AI186">
         <v>-0.008539999999999992</v>
       </c>
@@ -20713,10 +21712,13 @@
         <v>41.96</v>
       </c>
       <c r="AD187">
-        <v>-2.25007227885812</v>
+        <v>-3.1</v>
+      </c>
+      <c r="AE187">
+        <v>71.7</v>
       </c>
       <c r="AF187">
-        <v>28.4590147448871</v>
+        <v>34.124509721134</v>
       </c>
       <c r="AI187">
         <v>-0.004216999999999915</v>
@@ -20795,6 +21797,15 @@
       <c r="AC188">
         <v>70.86</v>
       </c>
+      <c r="AD188">
+        <v>5.5</v>
+      </c>
+      <c r="AE188">
+        <v>73</v>
+      </c>
+      <c r="AF188">
+        <v>47.453800196364</v>
+      </c>
       <c r="AI188">
         <v>0</v>
       </c>
@@ -20872,6 +21883,15 @@
       <c r="AC189">
         <v>100.93</v>
       </c>
+      <c r="AD189">
+        <v>-4.2</v>
+      </c>
+      <c r="AE189">
+        <v>64.5</v>
+      </c>
+      <c r="AF189">
+        <v>46.120831862921</v>
+      </c>
       <c r="AI189">
         <v>0.01367800000000008</v>
       </c>
@@ -20949,6 +21969,15 @@
       <c r="AC190">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD190">
+        <v>0.2</v>
+      </c>
+      <c r="AE190">
+        <v>60</v>
+      </c>
+      <c r="AF190">
+        <v>43.918553599208</v>
+      </c>
       <c r="AI190">
         <v>0.01791200000000004</v>
       </c>
@@ -21051,10 +22080,13 @@
         <v>52.32</v>
       </c>
       <c r="AD191">
-        <v>-1.90487703431729</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AE191">
+        <v>60.6</v>
       </c>
       <c r="AF191">
-        <v>19.7095456938961</v>
+        <v>20.89533788906</v>
       </c>
       <c r="AG191">
         <v>0.1462679491850953</v>
@@ -21164,10 +22196,13 @@
         <v>43.64</v>
       </c>
       <c r="AD192">
-        <v>-0.457476308554688</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AE192">
+        <v>60.2</v>
       </c>
       <c r="AF192">
-        <v>20.1305432828484</v>
+        <v>21.088067840973</v>
       </c>
       <c r="AG192">
         <v>0.1504102461140645</v>
@@ -21277,10 +22312,13 @@
         <v>54.13</v>
       </c>
       <c r="AD193">
-        <v>-0.861755832141083</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE193">
+        <v>59.9</v>
       </c>
       <c r="AF193">
-        <v>19.4078532828264</v>
+        <v>20.873035208705</v>
       </c>
       <c r="AG193">
         <v>0.1305017186056938</v>
@@ -21389,6 +22427,15 @@
       <c r="AC194">
         <v>71.34</v>
       </c>
+      <c r="AD194">
+        <v>-1.2</v>
+      </c>
+      <c r="AE194">
+        <v>60.3</v>
+      </c>
+      <c r="AF194">
+        <v>21.962418568542</v>
+      </c>
       <c r="AG194">
         <v>0.1484761584336482</v>
       </c>
@@ -21496,6 +22543,15 @@
       <c r="AC195">
         <v>64.3</v>
       </c>
+      <c r="AD195">
+        <v>-2.9</v>
+      </c>
+      <c r="AE195">
+        <v>62.1</v>
+      </c>
+      <c r="AF195">
+        <v>21.612343845576</v>
+      </c>
       <c r="AG195">
         <v>0.1655301124298607</v>
       </c>
@@ -21603,6 +22659,15 @@
       <c r="AC196">
         <v>41.96</v>
       </c>
+      <c r="AD196">
+        <v>-11.5</v>
+      </c>
+      <c r="AE196">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="AF196">
+        <v>21.611363074685</v>
+      </c>
       <c r="AG196">
         <v>0.1495272175829236</v>
       </c>
@@ -21710,6 +22775,15 @@
       <c r="AC197">
         <v>70.86</v>
       </c>
+      <c r="AD197">
+        <v>-5.4</v>
+      </c>
+      <c r="AE197">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AF197">
+        <v>21.347254713947</v>
+      </c>
       <c r="AG197">
         <v>0.1802907635768551</v>
       </c>
@@ -21817,6 +22891,15 @@
       <c r="AC198">
         <v>100.93</v>
       </c>
+      <c r="AD198">
+        <v>-2.5</v>
+      </c>
+      <c r="AE198">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AF198">
+        <v>21.30979606428</v>
+      </c>
       <c r="AG198">
         <v>0.2410425722331098</v>
       </c>
@@ -21924,6 +23007,15 @@
       <c r="AC199">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD199">
+        <v>-3.2</v>
+      </c>
+      <c r="AE199">
+        <v>75.2</v>
+      </c>
+      <c r="AF199">
+        <v>22.075761552913</v>
+      </c>
       <c r="AG199">
         <v>0.1770016776307124</v>
       </c>
@@ -22032,10 +23124,13 @@
         <v>52.32</v>
       </c>
       <c r="AD200">
-        <v>-3.11885188192299</v>
+        <v>-3.9</v>
+      </c>
+      <c r="AE200">
+        <v>51</v>
       </c>
       <c r="AF200">
-        <v>18.3681968714647</v>
+        <v>22.69858412115</v>
       </c>
       <c r="AG200">
         <v>0.609777513848424</v>
@@ -22145,10 +23240,13 @@
         <v>43.64</v>
       </c>
       <c r="AD201">
-        <v>-1.62118179871436</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE201">
+        <v>55</v>
       </c>
       <c r="AF201">
-        <v>19.1915888785393</v>
+        <v>23.841111867853</v>
       </c>
       <c r="AG201">
         <v>0.689670825989018</v>
@@ -22258,10 +23356,13 @@
         <v>54.13</v>
       </c>
       <c r="AD202">
-        <v>-0.845266946151578</v>
+        <v>-1</v>
+      </c>
+      <c r="AE202">
+        <v>52.5</v>
       </c>
       <c r="AF202">
-        <v>19.4469058462512</v>
+        <v>23.984132267382</v>
       </c>
       <c r="AG202">
         <v>0.6442564720267496</v>
@@ -22371,10 +23472,13 @@
         <v>71.34</v>
       </c>
       <c r="AD203">
-        <v>-2.11318831516787</v>
+        <v>-2.1</v>
+      </c>
+      <c r="AE203">
+        <v>52.2</v>
       </c>
       <c r="AF203">
-        <v>18.3342427407296</v>
+        <v>22.831150123991</v>
       </c>
       <c r="AG203">
         <v>0.6515684491594819</v>
@@ -22484,13 +23588,13 @@
         <v>64.3</v>
       </c>
       <c r="AD204">
-        <v>-1.61318460276811</v>
+        <v>-2.3</v>
       </c>
       <c r="AE204">
-        <v>41.3273940627237</v>
+        <v>51.9</v>
       </c>
       <c r="AF204">
-        <v>18.5191670625259</v>
+        <v>22.997031481126</v>
       </c>
       <c r="AG204">
         <v>0.5072426124578199</v>
@@ -22600,13 +23704,13 @@
         <v>41.96</v>
       </c>
       <c r="AD205">
-        <v>-3.63899768692085</v>
+        <v>-4.3</v>
       </c>
       <c r="AE205">
-        <v>45.8373464150183</v>
+        <v>58.5</v>
       </c>
       <c r="AF205">
-        <v>18.6445328298003</v>
+        <v>23.492741374543</v>
       </c>
       <c r="AG205">
         <v>0.3959599241498478</v>
@@ -22716,13 +23820,13 @@
         <v>70.86</v>
       </c>
       <c r="AD206">
-        <v>-3.32386358587642</v>
+        <v>-3.7</v>
       </c>
       <c r="AE206">
-        <v>44.8609558065004</v>
+        <v>56.7</v>
       </c>
       <c r="AF206">
-        <v>18.3430886486889</v>
+        <v>22.937162240865</v>
       </c>
       <c r="AG206">
         <v>0.5464290055379426</v>
@@ -22832,13 +23936,13 @@
         <v>100.93</v>
       </c>
       <c r="AD207">
-        <v>-4.30934820805177</v>
+        <v>-4.3</v>
       </c>
       <c r="AE207">
-        <v>43.9694401566719</v>
+        <v>53.8</v>
       </c>
       <c r="AF207">
-        <v>19.2711611449441</v>
+        <v>24.186707450403</v>
       </c>
       <c r="AG207">
         <v>0.9126818206176207</v>
@@ -22948,13 +24052,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD208">
-        <v>-4.18573429010021</v>
+        <v>-4.3</v>
       </c>
       <c r="AE208">
-        <v>45.055380246523</v>
+        <v>52.8</v>
       </c>
       <c r="AF208">
-        <v>19.0449981034342</v>
+        <v>24.284482760082</v>
       </c>
       <c r="AG208">
         <v>0.5807002676063495</v>
@@ -23064,10 +24168,13 @@
         <v>52.32</v>
       </c>
       <c r="AD209">
-        <v>-0.583201904246945</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE209">
+        <v>28.9</v>
       </c>
       <c r="AF209">
-        <v>16.7280500642775</v>
+        <v>23.808754837654</v>
       </c>
       <c r="AG209">
         <v>0.03759231048167294</v>
@@ -23177,10 +24284,13 @@
         <v>43.64</v>
       </c>
       <c r="AD210">
-        <v>-0.586115239305093</v>
+        <v>-1.9</v>
+      </c>
+      <c r="AE210">
+        <v>30.9</v>
       </c>
       <c r="AF210">
-        <v>17.3827290426753</v>
+        <v>24.916096353104</v>
       </c>
       <c r="AG210">
         <v>0.04099477282534929</v>
@@ -23290,10 +24400,13 @@
         <v>54.13</v>
       </c>
       <c r="AD211">
-        <v>-0.587948185967631</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE211">
+        <v>34.7</v>
       </c>
       <c r="AF211">
-        <v>17.8258154423666</v>
+        <v>25.552242979269</v>
       </c>
       <c r="AG211">
         <v>0.0270324770713714</v>
@@ -23403,10 +24516,13 @@
         <v>71.34</v>
       </c>
       <c r="AD212">
-        <v>-1.93864925584338</v>
+        <v>-4.3</v>
+      </c>
+      <c r="AE212">
+        <v>39.1</v>
       </c>
       <c r="AF212">
-        <v>16.9620048772188</v>
+        <v>23.33984371015</v>
       </c>
       <c r="AG212">
         <v>0.04831572401735952</v>
@@ -23516,10 +24632,13 @@
         <v>64.3</v>
       </c>
       <c r="AD213">
-        <v>0.257605882352745</v>
+        <v>-1.1</v>
+      </c>
+      <c r="AE213">
+        <v>44.2</v>
       </c>
       <c r="AF213">
-        <v>18.8466464658517</v>
+        <v>26.532048087316</v>
       </c>
       <c r="AG213">
         <v>0.05479898347597643</v>
@@ -23629,10 +24748,13 @@
         <v>41.96</v>
       </c>
       <c r="AD214">
-        <v>-1.04830949642303</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE214">
+        <v>49.2</v>
       </c>
       <c r="AF214">
-        <v>18.4889521054397</v>
+        <v>26.351337493527</v>
       </c>
       <c r="AG214">
         <v>0.0277834977957687</v>
@@ -23742,10 +24864,13 @@
         <v>70.86</v>
       </c>
       <c r="AD215">
-        <v>-0.7309295555961109</v>
+        <v>-1.3</v>
+      </c>
+      <c r="AE215">
+        <v>48.4</v>
       </c>
       <c r="AF215">
-        <v>20.5214773588265</v>
+        <v>28.745150540457</v>
       </c>
       <c r="AG215">
         <v>0.05738071631222737</v>
@@ -23855,10 +24980,13 @@
         <v>100.93</v>
       </c>
       <c r="AD216">
-        <v>1.29650798278862</v>
+        <v>0.6</v>
+      </c>
+      <c r="AE216">
+        <v>45.9</v>
       </c>
       <c r="AF216">
-        <v>21.5053904884945</v>
+        <v>29.222204030159</v>
       </c>
       <c r="AG216">
         <v>0.09165079808209134</v>
@@ -23968,10 +25096,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD217">
-        <v>2.65900583968355</v>
+        <v>2.3</v>
+      </c>
+      <c r="AE217">
+        <v>42.4</v>
       </c>
       <c r="AF217">
-        <v>21.5078651205282</v>
+        <v>28.308983963576</v>
       </c>
       <c r="AG217">
         <v>0.05035375620632591</v>
@@ -24081,10 +25212,13 @@
         <v>52.32</v>
       </c>
       <c r="AD218">
-        <v>-4.02680842956423</v>
+        <v>-2.2</v>
+      </c>
+      <c r="AE218">
+        <v>34.1</v>
       </c>
       <c r="AF218">
-        <v>12.8142247025193</v>
+        <v>19.188490194429</v>
       </c>
       <c r="AG218">
         <v>0.5202316416106539</v>
@@ -24194,10 +25328,13 @@
         <v>43.64</v>
       </c>
       <c r="AD219">
-        <v>-3.35818851413364</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE219">
+        <v>34</v>
       </c>
       <c r="AF219">
-        <v>12.6851464174451</v>
+        <v>19.489345116328</v>
       </c>
       <c r="AG219">
         <v>0.5197897252299571</v>
@@ -24307,10 +25444,13 @@
         <v>54.13</v>
       </c>
       <c r="AD220">
-        <v>-2.8001836747991</v>
+        <v>-1.8</v>
+      </c>
+      <c r="AE220">
+        <v>34.3</v>
       </c>
       <c r="AF220">
-        <v>13.4436093989475</v>
+        <v>19.341593374501</v>
       </c>
       <c r="AG220">
         <v>0.5267592575473012</v>
@@ -24420,10 +25560,13 @@
         <v>71.34</v>
       </c>
       <c r="AD221">
-        <v>-2.62383159040578</v>
+        <v>-2.8</v>
+      </c>
+      <c r="AE221">
+        <v>36.3</v>
       </c>
       <c r="AF221">
-        <v>13.1867976123542</v>
+        <v>18.948854234583</v>
       </c>
       <c r="AG221">
         <v>0.5476271963469707</v>
@@ -24533,10 +25676,13 @@
         <v>64.3</v>
       </c>
       <c r="AD222">
-        <v>-5.58323163423213</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AE222">
+        <v>42.5</v>
       </c>
       <c r="AF222">
-        <v>11.8306567007958</v>
+        <v>17.745742362238</v>
       </c>
       <c r="AG222">
         <v>0.5794281360619824</v>
@@ -24646,10 +25792,13 @@
         <v>41.96</v>
       </c>
       <c r="AD223">
-        <v>-8.237216127450161</v>
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="AE223">
+        <v>62.4</v>
       </c>
       <c r="AF223">
-        <v>11.5147047797974</v>
+        <v>17.340039630612</v>
       </c>
       <c r="AG223">
         <v>0.328172976061916</v>
@@ -24759,10 +25908,13 @@
         <v>70.86</v>
       </c>
       <c r="AD224">
-        <v>-6.64214833219757</v>
+        <v>-6.4</v>
+      </c>
+      <c r="AE224">
+        <v>58</v>
       </c>
       <c r="AF224">
-        <v>11.1554031256111</v>
+        <v>17.30181626401</v>
       </c>
       <c r="AG224">
         <v>0.4460314594719466</v>
@@ -24871,6 +26023,15 @@
       <c r="AC225">
         <v>100.93</v>
       </c>
+      <c r="AD225">
+        <v>-4</v>
+      </c>
+      <c r="AE225">
+        <v>56.2</v>
+      </c>
+      <c r="AF225">
+        <v>17.366397474296</v>
+      </c>
       <c r="AG225">
         <v>0.6199293258299089</v>
       </c>
@@ -24978,6 +26139,15 @@
       <c r="AC226">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD226">
+        <v>-3.9</v>
+      </c>
+      <c r="AE226">
+        <v>54.4</v>
+      </c>
+      <c r="AF226">
+        <v>17.48183179073</v>
+      </c>
       <c r="AG226">
         <v>0.5752674105252583</v>
       </c>
@@ -25086,13 +26256,13 @@
         <v>52.32</v>
       </c>
       <c r="AD227">
-        <v>-2.40967246414886</v>
+        <v>-2</v>
       </c>
       <c r="AE227">
-        <v>22.865554469277</v>
+        <v>23.7</v>
       </c>
       <c r="AF227">
-        <v>19.679565807863</v>
+        <v>19.973412793973</v>
       </c>
       <c r="AG227">
         <v>0.2751526610515737</v>
@@ -25202,13 +26372,13 @@
         <v>43.64</v>
       </c>
       <c r="AD228">
-        <v>-1.76643473125096</v>
+        <v>-2.1</v>
       </c>
       <c r="AE228">
-        <v>23.7062564342415</v>
+        <v>23.9</v>
       </c>
       <c r="AF228">
-        <v>18.2765652206734</v>
+        <v>18.386249957765</v>
       </c>
       <c r="AG228">
         <v>0.3256002683712015</v>
@@ -25318,13 +26488,13 @@
         <v>54.13</v>
       </c>
       <c r="AD229">
-        <v>-3.41282464124008</v>
+        <v>-2.8</v>
       </c>
       <c r="AE229">
-        <v>24.7483395120072</v>
+        <v>24.8</v>
       </c>
       <c r="AF229">
-        <v>17.8234033989894</v>
+        <v>17.834306954131</v>
       </c>
       <c r="AG229">
         <v>0.3144286352107324</v>
@@ -25434,13 +26604,13 @@
         <v>71.34</v>
       </c>
       <c r="AD230">
-        <v>-2.10453576583639</v>
+        <v>-1.9</v>
       </c>
       <c r="AE230">
-        <v>25.7290009576063</v>
+        <v>25.7</v>
       </c>
       <c r="AF230">
-        <v>19.0379642707319</v>
+        <v>19.02416548543</v>
       </c>
       <c r="AG230">
         <v>0.3225366394704361</v>
@@ -25550,13 +26720,13 @@
         <v>64.3</v>
       </c>
       <c r="AD231">
-        <v>-2.13920942147812</v>
+        <v>-1.4</v>
       </c>
       <c r="AE231">
-        <v>26.5266050304096</v>
+        <v>26.5</v>
       </c>
       <c r="AF231">
-        <v>19.5290026661565</v>
+        <v>19.45212028537</v>
       </c>
       <c r="AG231">
         <v>0.3042837054632178</v>
@@ -25666,13 +26836,13 @@
         <v>41.96</v>
       </c>
       <c r="AD232">
-        <v>-9.665793376200011</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE232">
-        <v>34.7649150438361</v>
+        <v>34.3</v>
       </c>
       <c r="AF232">
-        <v>18.0501223065786</v>
+        <v>17.484578092332</v>
       </c>
       <c r="AG232">
         <v>0.1547306627728198</v>
@@ -25782,13 +26952,13 @@
         <v>70.86</v>
       </c>
       <c r="AD233">
-        <v>-3.24203590484588</v>
+        <v>-2.5</v>
       </c>
       <c r="AE233">
-        <v>35.2492265648321</v>
+        <v>35.5</v>
       </c>
       <c r="AF233">
-        <v>20.6771966687553</v>
+        <v>20.637421925374</v>
       </c>
       <c r="AG233">
         <v>0.3208627151578587</v>
@@ -25897,6 +27067,15 @@
       <c r="AC234">
         <v>100.93</v>
       </c>
+      <c r="AD234">
+        <v>-1.4</v>
+      </c>
+      <c r="AE234">
+        <v>33.5</v>
+      </c>
+      <c r="AF234">
+        <v>21.721254903689</v>
+      </c>
       <c r="AG234">
         <v>0.3996484754000921</v>
       </c>
@@ -26004,6 +27183,15 @@
       <c r="AC235">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD235">
+        <v>-2.7</v>
+      </c>
+      <c r="AE235">
+        <v>32.4</v>
+      </c>
+      <c r="AF235">
+        <v>19.31675130698</v>
+      </c>
       <c r="AG235">
         <v>0.3281661013348033</v>
       </c>
@@ -26087,6 +27275,15 @@
       <c r="AC236">
         <v>52.32</v>
       </c>
+      <c r="AD236">
+        <v>-2.1</v>
+      </c>
+      <c r="AE236">
+        <v>52.7</v>
+      </c>
+      <c r="AF236">
+        <v>19.397136882288</v>
+      </c>
       <c r="AI236">
         <v>0.1805310000000001</v>
       </c>
@@ -26164,6 +27361,15 @@
       <c r="AC237">
         <v>43.64</v>
       </c>
+      <c r="AD237">
+        <v>-1.8</v>
+      </c>
+      <c r="AE237">
+        <v>49.9</v>
+      </c>
+      <c r="AF237">
+        <v>19.132555811352</v>
+      </c>
       <c r="AI237">
         <v>0.156406</v>
       </c>
@@ -26241,6 +27447,15 @@
       <c r="AC238">
         <v>54.13</v>
       </c>
+      <c r="AD238">
+        <v>-1.1</v>
+      </c>
+      <c r="AE238">
+        <v>51.2</v>
+      </c>
+      <c r="AF238">
+        <v>20.817029075596</v>
+      </c>
       <c r="AI238">
         <v>0.148888</v>
       </c>
@@ -26324,6 +27539,15 @@
       <c r="AC239">
         <v>71.34</v>
       </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>52.4</v>
+      </c>
+      <c r="AF239">
+        <v>22.153685052568</v>
+      </c>
       <c r="AI239">
         <v>0.1425739999999999</v>
       </c>
@@ -26407,6 +27631,15 @@
       <c r="AC240">
         <v>64.3</v>
       </c>
+      <c r="AD240">
+        <v>1.9</v>
+      </c>
+      <c r="AE240">
+        <v>48.8</v>
+      </c>
+      <c r="AF240">
+        <v>22.967000795425</v>
+      </c>
       <c r="AI240">
         <v>0.1522709999999999</v>
       </c>
@@ -26490,6 +27723,15 @@
       <c r="AC241">
         <v>41.96</v>
       </c>
+      <c r="AD241">
+        <v>-0.6</v>
+      </c>
+      <c r="AE241">
+        <v>50.2</v>
+      </c>
+      <c r="AF241">
+        <v>20.811395215793</v>
+      </c>
       <c r="AI241">
         <v>0.179935</v>
       </c>
@@ -26567,6 +27809,15 @@
       <c r="AC242">
         <v>70.86</v>
       </c>
+      <c r="AD242">
+        <v>-0.3</v>
+      </c>
+      <c r="AE242">
+        <v>48.9</v>
+      </c>
+      <c r="AF242">
+        <v>20.9685119887</v>
+      </c>
       <c r="AI242">
         <v>0.157776</v>
       </c>
@@ -26644,6 +27895,15 @@
       <c r="AC243">
         <v>100.93</v>
       </c>
+      <c r="AD243">
+        <v>1.8</v>
+      </c>
+      <c r="AE243">
+        <v>16.7</v>
+      </c>
+      <c r="AF243">
+        <v>22.360481959037</v>
+      </c>
       <c r="AI243">
         <v>0.1662939999999999</v>
       </c>
@@ -26721,6 +27981,15 @@
       <c r="AC244">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD244">
+        <v>0.3</v>
+      </c>
+      <c r="AE244">
+        <v>16.6</v>
+      </c>
+      <c r="AF244">
+        <v>22.499683210137</v>
+      </c>
       <c r="AI244">
         <v>0.15856</v>
       </c>
@@ -26823,10 +28092,13 @@
         <v>52.32</v>
       </c>
       <c r="AD245">
-        <v>-0.409459349125011</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE245">
+        <v>18.6</v>
       </c>
       <c r="AF245">
-        <v>17.358483664503</v>
+        <v>17.540823887257</v>
       </c>
       <c r="AG245">
         <v>0.03535054451848996</v>
@@ -26936,10 +28208,13 @@
         <v>43.64</v>
       </c>
       <c r="AD246">
-        <v>0.172164834815949</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE246">
+        <v>19.4</v>
       </c>
       <c r="AF246">
-        <v>16.8648796628618</v>
+        <v>17.325488368871</v>
       </c>
       <c r="AG246">
         <v>0.05849336057717551</v>
@@ -27049,10 +28324,13 @@
         <v>54.13</v>
       </c>
       <c r="AD247">
-        <v>-0.435394589337389</v>
+        <v>-0.4</v>
+      </c>
+      <c r="AE247">
+        <v>19.8</v>
       </c>
       <c r="AF247">
-        <v>17.4431333716598</v>
+        <v>17.618199707326</v>
       </c>
       <c r="AG247">
         <v>0.1174756752080819</v>
@@ -27162,10 +28440,13 @@
         <v>71.34</v>
       </c>
       <c r="AD248">
-        <v>-1.0181187376389</v>
+        <v>-1</v>
+      </c>
+      <c r="AE248">
+        <v>22.3</v>
       </c>
       <c r="AF248">
-        <v>17.3317797902031</v>
+        <v>17.473814176292</v>
       </c>
       <c r="AG248">
         <v>0.1425405054541917</v>
@@ -27275,10 +28556,13 @@
         <v>64.3</v>
       </c>
       <c r="AD249">
-        <v>-2.38557658966851</v>
+        <v>-2.4</v>
+      </c>
+      <c r="AE249">
+        <v>25.8</v>
       </c>
       <c r="AF249">
-        <v>17.5461211473444</v>
+        <v>17.679066979882</v>
       </c>
       <c r="AG249">
         <v>0.1502305633689002</v>
@@ -27388,10 +28672,13 @@
         <v>41.96</v>
       </c>
       <c r="AD250">
-        <v>-5.76161004932235</v>
+        <v>-5.7</v>
+      </c>
+      <c r="AE250">
+        <v>36.9</v>
       </c>
       <c r="AF250">
-        <v>16.7319714533199</v>
+        <v>16.912598843579</v>
       </c>
       <c r="AG250">
         <v>0.09492718247131303</v>
@@ -27501,10 +28788,13 @@
         <v>70.86</v>
       </c>
       <c r="AD251">
-        <v>-3.3855465837744</v>
+        <v>-3.4</v>
+      </c>
+      <c r="AE251">
+        <v>37.5</v>
       </c>
       <c r="AF251">
-        <v>16.8868520553405</v>
+        <v>17.060822883301</v>
       </c>
       <c r="AG251">
         <v>0.2331577763995551</v>
@@ -27614,10 +28904,13 @@
         <v>100.93</v>
       </c>
       <c r="AD252">
-        <v>-2.63772983075328</v>
+        <v>-2.6</v>
+      </c>
+      <c r="AE252">
+        <v>40.6</v>
       </c>
       <c r="AF252">
-        <v>17.3957386518946</v>
+        <v>17.568820278653</v>
       </c>
       <c r="AG252">
         <v>0.2503260212487441</v>
@@ -27727,10 +29020,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD253">
-        <v>-3.81724810364245</v>
+        <v>-3.8</v>
+      </c>
+      <c r="AE253">
+        <v>41</v>
       </c>
       <c r="AF253">
-        <v>17.5729662059172</v>
+        <v>17.657296830408</v>
       </c>
       <c r="AG253">
         <v>0.2179783652738688</v>
@@ -27840,13 +29136,13 @@
         <v>52.32</v>
       </c>
       <c r="AD254">
-        <v>-1.30542832718732</v>
+        <v>-3.6</v>
       </c>
       <c r="AE254">
-        <v>51.2784032678648</v>
+        <v>73.5</v>
       </c>
       <c r="AF254">
-        <v>20.8150431413365</v>
+        <v>23.475442198741</v>
       </c>
       <c r="AG254">
         <v>0.1661485828646336</v>
@@ -27956,13 +29252,13 @@
         <v>43.64</v>
       </c>
       <c r="AD255">
-        <v>-0.18585473187881</v>
+        <v>-3.1</v>
       </c>
       <c r="AE255">
-        <v>52.0656561693955</v>
+        <v>75.2</v>
       </c>
       <c r="AF255">
-        <v>23.6888663993406</v>
+        <v>24.357427428073</v>
       </c>
       <c r="AG255">
         <v>0.1903584250202927</v>
@@ -28072,13 +29368,13 @@
         <v>54.13</v>
       </c>
       <c r="AD256">
-        <v>-0.5756729081453</v>
+        <v>-2.5</v>
       </c>
       <c r="AE256">
-        <v>55.248518820306</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AF256">
-        <v>25.0974253686368</v>
+        <v>25.563798925946</v>
       </c>
       <c r="AG256">
         <v>0.1734023782230545</v>
@@ -28188,13 +29484,13 @@
         <v>71.34</v>
       </c>
       <c r="AD257">
-        <v>-0.620271820482421</v>
+        <v>-2.7</v>
       </c>
       <c r="AE257">
-        <v>52.2142820084663</v>
+        <v>77</v>
       </c>
       <c r="AF257">
-        <v>24.9488391040262</v>
+        <v>24.89983636259</v>
       </c>
       <c r="AG257">
         <v>0.1876659072047775</v>
@@ -28304,13 +29600,13 @@
         <v>64.3</v>
       </c>
       <c r="AD258">
-        <v>-0.889843213494666</v>
+        <v>-3.1</v>
       </c>
       <c r="AE258">
-        <v>53.8790393562178</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AF258">
-        <v>24.1024004190298</v>
+        <v>24.710748127642</v>
       </c>
       <c r="AG258">
         <v>0.2311784088477672</v>
@@ -28420,13 +29716,13 @@
         <v>41.96</v>
       </c>
       <c r="AD259">
-        <v>-10.1231120985796</v>
+        <v>-8.1</v>
       </c>
       <c r="AE259">
-        <v>70.3842794023881</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AF259">
-        <v>23.5586663397695</v>
+        <v>24.560865672947</v>
       </c>
       <c r="AG259">
         <v>0.1625644623022341</v>
@@ -28536,13 +29832,13 @@
         <v>70.86</v>
       </c>
       <c r="AD260">
-        <v>-2.89913556178843</v>
+        <v>-5.5</v>
       </c>
       <c r="AE260">
-        <v>66.4690525886664</v>
+        <v>88</v>
       </c>
       <c r="AF260">
-        <v>28.5747339991475</v>
+        <v>25.557972301198</v>
       </c>
       <c r="AG260">
         <v>0.2386546551606226</v>
@@ -28652,13 +29948,13 @@
         <v>100.93</v>
       </c>
       <c r="AD261">
-        <v>-2.727005734525</v>
+        <v>-2.7</v>
       </c>
       <c r="AE261">
-        <v>74.0361190983906</v>
+        <v>83.7</v>
       </c>
       <c r="AF261">
-        <v>28.191923971419</v>
+        <v>25.976506480758</v>
       </c>
       <c r="AG261">
         <v>0.3452747394036751</v>
@@ -28768,13 +30064,13 @@
         <v>82.48999999999999</v>
       </c>
       <c r="AD262">
-        <v>-2.81757812242829</v>
+        <v>-4.7</v>
       </c>
       <c r="AE262">
-        <v>102.190173433284</v>
+        <v>85</v>
       </c>
       <c r="AF262">
-        <v>26.0511443955415</v>
+        <v>25.838070090771</v>
       </c>
       <c r="AG262">
         <v>0.290760709544443</v>
@@ -28865,6 +30161,15 @@
       <c r="AC263">
         <v>52.32</v>
       </c>
+      <c r="AD263">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="AE263">
+        <v>41.2</v>
+      </c>
+      <c r="AF263">
+        <v>21.589644370223</v>
+      </c>
       <c r="AI263">
         <v>0.6916370000000001</v>
       </c>
@@ -28948,6 +30253,15 @@
       <c r="AC264">
         <v>43.64</v>
       </c>
+      <c r="AD264">
+        <v>-10.2</v>
+      </c>
+      <c r="AE264">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AF264">
+        <v>17.722771667668</v>
+      </c>
       <c r="AI264">
         <v>0.453898</v>
       </c>
@@ -29031,6 +30345,15 @@
       <c r="AC265">
         <v>54.13</v>
       </c>
+      <c r="AD265">
+        <v>-8.6</v>
+      </c>
+      <c r="AE265">
+        <v>73</v>
+      </c>
+      <c r="AF265">
+        <v>20.119897619026</v>
+      </c>
       <c r="AI265">
         <v>0.2438069999999999</v>
       </c>
@@ -29114,6 +30437,15 @@
       <c r="AC266">
         <v>71.34</v>
       </c>
+      <c r="AD266">
+        <v>-8.6</v>
+      </c>
+      <c r="AE266">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AF266">
+        <v>20.90257966034</v>
+      </c>
       <c r="AI266">
         <v>0.246162</v>
       </c>
@@ -29197,6 +30529,15 @@
       <c r="AC267">
         <v>64.3</v>
       </c>
+      <c r="AD267">
+        <v>-20.2</v>
+      </c>
+      <c r="AE267">
+        <v>84</v>
+      </c>
+      <c r="AF267">
+        <v>20.276977077242</v>
+      </c>
       <c r="AI267">
         <v>0.2644859999999999</v>
       </c>
@@ -29280,6 +30621,15 @@
       <c r="AC268">
         <v>41.96</v>
       </c>
+      <c r="AD268">
+        <v>-12</v>
+      </c>
+      <c r="AE268">
+        <v>146.4</v>
+      </c>
+      <c r="AF268">
+        <v>18.249217085754</v>
+      </c>
       <c r="AI268">
         <v>0.43801</v>
       </c>
@@ -29357,6 +30707,15 @@
       <c r="AC269">
         <v>70.86</v>
       </c>
+      <c r="AD269">
+        <v>-5.7</v>
+      </c>
+      <c r="AE269">
+        <v>115.8</v>
+      </c>
+      <c r="AF269">
+        <v>26.361081996692</v>
+      </c>
       <c r="AI269">
         <v>0.175181</v>
       </c>
@@ -29434,6 +30793,15 @@
       <c r="AC270">
         <v>100.93</v>
       </c>
+      <c r="AD270">
+        <v>-2.6</v>
+      </c>
+      <c r="AE270">
+        <v>111.7</v>
+      </c>
+      <c r="AF270">
+        <v>25.639811032126</v>
+      </c>
       <c r="AI270">
         <v>0.04551400000000005</v>
       </c>
@@ -29511,6 +30879,15 @@
       <c r="AC271">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD271">
+        <v>-1.7</v>
+      </c>
+      <c r="AE271">
+        <v>97.7</v>
+      </c>
+      <c r="AF271">
+        <v>27.209676284948</v>
+      </c>
       <c r="AI271">
         <v>0.2947609999999999</v>
       </c>
@@ -29613,10 +30990,13 @@
         <v>52.32</v>
       </c>
       <c r="AD272">
-        <v>-1.31681775954333</v>
+        <v>-7.4</v>
+      </c>
+      <c r="AE272">
+        <v>43.2</v>
       </c>
       <c r="AF272">
-        <v>35.8629396068095</v>
+        <v>26.761601220404</v>
       </c>
       <c r="AG272">
         <v>2.028157475950026</v>
@@ -29726,10 +31106,13 @@
         <v>43.64</v>
       </c>
       <c r="AD273">
-        <v>-3.90638326389358</v>
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AE273">
+        <v>53.3</v>
       </c>
       <c r="AF273">
-        <v>31.2390699061462</v>
+        <v>21.387847319011</v>
       </c>
       <c r="AG273">
         <v>1.616877699388077</v>
@@ -29839,10 +31222,13 @@
         <v>54.13</v>
       </c>
       <c r="AD274">
-        <v>-6.40135244377081</v>
+        <v>-10.5</v>
+      </c>
+      <c r="AE274">
+        <v>57.2</v>
       </c>
       <c r="AF274">
-        <v>28.7268899879201</v>
+        <v>20.487756070265</v>
       </c>
       <c r="AG274">
         <v>1.578568247367318</v>
@@ -29952,10 +31338,13 @@
         <v>71.34</v>
       </c>
       <c r="AD275">
-        <v>-3.34668595354151</v>
+        <v>-5.9</v>
+      </c>
+      <c r="AE275">
+        <v>58.1</v>
       </c>
       <c r="AF275">
-        <v>29.5653403216796</v>
+        <v>24.313605927755</v>
       </c>
       <c r="AG275">
         <v>1.604963512678892</v>
@@ -30065,10 +31454,13 @@
         <v>64.3</v>
       </c>
       <c r="AD276">
-        <v>-10.6222634278285</v>
+        <v>-3.7</v>
+      </c>
+      <c r="AE276">
+        <v>62.9</v>
       </c>
       <c r="AF276">
-        <v>24.2635768758849</v>
+        <v>27.285778597629</v>
       </c>
       <c r="AG276">
         <v>1.361651655999269</v>
@@ -30177,6 +31569,15 @@
       <c r="AC277">
         <v>41.96</v>
       </c>
+      <c r="AD277">
+        <v>-11.8</v>
+      </c>
+      <c r="AE277">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AF277">
+        <v>23.274604946051</v>
+      </c>
       <c r="AG277">
         <v>1.310573340877859</v>
       </c>
@@ -30284,6 +31685,15 @@
       <c r="AC278">
         <v>70.86</v>
       </c>
+      <c r="AD278">
+        <v>-8.4</v>
+      </c>
+      <c r="AE278">
+        <v>80.2</v>
+      </c>
+      <c r="AF278">
+        <v>22.996472491453</v>
+      </c>
       <c r="AG278">
         <v>1.298569481201671</v>
       </c>
@@ -30391,6 +31801,15 @@
       <c r="AC279">
         <v>100.93</v>
       </c>
+      <c r="AD279">
+        <v>1</v>
+      </c>
+      <c r="AE279">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AF279">
+        <v>29.222655520854</v>
+      </c>
       <c r="AG279">
         <v>1.418571512548388</v>
       </c>
@@ -30498,6 +31917,15 @@
       <c r="AC280">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD280">
+        <v>-1.2</v>
+      </c>
+      <c r="AE280">
+        <v>78.2</v>
+      </c>
+      <c r="AF280">
+        <v>31.228110301129</v>
+      </c>
       <c r="AG280">
         <v>1.211500267054534</v>
       </c>
@@ -30605,11 +32033,14 @@
       <c r="AC281">
         <v>52.32</v>
       </c>
+      <c r="AD281">
+        <v>-1.9</v>
+      </c>
       <c r="AE281">
-        <v>47.2765585126953</v>
+        <v>57.8</v>
       </c>
       <c r="AF281">
-        <v>28.1236212798537</v>
+        <v>26.494087204264</v>
       </c>
       <c r="AG281">
         <v>0.00880014618397759</v>
@@ -30718,11 +32149,14 @@
       <c r="AC282">
         <v>43.64</v>
       </c>
+      <c r="AD282">
+        <v>-2.7</v>
+      </c>
       <c r="AE282">
-        <v>46.4584676105582</v>
+        <v>56.4</v>
       </c>
       <c r="AF282">
-        <v>33.1100434313663</v>
+        <v>26.986566883822</v>
       </c>
       <c r="AG282">
         <v>0.01876950507112284</v>
@@ -30831,11 +32265,14 @@
       <c r="AC283">
         <v>54.13</v>
       </c>
+      <c r="AD283">
+        <v>-2.5</v>
+      </c>
       <c r="AE283">
-        <v>45.0744196869827</v>
+        <v>55.8</v>
       </c>
       <c r="AF283">
-        <v>29.7075109246204</v>
+        <v>27.217151511328</v>
       </c>
       <c r="AG283">
         <v>0.02061962035927803</v>
@@ -30944,11 +32381,14 @@
       <c r="AC284">
         <v>71.34</v>
       </c>
+      <c r="AD284">
+        <v>-1.9</v>
+      </c>
       <c r="AE284">
-        <v>47.341475064134</v>
+        <v>57.9</v>
       </c>
       <c r="AF284">
-        <v>31.3533848442693</v>
+        <v>28.454606221472</v>
       </c>
       <c r="AG284">
         <v>0.09579150785841301</v>
@@ -31057,11 +32497,14 @@
       <c r="AC285">
         <v>64.3</v>
       </c>
+      <c r="AD285">
+        <v>-2.7</v>
+      </c>
       <c r="AE285">
-        <v>50.1314491818532</v>
+        <v>59.6</v>
       </c>
       <c r="AF285">
-        <v>30.6396644583495</v>
+        <v>27.871529158277</v>
       </c>
       <c r="AG285">
         <v>0.1891882650418396</v>
@@ -31170,11 +32613,14 @@
       <c r="AC286">
         <v>41.96</v>
       </c>
+      <c r="AD286">
+        <v>-4.6</v>
+      </c>
       <c r="AE286">
-        <v>60.4014181135621</v>
+        <v>68.2</v>
       </c>
       <c r="AF286">
-        <v>30.8483157882517</v>
+        <v>28.152322040966</v>
       </c>
       <c r="AG286">
         <v>0.1325931364910255</v>
@@ -31283,11 +32729,14 @@
       <c r="AC287">
         <v>70.86</v>
       </c>
+      <c r="AD287">
+        <v>-2.6</v>
+      </c>
       <c r="AE287">
-        <v>58.113052857752</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF287">
-        <v>29.1017733541657</v>
+        <v>27.600825237438</v>
       </c>
       <c r="AG287">
         <v>0.3647370911312941</v>
@@ -31396,11 +32845,14 @@
       <c r="AC288">
         <v>100.93</v>
       </c>
+      <c r="AD288">
+        <v>-2.5</v>
+      </c>
       <c r="AE288">
-        <v>54.2372595323111</v>
+        <v>59.4</v>
       </c>
       <c r="AF288">
-        <v>29.6888696320693</v>
+        <v>27.225830232134</v>
       </c>
       <c r="AG288">
         <v>0.4442138399730595</v>
@@ -31509,11 +32961,14 @@
       <c r="AC289">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD289">
+        <v>-3.1</v>
+      </c>
       <c r="AE289">
-        <v>62.3670975853084</v>
+        <v>63</v>
       </c>
       <c r="AF289">
-        <v>30.8302778846325</v>
+        <v>26.96831113044</v>
       </c>
       <c r="AG289">
         <v>0.2503279557553382</v>
@@ -31623,10 +33078,13 @@
         <v>52.32</v>
       </c>
       <c r="AD290">
-        <v>-1.23463766068654</v>
+        <v>-2</v>
+      </c>
+      <c r="AE290">
+        <v>76</v>
       </c>
       <c r="AF290">
-        <v>24.4295333615859</v>
+        <v>25.574785015284</v>
       </c>
       <c r="AG290">
         <v>0.375300181165998</v>
@@ -31736,10 +33194,13 @@
         <v>43.64</v>
       </c>
       <c r="AD291">
-        <v>2.08176037696373</v>
+        <v>0</v>
+      </c>
+      <c r="AE291">
+        <v>78.09999999999999</v>
       </c>
       <c r="AF291">
-        <v>26.9523610264621</v>
+        <v>27.091906884705</v>
       </c>
       <c r="AG291">
         <v>0.3162291293130229</v>
@@ -31849,10 +33310,13 @@
         <v>54.13</v>
       </c>
       <c r="AD292">
-        <v>-1.54196523776718</v>
+        <v>-1.6</v>
+      </c>
+      <c r="AE292">
+        <v>69.5</v>
       </c>
       <c r="AF292">
-        <v>25.5657309854272</v>
+        <v>25.080008609841</v>
       </c>
       <c r="AG292">
         <v>0.2851266880708015</v>
@@ -31961,6 +33425,15 @@
       <c r="AC293">
         <v>71.34</v>
       </c>
+      <c r="AD293">
+        <v>-1.6</v>
+      </c>
+      <c r="AE293">
+        <v>69.3</v>
+      </c>
+      <c r="AF293">
+        <v>24.642726442952</v>
+      </c>
       <c r="AG293">
         <v>0.3363673435847722</v>
       </c>
@@ -32068,6 +33541,15 @@
       <c r="AC294">
         <v>64.3</v>
       </c>
+      <c r="AD294">
+        <v>-3.4</v>
+      </c>
+      <c r="AE294">
+        <v>68</v>
+      </c>
+      <c r="AF294">
+        <v>25.684481352805</v>
+      </c>
       <c r="AG294">
         <v>0.3258294205634602</v>
       </c>
@@ -32175,6 +33657,15 @@
       <c r="AC295">
         <v>41.96</v>
       </c>
+      <c r="AD295">
+        <v>-5.9</v>
+      </c>
+      <c r="AE295">
+        <v>81.7</v>
+      </c>
+      <c r="AF295">
+        <v>26.983713475692</v>
+      </c>
       <c r="AG295">
         <v>0.386093303948417</v>
       </c>
@@ -32282,6 +33773,15 @@
       <c r="AC296">
         <v>70.86</v>
       </c>
+      <c r="AD296">
+        <v>-7.2</v>
+      </c>
+      <c r="AE296">
+        <v>88.3</v>
+      </c>
+      <c r="AF296">
+        <v>29.98345285686</v>
+      </c>
       <c r="AG296">
         <v>0.3904936405966725</v>
       </c>
@@ -32389,6 +33889,15 @@
       <c r="AC297">
         <v>100.93</v>
       </c>
+      <c r="AD297">
+        <v>-9.4</v>
+      </c>
+      <c r="AE297">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="AF297">
+        <v>27.251410791841</v>
+      </c>
       <c r="AG297">
         <v>0.3625964102769348</v>
       </c>
@@ -32496,6 +34005,15 @@
       <c r="AC298">
         <v>82.48999999999999</v>
       </c>
+      <c r="AD298">
+        <v>-12.5</v>
+      </c>
+      <c r="AE298">
+        <v>91.3</v>
+      </c>
+      <c r="AF298">
+        <v>27.233359057137</v>
+      </c>
       <c r="AG298">
         <v>0.4032822978810752</v>
       </c>
@@ -32603,6 +34121,15 @@
       <c r="AC299">
         <v>52.32</v>
       </c>
+      <c r="AD299">
+        <v>-8.1</v>
+      </c>
+      <c r="AE299">
+        <v>129.8</v>
+      </c>
+      <c r="AF299">
+        <v>14.884998736729</v>
+      </c>
       <c r="AG299">
         <v>1.361934921437563</v>
       </c>
@@ -32710,6 +34237,15 @@
       <c r="AC300">
         <v>43.64</v>
       </c>
+      <c r="AD300">
+        <v>-8.5</v>
+      </c>
+      <c r="AE300">
+        <v>138.4</v>
+      </c>
+      <c r="AF300">
+        <v>11.223238545101</v>
+      </c>
       <c r="AG300">
         <v>1.096917363467532</v>
       </c>
@@ -32817,6 +34353,15 @@
       <c r="AC301">
         <v>54.13</v>
       </c>
+      <c r="AD301">
+        <v>-13.3</v>
+      </c>
+      <c r="AE301">
+        <v>133.6</v>
+      </c>
+      <c r="AF301">
+        <v>8.493169486935599</v>
+      </c>
       <c r="AG301">
         <v>1.11715499189858</v>
       </c>
@@ -32924,6 +34469,15 @@
       <c r="AC302">
         <v>71.34</v>
       </c>
+      <c r="AD302">
+        <v>-31</v>
+      </c>
+      <c r="AE302">
+        <v>175.3</v>
+      </c>
+      <c r="AF302">
+        <v>6.8844126251794</v>
+      </c>
       <c r="AG302">
         <v>1.149642408410487</v>
       </c>
@@ -33031,6 +34585,15 @@
       <c r="AC303">
         <v>64.3</v>
       </c>
+      <c r="AD303">
+        <v>-10.9</v>
+      </c>
+      <c r="AE303">
+        <v>206</v>
+      </c>
+      <c r="AF303">
+        <v>10.089038802382</v>
+      </c>
       <c r="AG303">
         <v>0.792500473871768</v>
       </c>
@@ -33138,6 +34701,15 @@
       <c r="AC304">
         <v>41.96</v>
       </c>
+      <c r="AD304">
+        <v>-6.6</v>
+      </c>
+      <c r="AE304">
+        <v>336.5</v>
+      </c>
+      <c r="AF304">
+        <v>4.5309807354375</v>
+      </c>
       <c r="AG304">
         <v>0.3598697166024167</v>
       </c>
@@ -33245,6 +34817,15 @@
       <c r="AC305">
         <v>70.86</v>
       </c>
+      <c r="AD305">
+        <v>-5.8</v>
+      </c>
+      <c r="AE305">
+        <v>254.2</v>
+      </c>
+      <c r="AF305">
+        <v>7.2837669267974</v>
+      </c>
       <c r="AG305">
         <v>0.38645416567327</v>
       </c>
@@ -33352,6 +34933,15 @@
       <c r="AC306">
         <v>100.93</v>
       </c>
+      <c r="AD306">
+        <v>-5.3</v>
+      </c>
+      <c r="AE306">
+        <v>164.4</v>
+      </c>
+      <c r="AF306">
+        <v>9.849302608263301</v>
+      </c>
       <c r="AG306">
         <v>0.5978481734576608</v>
       </c>
@@ -33458,6 +35048,15 @@
       </c>
       <c r="AC307">
         <v>82.48999999999999</v>
+      </c>
+      <c r="AD307">
+        <v>-1.2</v>
+      </c>
+      <c r="AE307">
+        <v>138.5</v>
+      </c>
+      <c r="AF307">
+        <v>11.872607940332</v>
       </c>
       <c r="AG307">
         <v>0.4909768294336784</v>
